--- a/data/台股財報估值.xlsx
+++ b/data/台股財報估值.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V133"/>
+  <dimension ref="A1:V135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1842,12 +1842,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1857,69 +1857,69 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.6</v>
+        <v>7.1</v>
       </c>
       <c r="F20" t="n">
-        <v>14.9</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
         <v>24.2</v>
       </c>
       <c r="H20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I20" t="n">
-        <v>18.3</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>16.3</v>
+        <v>1.5</v>
       </c>
       <c r="K20" t="n">
-        <v>14.12</v>
+        <v>6.96</v>
       </c>
       <c r="L20" t="n">
-        <v>28.8</v>
+        <v>17.5</v>
       </c>
       <c r="M20" t="n">
-        <v>39.7</v>
+        <v>88.2</v>
       </c>
       <c r="N20" t="n">
-        <v>215</v>
+        <v>45</v>
       </c>
       <c r="O20" t="n">
-        <v>1.21</v>
+        <v>6.49</v>
       </c>
       <c r="P20" t="n">
-        <v>13.2</v>
+        <v>62.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>394</v>
+        <v>188</v>
       </c>
       <c r="R20" t="n">
-        <v>27.9</v>
+        <v>27.01</v>
       </c>
       <c r="S20" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="T20" t="n">
-        <v>8.57</v>
+        <v>5.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.79</v>
+        <v>3.46</v>
       </c>
       <c r="V20" t="n">
-        <v>15.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>敦陽科</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1929,69 +1929,69 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.3</v>
+        <v>2.6</v>
       </c>
       <c r="F21" t="n">
-        <v>10.4</v>
+        <v>14.9</v>
       </c>
       <c r="G21" t="n">
         <v>24.2</v>
       </c>
       <c r="H21" t="n">
-        <v>23.9</v>
+        <v>37</v>
       </c>
       <c r="I21" t="n">
-        <v>11.8</v>
+        <v>18.3</v>
       </c>
       <c r="J21" t="n">
-        <v>10.2</v>
+        <v>16.3</v>
       </c>
       <c r="K21" t="n">
-        <v>8.390000000000001</v>
+        <v>14.12</v>
       </c>
       <c r="L21" t="n">
-        <v>29.9</v>
+        <v>28.8</v>
       </c>
       <c r="M21" t="n">
-        <v>64.40000000000001</v>
+        <v>39.7</v>
       </c>
       <c r="N21" t="n">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="P21" t="n">
-        <v>10.8</v>
+        <v>13.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>154.5</v>
+        <v>394</v>
       </c>
       <c r="R21" t="n">
-        <v>18.41</v>
+        <v>27.9</v>
       </c>
       <c r="S21" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="T21" t="n">
-        <v>5.5</v>
+        <v>8.57</v>
       </c>
       <c r="U21" t="n">
-        <v>5.05</v>
+        <v>2.79</v>
       </c>
       <c r="V21" t="n">
-        <v>16.4</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>敦陽科</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -2001,58 +2001,58 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>10.4</v>
       </c>
       <c r="G22" t="n">
         <v>24.2</v>
       </c>
       <c r="H22" t="n">
-        <v>36</v>
+        <v>23.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="K22" t="n">
-        <v>6.96</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>17.5</v>
+        <v>29.9</v>
       </c>
       <c r="M22" t="n">
-        <v>88.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="O22" t="n">
-        <v>6.49</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>62.8</v>
+        <v>10.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>188</v>
+        <v>154.5</v>
       </c>
       <c r="R22" t="n">
-        <v>27.01</v>
+        <v>18.41</v>
       </c>
       <c r="S22" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="T22" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="U22" t="n">
-        <v>3.46</v>
+        <v>5.05</v>
       </c>
       <c r="V22" t="n">
-        <v>7.4</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="23">
@@ -2418,12 +2418,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>長聖</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -2433,69 +2433,69 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13.8</v>
+        <v>23.4</v>
       </c>
       <c r="F28" t="n">
-        <v>3.9</v>
+        <v>49.4</v>
       </c>
       <c r="G28" t="n">
         <v>21.9</v>
       </c>
       <c r="H28" t="n">
-        <v>28.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>44.9</v>
       </c>
       <c r="J28" t="n">
-        <v>2.9</v>
+        <v>48.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.91</v>
+        <v>5.27</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="M28" t="n">
-        <v>73.5</v>
+        <v>22.4</v>
       </c>
       <c r="N28" t="n">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="O28" t="n">
-        <v>2.05</v>
+        <v>1.16</v>
       </c>
       <c r="P28" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>74.3</v>
+        <v>142.5</v>
       </c>
       <c r="R28" t="n">
-        <v>19</v>
+        <v>27.04</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T28" t="n">
-        <v>3.12</v>
+        <v>4.87</v>
       </c>
       <c r="U28" t="n">
-        <v>5.06</v>
+        <v>2.81</v>
       </c>
       <c r="V28" t="n">
-        <v>2.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>長聖</t>
+          <t>大樹</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -2505,58 +2505,58 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>23.4</v>
+        <v>13.8</v>
       </c>
       <c r="F29" t="n">
-        <v>49.4</v>
+        <v>3.9</v>
       </c>
       <c r="G29" t="n">
         <v>21.9</v>
       </c>
       <c r="H29" t="n">
-        <v>73.09999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="I29" t="n">
-        <v>44.9</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
-        <v>48.4</v>
+        <v>2.9</v>
       </c>
       <c r="K29" t="n">
-        <v>5.27</v>
+        <v>3.91</v>
       </c>
       <c r="L29" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="M29" t="n">
-        <v>22.4</v>
+        <v>73.5</v>
       </c>
       <c r="N29" t="n">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="O29" t="n">
-        <v>1.16</v>
+        <v>2.05</v>
       </c>
       <c r="P29" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="Q29" t="n">
-        <v>142.5</v>
+        <v>74.3</v>
       </c>
       <c r="R29" t="n">
-        <v>27.04</v>
+        <v>19</v>
       </c>
       <c r="S29" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>4.87</v>
+        <v>3.12</v>
       </c>
       <c r="U29" t="n">
-        <v>2.81</v>
+        <v>5.06</v>
       </c>
       <c r="V29" t="n">
-        <v>25</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30">
@@ -3642,12 +3642,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>緯軟</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -3657,69 +3657,69 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17</v>
+        <v>2.8</v>
       </c>
       <c r="F45" t="n">
-        <v>6.1</v>
+        <v>15.4</v>
       </c>
       <c r="G45" t="n">
         <v>17.6</v>
       </c>
       <c r="H45" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="I45" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>5.5</v>
+        <v>14.3</v>
       </c>
       <c r="K45" t="n">
-        <v>9.26</v>
+        <v>6.07</v>
       </c>
       <c r="L45" t="n">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="M45" t="n">
-        <v>34.8</v>
+        <v>39.6</v>
       </c>
       <c r="N45" t="n">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="O45" t="n">
-        <v>0.53</v>
+        <v>1.71</v>
       </c>
       <c r="P45" t="n">
-        <v>3.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>132.5</v>
+        <v>155</v>
       </c>
       <c r="R45" t="n">
-        <v>14.31</v>
+        <v>25.54</v>
       </c>
       <c r="S45" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="T45" t="n">
-        <v>2.22</v>
+        <v>4.56</v>
       </c>
       <c r="U45" t="n">
-        <v>3.88</v>
+        <v>3.23</v>
       </c>
       <c r="V45" t="n">
-        <v>29.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>緯軟</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -3729,58 +3729,58 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.8</v>
+        <v>17</v>
       </c>
       <c r="F46" t="n">
-        <v>15.4</v>
+        <v>6.1</v>
       </c>
       <c r="G46" t="n">
         <v>17.6</v>
       </c>
       <c r="H46" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="J46" t="n">
-        <v>14.3</v>
+        <v>5.5</v>
       </c>
       <c r="K46" t="n">
-        <v>6.07</v>
+        <v>9.26</v>
       </c>
       <c r="L46" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="M46" t="n">
-        <v>39.6</v>
+        <v>34.8</v>
       </c>
       <c r="N46" t="n">
-        <v>183</v>
+        <v>266</v>
       </c>
       <c r="O46" t="n">
-        <v>1.71</v>
+        <v>0.53</v>
       </c>
       <c r="P46" t="n">
-        <v>10.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>155</v>
+        <v>132.5</v>
       </c>
       <c r="R46" t="n">
-        <v>25.54</v>
+        <v>14.31</v>
       </c>
       <c r="S46" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="T46" t="n">
-        <v>4.56</v>
+        <v>2.22</v>
       </c>
       <c r="U46" t="n">
-        <v>3.23</v>
+        <v>3.88</v>
       </c>
       <c r="V46" t="n">
-        <v>19</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="47">
@@ -3858,12 +3858,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -3873,58 +3873,58 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.2</v>
+        <v>11.1</v>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="G48" t="n">
         <v>17.1</v>
       </c>
       <c r="H48" t="n">
-        <v>35.5</v>
+        <v>25.9</v>
       </c>
       <c r="I48" t="n">
-        <v>16.4</v>
+        <v>18.1</v>
       </c>
       <c r="J48" t="n">
-        <v>13.3</v>
+        <v>14.8</v>
       </c>
       <c r="K48" t="n">
-        <v>27.11</v>
+        <v>8.23</v>
       </c>
       <c r="L48" t="n">
-        <v>22.3</v>
+        <v>18.6</v>
       </c>
       <c r="M48" t="n">
-        <v>47.8</v>
+        <v>55.1</v>
       </c>
       <c r="N48" t="n">
-        <v>195</v>
+        <v>111</v>
       </c>
       <c r="O48" t="n">
-        <v>1.28</v>
+        <v>2.74</v>
       </c>
       <c r="P48" t="n">
-        <v>535.6</v>
+        <v>107</v>
       </c>
       <c r="Q48" t="n">
-        <v>2150</v>
+        <v>181</v>
       </c>
       <c r="R48" t="n">
-        <v>79.31</v>
+        <v>21.99</v>
       </c>
       <c r="S48" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="T48" t="n">
-        <v>18.64</v>
+        <v>4.15</v>
       </c>
       <c r="U48" t="n">
-        <v>0.54</v>
+        <v>3.31</v>
       </c>
       <c r="V48" t="n">
-        <v>43.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="49">
@@ -4002,12 +4002,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -4017,58 +4017,58 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11.1</v>
+        <v>15.2</v>
       </c>
       <c r="F50" t="n">
-        <v>11.9</v>
+        <v>10</v>
       </c>
       <c r="G50" t="n">
         <v>17.1</v>
       </c>
       <c r="H50" t="n">
-        <v>25.9</v>
+        <v>35.5</v>
       </c>
       <c r="I50" t="n">
-        <v>18.1</v>
+        <v>16.4</v>
       </c>
       <c r="J50" t="n">
-        <v>14.8</v>
+        <v>13.3</v>
       </c>
       <c r="K50" t="n">
-        <v>8.23</v>
+        <v>27.11</v>
       </c>
       <c r="L50" t="n">
-        <v>18.6</v>
+        <v>22.3</v>
       </c>
       <c r="M50" t="n">
-        <v>55.1</v>
+        <v>47.8</v>
       </c>
       <c r="N50" t="n">
-        <v>111</v>
+        <v>195</v>
       </c>
       <c r="O50" t="n">
-        <v>2.74</v>
+        <v>1.28</v>
       </c>
       <c r="P50" t="n">
-        <v>107</v>
+        <v>535.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>181</v>
+        <v>2150</v>
       </c>
       <c r="R50" t="n">
-        <v>21.99</v>
+        <v>79.31</v>
       </c>
       <c r="S50" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="T50" t="n">
-        <v>4.15</v>
+        <v>18.64</v>
       </c>
       <c r="U50" t="n">
-        <v>3.31</v>
+        <v>0.54</v>
       </c>
       <c r="V50" t="n">
-        <v>3.6</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="51">
@@ -4578,12 +4578,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -4593,58 +4593,58 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>-0.8</v>
+        <v>13.3</v>
       </c>
       <c r="F58" t="n">
-        <v>15.7</v>
+        <v>13.5</v>
       </c>
       <c r="G58" t="n">
         <v>15.8</v>
       </c>
       <c r="H58" t="n">
-        <v>18.3</v>
+        <v>30</v>
       </c>
       <c r="I58" t="n">
-        <v>5.6</v>
+        <v>11.4</v>
       </c>
       <c r="J58" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>8.640000000000001</v>
+        <v>7.57</v>
       </c>
       <c r="L58" t="n">
-        <v>21.8</v>
+        <v>9.9</v>
       </c>
       <c r="M58" t="n">
-        <v>25.7</v>
+        <v>46.1</v>
       </c>
       <c r="N58" t="n">
-        <v>377</v>
+        <v>200</v>
       </c>
       <c r="O58" t="n">
-        <v>0.01</v>
+        <v>3.9</v>
       </c>
       <c r="P58" t="n">
-        <v>-2.1</v>
+        <v>13.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>870</v>
+        <v>304</v>
       </c>
       <c r="R58" t="n">
-        <v>100.69</v>
+        <v>40.16</v>
       </c>
       <c r="S58" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="T58" t="n">
-        <v>21.95</v>
+        <v>4.01</v>
       </c>
       <c r="U58" t="n">
-        <v>0.4</v>
+        <v>1.48</v>
       </c>
       <c r="V58" t="n">
-        <v>30</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="59">
@@ -4722,12 +4722,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -4737,58 +4737,58 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>13.3</v>
+        <v>-0.8</v>
       </c>
       <c r="F60" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="G60" t="n">
         <v>15.8</v>
       </c>
       <c r="H60" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J60" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="K60" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="L60" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="M60" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="N60" t="n">
+        <v>377</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>870</v>
+      </c>
+      <c r="R60" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="S60" t="n">
+        <v>94</v>
+      </c>
+      <c r="T60" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V60" t="n">
         <v>30</v>
-      </c>
-      <c r="I60" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J60" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K60" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="L60" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M60" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="N60" t="n">
-        <v>200</v>
-      </c>
-      <c r="O60" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P60" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>304</v>
-      </c>
-      <c r="R60" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="S60" t="n">
-        <v>97</v>
-      </c>
-      <c r="T60" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V60" t="n">
-        <v>26.9</v>
       </c>
     </row>
     <row r="61">
@@ -5514,12 +5514,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>台特化</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -5529,69 +5529,69 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>126.1</v>
+        <v>10.9</v>
       </c>
       <c r="F71" t="n">
-        <v>41.8</v>
+        <v>23.2</v>
       </c>
       <c r="G71" t="n">
         <v>14.1</v>
       </c>
       <c r="H71" t="n">
-        <v>53.1</v>
+        <v>39.8</v>
       </c>
       <c r="I71" t="n">
-        <v>42.8</v>
+        <v>21.3</v>
       </c>
       <c r="J71" t="n">
-        <v>36.1</v>
+        <v>26.7</v>
       </c>
       <c r="K71" t="n">
-        <v>4.84</v>
+        <v>7.68</v>
       </c>
       <c r="L71" t="n">
-        <v>20.7</v>
+        <v>14.7</v>
       </c>
       <c r="M71" t="n">
-        <v>42.3</v>
+        <v>36</v>
       </c>
       <c r="N71" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="O71" t="n">
-        <v>1.36</v>
+        <v>0.63</v>
       </c>
       <c r="P71" t="n">
-        <v>8.800000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="Q71" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="R71" t="n">
-        <v>58.47</v>
+        <v>38.15</v>
       </c>
       <c r="S71" t="n">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="T71" t="n">
-        <v>12.02</v>
+        <v>5.71</v>
       </c>
       <c r="U71" t="n">
-        <v>1.06</v>
+        <v>1.57</v>
       </c>
       <c r="V71" t="n">
-        <v>241.2</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>台特化</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -5601,58 +5601,58 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>10.9</v>
+        <v>126.1</v>
       </c>
       <c r="F72" t="n">
-        <v>23.2</v>
+        <v>41.8</v>
       </c>
       <c r="G72" t="n">
         <v>14.1</v>
       </c>
       <c r="H72" t="n">
-        <v>39.8</v>
+        <v>53.1</v>
       </c>
       <c r="I72" t="n">
-        <v>21.3</v>
+        <v>42.8</v>
       </c>
       <c r="J72" t="n">
-        <v>26.7</v>
+        <v>36.1</v>
       </c>
       <c r="K72" t="n">
-        <v>7.68</v>
+        <v>4.84</v>
       </c>
       <c r="L72" t="n">
-        <v>14.7</v>
+        <v>20.7</v>
       </c>
       <c r="M72" t="n">
-        <v>36</v>
+        <v>42.3</v>
       </c>
       <c r="N72" t="n">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="O72" t="n">
-        <v>0.63</v>
+        <v>1.36</v>
       </c>
       <c r="P72" t="n">
-        <v>-1.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q72" t="n">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="R72" t="n">
-        <v>38.15</v>
+        <v>58.47</v>
       </c>
       <c r="S72" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="T72" t="n">
-        <v>5.71</v>
+        <v>12.02</v>
       </c>
       <c r="U72" t="n">
-        <v>1.57</v>
+        <v>1.06</v>
       </c>
       <c r="V72" t="n">
-        <v>16.6</v>
+        <v>241.2</v>
       </c>
     </row>
     <row r="73">
@@ -6666,12 +6666,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>世禾</t>
+          <t>遠雄港</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -6681,69 +6681,69 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="F87" t="n">
-        <v>15.7</v>
+        <v>28.5</v>
       </c>
       <c r="G87" t="n">
         <v>10.5</v>
       </c>
       <c r="H87" t="n">
-        <v>35.6</v>
+        <v>50.4</v>
       </c>
       <c r="I87" t="n">
-        <v>17.5</v>
+        <v>39.2</v>
       </c>
       <c r="J87" t="n">
-        <v>16.3</v>
+        <v>27</v>
       </c>
       <c r="K87" t="n">
-        <v>8.69</v>
+        <v>3.24</v>
       </c>
       <c r="L87" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="M87" t="n">
-        <v>19.3</v>
+        <v>58</v>
       </c>
       <c r="N87" t="n">
-        <v>434</v>
+        <v>48</v>
       </c>
       <c r="O87" t="n">
-        <v>-0.79</v>
+        <v>1.91</v>
       </c>
       <c r="P87" t="n">
-        <v>-6.2</v>
+        <v>18.5</v>
       </c>
       <c r="Q87" t="n">
-        <v>212.5</v>
+        <v>52.2</v>
       </c>
       <c r="R87" t="n">
-        <v>24.45</v>
+        <v>16.11</v>
       </c>
       <c r="S87" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="T87" t="n">
-        <v>2.57</v>
+        <v>1.69</v>
       </c>
       <c r="U87" t="n">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="V87" t="n">
-        <v>21.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>遠雄港</t>
+          <t>世禾</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -6753,58 +6753,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="F88" t="n">
-        <v>28.5</v>
+        <v>15.7</v>
       </c>
       <c r="G88" t="n">
         <v>10.5</v>
       </c>
       <c r="H88" t="n">
-        <v>50.4</v>
+        <v>35.6</v>
       </c>
       <c r="I88" t="n">
-        <v>39.2</v>
+        <v>17.5</v>
       </c>
       <c r="J88" t="n">
-        <v>27</v>
+        <v>16.3</v>
       </c>
       <c r="K88" t="n">
-        <v>3.24</v>
+        <v>8.69</v>
       </c>
       <c r="L88" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="M88" t="n">
-        <v>58</v>
+        <v>19.3</v>
       </c>
       <c r="N88" t="n">
-        <v>48</v>
+        <v>434</v>
       </c>
       <c r="O88" t="n">
-        <v>1.91</v>
+        <v>-0.79</v>
       </c>
       <c r="P88" t="n">
-        <v>18.5</v>
+        <v>-6.2</v>
       </c>
       <c r="Q88" t="n">
-        <v>52.2</v>
+        <v>212.5</v>
       </c>
       <c r="R88" t="n">
-        <v>16.11</v>
+        <v>24.45</v>
       </c>
       <c r="S88" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="T88" t="n">
-        <v>1.69</v>
+        <v>2.57</v>
       </c>
       <c r="U88" t="n">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="V88" t="n">
-        <v>39</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="89">
@@ -7950,12 +7950,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -7965,69 +7965,69 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4.3</v>
+        <v>-2.9</v>
       </c>
       <c r="F105" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G105" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="H105" t="n">
-        <v>17</v>
+        <v>29.3</v>
       </c>
       <c r="I105" t="n">
-        <v>-2</v>
+        <v>7.5</v>
       </c>
       <c r="J105" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="K105" t="n">
-        <v>-1.84</v>
+        <v>4.58</v>
       </c>
       <c r="L105" t="n">
-        <v>-7.2</v>
+        <v>4</v>
       </c>
       <c r="M105" t="n">
-        <v>65.7</v>
+        <v>31.3</v>
       </c>
       <c r="N105" t="n">
-        <v>94</v>
+        <v>229</v>
       </c>
       <c r="O105" t="n">
-        <v>-0.67</v>
+        <v>3.06</v>
       </c>
       <c r="P105" t="n">
-        <v>-6.6</v>
+        <v>29.5</v>
       </c>
       <c r="Q105" t="n">
-        <v>129</v>
+        <v>343.5</v>
       </c>
       <c r="R105" t="n">
-        <v>65.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="S105" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="T105" t="n">
-        <v>8.01</v>
+        <v>3.16</v>
       </c>
       <c r="U105" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V105" t="n">
-        <v>-13.9</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -8037,69 +8037,69 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.2</v>
+        <v>4.3</v>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="G106" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="H106" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="I106" t="n">
-        <v>4.8</v>
+        <v>-2</v>
       </c>
       <c r="J106" t="n">
-        <v>4.1</v>
+        <v>-6</v>
       </c>
       <c r="K106" t="n">
-        <v>2.79</v>
+        <v>-1.84</v>
       </c>
       <c r="L106" t="n">
-        <v>7</v>
+        <v>-7.2</v>
       </c>
       <c r="M106" t="n">
-        <v>17.9</v>
+        <v>65.7</v>
       </c>
       <c r="N106" t="n">
-        <v>451</v>
+        <v>94</v>
       </c>
       <c r="O106" t="n">
-        <v>1.85</v>
+        <v>-0.67</v>
       </c>
       <c r="P106" t="n">
-        <v>409.6</v>
+        <v>-6.6</v>
       </c>
       <c r="Q106" t="n">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="R106" t="n">
-        <v>19.35</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="S106" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="T106" t="n">
-        <v>1.36</v>
+        <v>8.01</v>
       </c>
       <c r="U106" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>26.9</v>
+        <v>-13.9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>健喬</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -8109,69 +8109,69 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>17.6</v>
+        <v>3</v>
       </c>
       <c r="F107" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I107" t="n">
         <v>8.9</v>
       </c>
-      <c r="G107" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H107" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="I107" t="n">
-        <v>11.8</v>
-      </c>
       <c r="J107" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="K107" t="n">
-        <v>1.61</v>
+        <v>2.39</v>
       </c>
       <c r="L107" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="M107" t="n">
-        <v>28.3</v>
+        <v>36.6</v>
       </c>
       <c r="N107" t="n">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="O107" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="P107" t="n">
-        <v>2.9</v>
+        <v>23.6</v>
       </c>
       <c r="Q107" t="n">
-        <v>30.9</v>
+        <v>72.2</v>
       </c>
       <c r="R107" t="n">
-        <v>19.22</v>
+        <v>30.21</v>
       </c>
       <c r="S107" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="T107" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="U107" t="n">
-        <v>5.33</v>
+        <v>2.86</v>
       </c>
       <c r="V107" t="n">
-        <v>12.9</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>奈米醫材</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -8181,69 +8181,69 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>30.5</v>
+        <v>0.2</v>
       </c>
       <c r="F108" t="n">
-        <v>9.300000000000001</v>
+        <v>3</v>
       </c>
       <c r="G108" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="H108" t="n">
-        <v>58.4</v>
+        <v>6.6</v>
       </c>
       <c r="I108" t="n">
-        <v>10.2</v>
+        <v>4.8</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.2</v>
+        <v>4.1</v>
       </c>
       <c r="K108" t="n">
-        <v>0.85</v>
+        <v>2.79</v>
       </c>
       <c r="L108" t="n">
-        <v>-0.5</v>
+        <v>7</v>
       </c>
       <c r="M108" t="n">
-        <v>37.5</v>
+        <v>17.9</v>
       </c>
       <c r="N108" t="n">
-        <v>207</v>
+        <v>451</v>
       </c>
       <c r="O108" t="n">
-        <v>-1.67</v>
+        <v>1.85</v>
       </c>
       <c r="P108" t="n">
-        <v>-0.2</v>
+        <v>409.6</v>
       </c>
       <c r="Q108" t="n">
-        <v>72.90000000000001</v>
+        <v>54</v>
       </c>
       <c r="R108" t="n">
-        <v>85.76000000000001</v>
+        <v>19.35</v>
       </c>
       <c r="S108" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="T108" t="n">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="U108" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="V108" t="n">
-        <v>43.3</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>健喬</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -8253,69 +8253,69 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4</v>
+        <v>17.6</v>
       </c>
       <c r="F109" t="n">
-        <v>3.7</v>
+        <v>8.9</v>
       </c>
       <c r="G109" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="H109" t="n">
-        <v>47.6</v>
+        <v>42.8</v>
       </c>
       <c r="I109" t="n">
-        <v>29.9</v>
+        <v>11.8</v>
       </c>
       <c r="J109" t="n">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="K109" t="n">
-        <v>7.64</v>
+        <v>1.61</v>
       </c>
       <c r="L109" t="n">
-        <v>16.6</v>
+        <v>5.9</v>
       </c>
       <c r="M109" t="n">
-        <v>25.3</v>
+        <v>28.3</v>
       </c>
       <c r="N109" t="n">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="O109" t="n">
-        <v>1.13</v>
+        <v>0.76</v>
       </c>
       <c r="P109" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q109" t="n">
-        <v>2375</v>
+        <v>30.9</v>
       </c>
       <c r="R109" t="n">
-        <v>310.86</v>
+        <v>19.22</v>
       </c>
       <c r="S109" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="T109" t="n">
-        <v>51.83</v>
+        <v>1.76</v>
       </c>
       <c r="U109" t="n">
-        <v>0.17</v>
+        <v>5.33</v>
       </c>
       <c r="V109" t="n">
-        <v>118.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>奈米醫材</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -8325,69 +8325,69 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>15.3</v>
+        <v>30.5</v>
       </c>
       <c r="F110" t="n">
-        <v>4.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="H110" t="n">
-        <v>17.8</v>
+        <v>58.4</v>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>10.2</v>
       </c>
       <c r="J110" t="n">
-        <v>0.1</v>
+        <v>-1.2</v>
       </c>
       <c r="K110" t="n">
-        <v>-0.14</v>
+        <v>0.85</v>
       </c>
       <c r="L110" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="M110" t="n">
-        <v>59.7</v>
+        <v>37.5</v>
       </c>
       <c r="N110" t="n">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="O110" t="n">
-        <v>7.24</v>
+        <v>-1.67</v>
       </c>
       <c r="P110" t="n">
-        <v>-15.2</v>
+        <v>-0.2</v>
       </c>
       <c r="Q110" t="n">
-        <v>525</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="R110" t="n">
-        <v>2019.23</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="S110" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="T110" t="n">
-        <v>9.34</v>
+        <v>1.84</v>
       </c>
       <c r="U110" t="n">
-        <v>0.04</v>
+        <v>1.78</v>
       </c>
       <c r="V110" t="n">
-        <v>4.9</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>矽統</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -8397,69 +8397,69 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>83.3</v>
+        <v>4</v>
       </c>
       <c r="F111" t="n">
-        <v>114.5</v>
+        <v>3.7</v>
       </c>
       <c r="G111" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="H111" t="n">
-        <v>28.7</v>
+        <v>47.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6</v>
+        <v>29.9</v>
       </c>
       <c r="J111" t="n">
-        <v>30.7</v>
+        <v>25</v>
       </c>
       <c r="K111" t="n">
-        <v>1.7</v>
+        <v>7.64</v>
       </c>
       <c r="L111" t="n">
-        <v>4.2</v>
+        <v>16.6</v>
       </c>
       <c r="M111" t="n">
-        <v>9.199999999999999</v>
+        <v>25.3</v>
       </c>
       <c r="N111" t="n">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="O111" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="P111" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
       <c r="Q111" t="n">
-        <v>69.09999999999999</v>
+        <v>2375</v>
       </c>
       <c r="R111" t="n">
-        <v>40.65</v>
+        <v>310.86</v>
       </c>
       <c r="S111" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="T111" t="n">
-        <v>1.75</v>
+        <v>51.83</v>
       </c>
       <c r="U111" t="n">
-        <v>0.87</v>
+        <v>0.17</v>
       </c>
       <c r="V111" t="n">
-        <v>88.8</v>
+        <v>118.8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -8469,69 +8469,69 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>-1.3</v>
+        <v>15.3</v>
       </c>
       <c r="F112" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="G112" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="H112" t="n">
-        <v>14.5</v>
+        <v>17.8</v>
       </c>
       <c r="I112" t="n">
-        <v>-10.6</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
-        <v>-6.7</v>
+        <v>0.1</v>
       </c>
       <c r="K112" t="n">
-        <v>-0.83</v>
+        <v>-0.14</v>
       </c>
       <c r="L112" t="n">
-        <v>-1.6</v>
+        <v>0.5</v>
       </c>
       <c r="M112" t="n">
-        <v>9.1</v>
+        <v>59.7</v>
       </c>
       <c r="N112" t="n">
-        <v>1107</v>
+        <v>167</v>
       </c>
       <c r="O112" t="n">
-        <v>0.97</v>
+        <v>7.24</v>
       </c>
       <c r="P112" t="n">
-        <v>-2.4</v>
+        <v>-15.2</v>
       </c>
       <c r="Q112" t="n">
-        <v>902</v>
+        <v>525</v>
       </c>
       <c r="R112" t="n">
-        <v>5637.5</v>
+        <v>2019.23</v>
       </c>
       <c r="S112" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="T112" t="n">
-        <v>14.11</v>
+        <v>9.34</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="V112" t="n">
-        <v>-24.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>精確</t>
+          <t>矽統</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -8541,69 +8541,69 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>54.8</v>
+        <v>83.3</v>
       </c>
       <c r="F113" t="n">
-        <v>0.4</v>
+        <v>114.5</v>
       </c>
       <c r="G113" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="H113" t="n">
-        <v>11.8</v>
+        <v>28.7</v>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>-0.6</v>
       </c>
       <c r="J113" t="n">
-        <v>2.1</v>
+        <v>30.7</v>
       </c>
       <c r="K113" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="L113" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="M113" t="n">
-        <v>62.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N113" t="n">
-        <v>96</v>
+        <v>298</v>
       </c>
       <c r="O113" t="n">
-        <v>5.72</v>
+        <v>0.6</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q113" t="n">
-        <v>84.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="R113" t="n">
-        <v>69.34</v>
+        <v>40.65</v>
       </c>
       <c r="S113" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="T113" t="n">
-        <v>3.17</v>
+        <v>1.75</v>
       </c>
       <c r="U113" t="n">
-        <v>1.18</v>
+        <v>0.87</v>
       </c>
       <c r="V113" t="n">
-        <v>21.9</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -8613,197 +8613,213 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>11.7</v>
+        <v>-1.3</v>
       </c>
       <c r="F114" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="H114" t="n">
-        <v>84.3</v>
+        <v>14.5</v>
       </c>
       <c r="I114" t="n">
-        <v>15.3</v>
+        <v>-10.6</v>
       </c>
       <c r="J114" t="n">
-        <v>11.6</v>
+        <v>-6.7</v>
       </c>
       <c r="K114" t="n">
-        <v>3.68</v>
+        <v>-0.83</v>
       </c>
       <c r="L114" t="n">
-        <v>6.1</v>
+        <v>-1.6</v>
       </c>
       <c r="M114" t="n">
-        <v>22.2</v>
+        <v>9.1</v>
       </c>
       <c r="N114" t="n">
-        <v>273</v>
+        <v>1107</v>
       </c>
       <c r="O114" t="n">
-        <v>-2.09</v>
+        <v>0.97</v>
       </c>
       <c r="P114" t="n">
-        <v>-6.1</v>
+        <v>-2.4</v>
       </c>
       <c r="Q114" t="n">
-        <v>69</v>
+        <v>902</v>
       </c>
       <c r="R114" t="n">
-        <v>18.75</v>
+        <v>5637.5</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="T114" t="n">
-        <v>1.14</v>
+        <v>14.11</v>
       </c>
       <c r="U114" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>-14.8</v>
+        <v>-24.8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
+          <t>精確</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>24</v>
-      </c>
-      <c r="F115" t="inlineStr"/>
+        <v>54.8</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.4</v>
+      </c>
       <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="H115" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K115" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M115" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+        <v>62.1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>96</v>
+      </c>
+      <c r="O115" t="n">
+        <v>5.72</v>
+      </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="Q115" t="n">
-        <v>32</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="R115" t="n">
-        <v>16.78</v>
+        <v>69.34</v>
       </c>
       <c r="S115" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="T115" t="n">
-        <v>1.41</v>
+        <v>3.17</v>
       </c>
       <c r="U115" t="n">
-        <v>3.43</v>
+        <v>1.18</v>
       </c>
       <c r="V115" t="n">
-        <v>117.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
+          <t>訊連</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>13</v>
-      </c>
-      <c r="F116" t="inlineStr"/>
+        <v>11.7</v>
+      </c>
+      <c r="F116" t="n">
+        <v>3.2</v>
+      </c>
       <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="H116" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="I116" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J116" t="n">
+        <v>11.6</v>
+      </c>
       <c r="K116" t="n">
-        <v>1.4</v>
+        <v>3.68</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="M116" t="n">
-        <v>93</v>
-      </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+        <v>22.2</v>
+      </c>
+      <c r="N116" t="n">
+        <v>273</v>
+      </c>
+      <c r="O116" t="n">
+        <v>-2.09</v>
+      </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>-6.1</v>
       </c>
       <c r="Q116" t="n">
-        <v>39.8</v>
+        <v>69</v>
       </c>
       <c r="R116" t="n">
-        <v>20.2</v>
+        <v>18.75</v>
       </c>
       <c r="S116" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="T116" t="n">
-        <v>2.17</v>
+        <v>1.14</v>
       </c>
       <c r="U116" t="n">
-        <v>3.27</v>
+        <v>5.22</v>
       </c>
       <c r="V116" t="n">
-        <v>82.7</v>
+        <v>-14.8</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8817,7 +8833,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>-24</v>
+        <v>8</v>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
@@ -8827,13 +8843,13 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>91.2</v>
+        <v>94.5</v>
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
@@ -8841,33 +8857,33 @@
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>30.4</v>
+        <v>37.6</v>
       </c>
       <c r="R117" t="n">
-        <v>17.44</v>
+        <v>19.79</v>
       </c>
       <c r="S117" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T117" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="U117" t="n">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="V117" t="n">
-        <v>-172.7</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8881,7 +8897,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>-5.9</v>
+        <v>13</v>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -8891,13 +8907,13 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="n">
-        <v>5.37</v>
+        <v>1.4</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>92.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
@@ -8905,33 +8921,33 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>138.5</v>
+        <v>39.8</v>
       </c>
       <c r="R118" t="n">
-        <v>16.55</v>
+        <v>20.2</v>
       </c>
       <c r="S118" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="T118" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="U118" t="n">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
       <c r="V118" t="n">
-        <v>-300.3</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8945,7 +8961,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
@@ -8955,13 +8971,13 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>94.5</v>
+        <v>91.7</v>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
@@ -8969,33 +8985,33 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>37.6</v>
+        <v>68.8</v>
       </c>
       <c r="R119" t="n">
-        <v>19.79</v>
+        <v>25.11</v>
       </c>
       <c r="S119" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T119" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="U119" t="n">
-        <v>3.86</v>
+        <v>3.24</v>
       </c>
       <c r="V119" t="n">
-        <v>58.3</v>
+        <v>227.3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9008,7 +9024,9 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
+      <c r="E120" t="n">
+        <v>-5.9</v>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
         <v>0</v>
@@ -9017,13 +9035,13 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
-        <v>1.14</v>
+        <v>5.37</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>90.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
@@ -9031,33 +9049,33 @@
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>19.6</v>
+        <v>138.5</v>
       </c>
       <c r="R120" t="n">
-        <v>12.84</v>
+        <v>16.55</v>
       </c>
       <c r="S120" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="T120" t="n">
-        <v>1.26</v>
+        <v>2.11</v>
       </c>
       <c r="U120" t="n">
-        <v>5.39</v>
+        <v>3.08</v>
       </c>
       <c r="V120" t="n">
-        <v>28.3</v>
+        <v>-300.3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9071,7 +9089,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>-13.5</v>
+        <v>24</v>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -9081,13 +9099,13 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="n">
-        <v>4.88</v>
+        <v>1.58</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>94.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
@@ -9095,33 +9113,33 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="R121" t="n">
-        <v>16.01</v>
+        <v>16.78</v>
       </c>
       <c r="S121" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T121" t="n">
-        <v>2.31</v>
+        <v>1.41</v>
       </c>
       <c r="U121" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="V121" t="n">
-        <v>28.8</v>
+        <v>117.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -9134,9 +9152,7 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E122" t="n">
-        <v>-4.1</v>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
         <v>0</v>
@@ -9145,13 +9161,13 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="n">
-        <v>0.52</v>
+        <v>1.14</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>88.3</v>
+        <v>90.8</v>
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
@@ -9159,33 +9175,33 @@
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>15.1</v>
+        <v>19.6</v>
       </c>
       <c r="R122" t="n">
-        <v>23.89</v>
+        <v>12.84</v>
       </c>
       <c r="S122" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="T122" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="U122" t="n">
-        <v>3.92</v>
+        <v>5.39</v>
       </c>
       <c r="V122" t="n">
-        <v>147.9</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9199,7 +9215,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>7.1</v>
+        <v>-24</v>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
@@ -9209,13 +9225,13 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="n">
-        <v>3.06</v>
+        <v>1.22</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>93.8</v>
+        <v>91.2</v>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
@@ -9223,33 +9239,33 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>70.5</v>
+        <v>30.4</v>
       </c>
       <c r="R123" t="n">
-        <v>17.28</v>
+        <v>17.44</v>
       </c>
       <c r="S123" t="n">
         <v>95</v>
       </c>
       <c r="T123" t="n">
-        <v>2.52</v>
+        <v>1.54</v>
       </c>
       <c r="U123" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="V123" t="n">
-        <v>76.09999999999999</v>
+        <v>-172.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9263,7 +9279,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>12.2</v>
+        <v>7.1</v>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
@@ -9273,13 +9289,13 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="n">
-        <v>1.57</v>
+        <v>3.06</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
@@ -9287,33 +9303,33 @@
         <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>35.8</v>
+        <v>70.5</v>
       </c>
       <c r="R124" t="n">
-        <v>16.89</v>
+        <v>17.28</v>
       </c>
       <c r="S124" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="T124" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="U124" t="n">
-        <v>3.91</v>
+        <v>3.55</v>
       </c>
       <c r="V124" t="n">
-        <v>24.8</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9327,7 +9343,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1.9</v>
+        <v>12.2</v>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
@@ -9337,13 +9353,13 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>91.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
@@ -9351,177 +9367,161 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>68.8</v>
+        <v>35.8</v>
       </c>
       <c r="R125" t="n">
-        <v>25.11</v>
+        <v>16.89</v>
       </c>
       <c r="S125" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="T125" t="n">
-        <v>2.53</v>
+        <v>2.03</v>
       </c>
       <c r="U125" t="n">
-        <v>3.24</v>
+        <v>3.91</v>
       </c>
       <c r="V125" t="n">
-        <v>227.3</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>今國光</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>國票金</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F126" t="n">
-        <v>-1.3</v>
-      </c>
+        <v>-4.1</v>
+      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="H126" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I126" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J126" t="n">
-        <v>7.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="n">
-        <v>1.73</v>
+        <v>0.52</v>
       </c>
       <c r="L126" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="N126" t="n">
-        <v>217</v>
-      </c>
-      <c r="O126" t="n">
-        <v>1.08</v>
-      </c>
+        <v>88.3</v>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
       <c r="P126" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>97.2</v>
+        <v>15.1</v>
       </c>
       <c r="R126" t="n">
-        <v>56.18</v>
+        <v>23.89</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="T126" t="n">
-        <v>4.97</v>
+        <v>1.17</v>
       </c>
       <c r="U126" t="n">
-        <v>0.51</v>
+        <v>3.92</v>
       </c>
       <c r="V126" t="n">
-        <v>70.7</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>揚明光</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="F127" t="n">
-        <v>-4</v>
-      </c>
+        <v>-13.5</v>
+      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="H127" t="n">
-        <v>18</v>
-      </c>
-      <c r="I127" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J127" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
-        <v>-0.07000000000000001</v>
+        <v>4.88</v>
       </c>
       <c r="L127" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="N127" t="n">
-        <v>219</v>
-      </c>
-      <c r="O127" t="n">
-        <v>-41.26</v>
-      </c>
+        <v>94.3</v>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
       <c r="P127" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>53.1</v>
+        <v>113</v>
       </c>
       <c r="R127" t="n">
-        <v>132.75</v>
+        <v>16.01</v>
       </c>
       <c r="S127" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="T127" t="n">
-        <v>3.69</v>
+        <v>2.31</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V127" t="n">
-        <v>16.1</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>新鉅科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -9531,69 +9531,69 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>-1.6</v>
+        <v>0.3</v>
       </c>
       <c r="F128" t="n">
-        <v>-22.3</v>
+        <v>-1.3</v>
       </c>
       <c r="G128" t="n">
-        <v>-11.8</v>
+        <v>-0.7</v>
       </c>
       <c r="H128" t="n">
-        <v>8.6</v>
+        <v>23.9</v>
       </c>
       <c r="I128" t="n">
-        <v>-19</v>
+        <v>8.9</v>
       </c>
       <c r="J128" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="K128" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="L128" t="n">
-        <v>14.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M128" t="n">
-        <v>31.3</v>
+        <v>33.3</v>
       </c>
       <c r="N128" t="n">
-        <v>293</v>
+        <v>217</v>
       </c>
       <c r="O128" t="n">
-        <v>-0.18</v>
+        <v>1.08</v>
       </c>
       <c r="P128" t="n">
-        <v>-10.3</v>
+        <v>-0.6</v>
       </c>
       <c r="Q128" t="n">
-        <v>33.6</v>
+        <v>97.2</v>
       </c>
       <c r="R128" t="n">
-        <v>16.02</v>
+        <v>56.18</v>
       </c>
       <c r="S128" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T128" t="n">
-        <v>2.3</v>
+        <v>4.97</v>
       </c>
       <c r="U128" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="V128" t="n">
-        <v>5.7</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -9603,69 +9603,69 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>15.3</v>
+        <v>-12.4</v>
       </c>
       <c r="F129" t="n">
-        <v>-36.2</v>
+        <v>-4</v>
       </c>
       <c r="G129" t="n">
-        <v>-12.6</v>
+        <v>-3.1</v>
       </c>
       <c r="H129" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="I129" t="n">
-        <v>22.4</v>
+        <v>-1.9</v>
       </c>
       <c r="J129" t="n">
-        <v>10.7</v>
+        <v>-0.3</v>
       </c>
       <c r="K129" t="n">
-        <v>2.53</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L129" t="n">
-        <v>6.9</v>
+        <v>-0.3</v>
       </c>
       <c r="M129" t="n">
-        <v>12.3</v>
+        <v>33.5</v>
       </c>
       <c r="N129" t="n">
-        <v>1077</v>
+        <v>219</v>
       </c>
       <c r="O129" t="n">
-        <v>2.3</v>
+        <v>-41.26</v>
       </c>
       <c r="P129" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q129" t="n">
-        <v>564</v>
+        <v>53.1</v>
       </c>
       <c r="R129" t="n">
-        <v>222.92</v>
+        <v>132.75</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="T129" t="n">
-        <v>16</v>
+        <v>3.69</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>54.4</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>新鉅科</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -9675,69 +9675,69 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>120.6</v>
+        <v>-1.6</v>
       </c>
       <c r="F130" t="n">
-        <v>-122.9</v>
+        <v>-22.3</v>
       </c>
       <c r="G130" t="n">
-        <v>-13.5</v>
+        <v>-11.8</v>
       </c>
       <c r="H130" t="n">
-        <v>89</v>
+        <v>8.6</v>
       </c>
       <c r="I130" t="n">
-        <v>33.3</v>
+        <v>-19</v>
       </c>
       <c r="J130" t="n">
-        <v>33.3</v>
+        <v>17.1</v>
       </c>
       <c r="K130" t="n">
-        <v>16.26</v>
+        <v>2.1</v>
       </c>
       <c r="L130" t="n">
-        <v>17.2</v>
+        <v>14.4</v>
       </c>
       <c r="M130" t="n">
-        <v>14.1</v>
+        <v>31.3</v>
       </c>
       <c r="N130" t="n">
-        <v>653</v>
+        <v>293</v>
       </c>
       <c r="O130" t="n">
-        <v>1</v>
+        <v>-0.18</v>
       </c>
       <c r="P130" t="n">
-        <v>40.9</v>
+        <v>-10.3</v>
       </c>
       <c r="Q130" t="n">
-        <v>1060</v>
+        <v>33.6</v>
       </c>
       <c r="R130" t="n">
-        <v>65.19</v>
+        <v>16.02</v>
       </c>
       <c r="S130" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="T130" t="n">
-        <v>11.44</v>
+        <v>2.3</v>
       </c>
       <c r="U130" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>108.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>博晟生醫</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -9746,62 +9746,70 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="n">
+        <v>15.3</v>
+      </c>
       <c r="F131" t="n">
-        <v>-682.5</v>
+        <v>-36.2</v>
       </c>
       <c r="G131" t="n">
-        <v>-16.8</v>
+        <v>-12.6</v>
       </c>
       <c r="H131" t="n">
-        <v>71.2</v>
+        <v>51</v>
       </c>
       <c r="I131" t="n">
-        <v>-39.6</v>
+        <v>22.4</v>
       </c>
       <c r="J131" t="n">
-        <v>-33.9</v>
+        <v>10.7</v>
       </c>
       <c r="K131" t="n">
-        <v>-0.55</v>
+        <v>2.53</v>
       </c>
       <c r="L131" t="n">
-        <v>-6.9</v>
+        <v>6.9</v>
       </c>
       <c r="M131" t="n">
-        <v>4.1</v>
+        <v>12.3</v>
       </c>
       <c r="N131" t="n">
-        <v>3437</v>
+        <v>1077</v>
       </c>
       <c r="O131" t="n">
-        <v>0.58</v>
+        <v>2.3</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
+        <v>5.1</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>564</v>
+      </c>
+      <c r="R131" t="n">
+        <v>222.92</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
       <c r="T131" t="n">
-        <v>2.98</v>
+        <v>16</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>-14.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -9811,113 +9819,249 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>-15.3</v>
+        <v>120.6</v>
       </c>
       <c r="F132" t="n">
-        <v>-30.5</v>
+        <v>-122.9</v>
       </c>
       <c r="G132" t="n">
-        <v>-28.2</v>
+        <v>-13.5</v>
       </c>
       <c r="H132" t="n">
-        <v>7.3</v>
+        <v>89</v>
       </c>
       <c r="I132" t="n">
-        <v>-30.2</v>
+        <v>33.3</v>
       </c>
       <c r="J132" t="n">
-        <v>-31.4</v>
+        <v>33.3</v>
       </c>
       <c r="K132" t="n">
-        <v>-1.79</v>
+        <v>16.26</v>
       </c>
       <c r="L132" t="n">
-        <v>-27.9</v>
+        <v>17.2</v>
       </c>
       <c r="M132" t="n">
-        <v>42.4</v>
+        <v>14.1</v>
       </c>
       <c r="N132" t="n">
-        <v>209</v>
+        <v>653</v>
       </c>
       <c r="O132" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.7</v>
+        <v>40.9</v>
       </c>
       <c r="Q132" t="n">
-        <v>27.8</v>
+        <v>1060</v>
       </c>
       <c r="R132" t="n">
-        <v>308.33</v>
+        <v>65.19</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="T132" t="n">
-        <v>21.75</v>
+        <v>11.44</v>
       </c>
       <c r="U132" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V132" t="n">
-        <v>13.3</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>晶瑞光</t>
+          <t>博晟生醫</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+      <c r="F133" t="n">
+        <v>-682.5</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-16.8</v>
+      </c>
       <c r="H133" t="n">
-        <v>-54.1</v>
+        <v>71.2</v>
       </c>
       <c r="I133" t="n">
-        <v>-141.4</v>
+        <v>-39.6</v>
       </c>
       <c r="J133" t="n">
-        <v>-156.2</v>
+        <v>-33.9</v>
       </c>
       <c r="K133" t="n">
-        <v>-9.279999999999999</v>
+        <v>-0.55</v>
       </c>
       <c r="L133" t="n">
-        <v>-66.09999999999999</v>
+        <v>-6.9</v>
       </c>
       <c r="M133" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="N133" t="n">
-        <v>455</v>
+        <v>3437</v>
       </c>
       <c r="O133" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="P133" t="n">
-        <v>-2.9</v>
+        <v>-0.3</v>
       </c>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr"/>
+      <c r="T133" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
       <c r="V133" t="n">
+        <v>-14.5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>光環</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-30.2</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-31.4</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="M134" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>209</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P134" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R134" t="n">
+        <v>308.33</v>
+      </c>
+      <c r="S134" t="n">
+        <v>3</v>
+      </c>
+      <c r="T134" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>晶瑞光</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
+        <v>-54.1</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-141.4</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-156.2</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-9.279999999999999</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-66.09999999999999</v>
+      </c>
+      <c r="M135" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N135" t="n">
+        <v>455</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P135" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="n">
         <v>58</v>
       </c>
     </row>
@@ -9932,7 +10076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X133"/>
+  <dimension ref="A1:X135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11428,229 +11572,229 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>全家</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>37.1</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>35.7</v>
+        <v>36.4</v>
       </c>
       <c r="F20" t="n">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>18.3</v>
+        <v>1.7</v>
       </c>
       <c r="H20" t="n">
-        <v>16.7</v>
+        <v>2.1</v>
       </c>
       <c r="I20" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>16.3</v>
+        <v>1.5</v>
       </c>
       <c r="K20" t="n">
-        <v>14.7</v>
+        <v>2.2</v>
       </c>
       <c r="L20" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>28.8</v>
+        <v>17.5</v>
       </c>
       <c r="N20" t="n">
-        <v>25.6</v>
+        <v>27.5</v>
       </c>
       <c r="O20" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>27.9</v>
+        <v>27.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>19.06</v>
+        <v>25.03</v>
       </c>
       <c r="R20" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="S20" t="n">
-        <v>8.57</v>
+        <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>4.21</v>
+        <v>7.42</v>
       </c>
       <c r="U20" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="V20" t="n">
-        <v>2.79</v>
+        <v>3.46</v>
       </c>
       <c r="W20" t="n">
-        <v>4.66</v>
+        <v>3.33</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>敦陽科</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>23.9</v>
+        <v>37.1</v>
       </c>
       <c r="E21" t="n">
-        <v>24.8</v>
+        <v>35.7</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="G21" t="n">
-        <v>11.8</v>
+        <v>18.3</v>
       </c>
       <c r="H21" t="n">
-        <v>11.6</v>
+        <v>16.7</v>
       </c>
       <c r="I21" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="J21" t="n">
-        <v>10.2</v>
+        <v>16.3</v>
       </c>
       <c r="K21" t="n">
-        <v>10.3</v>
+        <v>14.7</v>
       </c>
       <c r="L21" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="M21" t="n">
-        <v>29.9</v>
+        <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>24.9</v>
+        <v>25.6</v>
       </c>
       <c r="O21" t="n">
+        <v>71</v>
+      </c>
+      <c r="P21" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="R21" t="n">
+        <v>91</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="U21" t="n">
         <v>100</v>
       </c>
-      <c r="P21" t="n">
-        <v>18.41</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="R21" t="n">
-        <v>79</v>
-      </c>
-      <c r="S21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="U21" t="n">
-        <v>92</v>
-      </c>
       <c r="V21" t="n">
-        <v>5.05</v>
+        <v>2.79</v>
       </c>
       <c r="W21" t="n">
-        <v>5.79</v>
+        <v>4.66</v>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>全家</t>
+          <t>敦陽科</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I22" t="n">
         <v>36</v>
       </c>
-      <c r="E22" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>9</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
       <c r="J22" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2</v>
+        <v>10.3</v>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="M22" t="n">
-        <v>17.5</v>
+        <v>29.9</v>
       </c>
       <c r="N22" t="n">
-        <v>27.5</v>
+        <v>24.9</v>
       </c>
       <c r="O22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>27.01</v>
+        <v>18.41</v>
       </c>
       <c r="Q22" t="n">
-        <v>25.03</v>
+        <v>16.33</v>
       </c>
       <c r="R22" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="S22" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T22" t="n">
-        <v>7.42</v>
+        <v>3.78</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="V22" t="n">
-        <v>3.46</v>
+        <v>5.05</v>
       </c>
       <c r="W22" t="n">
-        <v>3.33</v>
+        <v>5.79</v>
       </c>
       <c r="X22" t="n">
-        <v>82</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -12036,153 +12180,153 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>長聖</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>28.7</v>
+        <v>72.5</v>
       </c>
       <c r="E28" t="n">
-        <v>27.3</v>
+        <v>60.5</v>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>3.3</v>
+        <v>44.8</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>29</v>
       </c>
       <c r="I28" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J28" t="n">
-        <v>2.9</v>
+        <v>45.9</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>45.2</v>
       </c>
       <c r="L28" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="M28" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="N28" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="O28" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="P28" t="n">
-        <v>19</v>
+        <v>27.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>36.16</v>
+        <v>118.22</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>4.87</v>
       </c>
       <c r="T28" t="n">
-        <v>7.45</v>
+        <v>9.82</v>
       </c>
       <c r="U28" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>5.06</v>
+        <v>2.81</v>
       </c>
       <c r="W28" t="n">
-        <v>2.66</v>
+        <v>2.37</v>
       </c>
       <c r="X28" t="n">
-        <v>98</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>長聖</t>
+          <t>大樹</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>72.5</v>
+        <v>28.7</v>
       </c>
       <c r="E29" t="n">
-        <v>60.5</v>
+        <v>27.3</v>
       </c>
       <c r="F29" t="n">
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>44.8</v>
+        <v>3.3</v>
       </c>
       <c r="H29" t="n">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="J29" t="n">
-        <v>45.9</v>
+        <v>2.9</v>
       </c>
       <c r="K29" t="n">
-        <v>45.2</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="M29" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="N29" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="O29" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>27.04</v>
+        <v>19</v>
       </c>
       <c r="Q29" t="n">
-        <v>118.22</v>
+        <v>36.16</v>
       </c>
       <c r="R29" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>4.87</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>9.82</v>
+        <v>7.45</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="V29" t="n">
-        <v>2.81</v>
+        <v>5.06</v>
       </c>
       <c r="W29" t="n">
-        <v>2.37</v>
+        <v>2.66</v>
       </c>
       <c r="X29" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
@@ -13328,153 +13472,153 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>緯軟</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>16.4</v>
+        <v>27</v>
       </c>
       <c r="E45" t="n">
-        <v>20.4</v>
+        <v>25.8</v>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="G45" t="n">
-        <v>6.3</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>6.8</v>
+        <v>18.4</v>
       </c>
       <c r="I45" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="J45" t="n">
-        <v>5.5</v>
+        <v>14.3</v>
       </c>
       <c r="K45" t="n">
-        <v>6.5</v>
+        <v>15.7</v>
       </c>
       <c r="L45" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M45" t="n">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="N45" t="n">
-        <v>17.7</v>
+        <v>18.8</v>
       </c>
       <c r="O45" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="P45" t="n">
-        <v>14.31</v>
+        <v>25.54</v>
       </c>
       <c r="Q45" t="n">
-        <v>14.46</v>
+        <v>13.67</v>
       </c>
       <c r="R45" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="S45" t="n">
-        <v>2.22</v>
+        <v>4.56</v>
       </c>
       <c r="T45" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U45" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="V45" t="n">
-        <v>3.88</v>
+        <v>3.23</v>
       </c>
       <c r="W45" t="n">
-        <v>4.34</v>
+        <v>6.16</v>
       </c>
       <c r="X45" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>緯軟</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F46" t="n">
+        <v>9</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>32</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L46" t="n">
         <v>27</v>
       </c>
-      <c r="E46" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="F46" t="n">
-        <v>73</v>
-      </c>
-      <c r="G46" t="n">
-        <v>20</v>
-      </c>
-      <c r="H46" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="I46" t="n">
-        <v>73</v>
-      </c>
-      <c r="J46" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K46" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="L46" t="n">
-        <v>41</v>
-      </c>
       <c r="M46" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="N46" t="n">
-        <v>18.8</v>
+        <v>17.7</v>
       </c>
       <c r="O46" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="P46" t="n">
-        <v>25.54</v>
+        <v>14.31</v>
       </c>
       <c r="Q46" t="n">
-        <v>13.67</v>
+        <v>14.46</v>
       </c>
       <c r="R46" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="S46" t="n">
-        <v>4.56</v>
+        <v>2.22</v>
       </c>
       <c r="T46" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U46" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="V46" t="n">
-        <v>3.23</v>
+        <v>3.88</v>
       </c>
       <c r="W46" t="n">
-        <v>6.16</v>
+        <v>4.34</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47">
@@ -13556,77 +13700,77 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>35.5</v>
+        <v>25.9</v>
       </c>
       <c r="E48" t="n">
-        <v>30.7</v>
+        <v>25.6</v>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="G48" t="n">
-        <v>16.5</v>
+        <v>18.1</v>
       </c>
       <c r="H48" t="n">
-        <v>11.4</v>
+        <v>16.7</v>
       </c>
       <c r="I48" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J48" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="K48" t="n">
-        <v>10.1</v>
+        <v>11.9</v>
       </c>
       <c r="L48" t="n">
         <v>100</v>
       </c>
       <c r="M48" t="n">
-        <v>22.3</v>
+        <v>18.6</v>
       </c>
       <c r="N48" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="O48" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="P48" t="n">
-        <v>79.31</v>
+        <v>21.99</v>
       </c>
       <c r="Q48" t="n">
-        <v>32.09</v>
+        <v>22.15</v>
       </c>
       <c r="R48" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="S48" t="n">
-        <v>18.64</v>
+        <v>4.15</v>
       </c>
       <c r="T48" t="n">
-        <v>5.46</v>
+        <v>3.12</v>
       </c>
       <c r="U48" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="V48" t="n">
-        <v>0.54</v>
+        <v>3.31</v>
       </c>
       <c r="W48" t="n">
-        <v>2.11</v>
+        <v>3.48</v>
       </c>
       <c r="X48" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49">
@@ -13708,77 +13852,77 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>25.9</v>
+        <v>35.5</v>
       </c>
       <c r="E50" t="n">
-        <v>25.6</v>
+        <v>30.7</v>
       </c>
       <c r="F50" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>18.1</v>
+        <v>16.5</v>
       </c>
       <c r="H50" t="n">
-        <v>16.7</v>
+        <v>11.4</v>
       </c>
       <c r="I50" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>14.8</v>
+        <v>13.4</v>
       </c>
       <c r="K50" t="n">
-        <v>11.9</v>
+        <v>10.1</v>
       </c>
       <c r="L50" t="n">
         <v>100</v>
       </c>
       <c r="M50" t="n">
-        <v>18.6</v>
+        <v>22.3</v>
       </c>
       <c r="N50" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="O50" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>21.99</v>
+        <v>79.31</v>
       </c>
       <c r="Q50" t="n">
-        <v>22.15</v>
+        <v>32.09</v>
       </c>
       <c r="R50" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="S50" t="n">
-        <v>4.15</v>
+        <v>18.64</v>
       </c>
       <c r="T50" t="n">
-        <v>3.12</v>
+        <v>5.46</v>
       </c>
       <c r="U50" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="V50" t="n">
-        <v>3.31</v>
+        <v>0.54</v>
       </c>
       <c r="W50" t="n">
-        <v>3.48</v>
+        <v>2.11</v>
       </c>
       <c r="X50" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -14320,77 +14464,77 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>18.3</v>
+        <v>30.1</v>
       </c>
       <c r="E58" t="n">
-        <v>19.5</v>
+        <v>33.6</v>
       </c>
       <c r="F58" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="G58" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="H58" t="n">
-        <v>7.9</v>
+        <v>15.8</v>
       </c>
       <c r="I58" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>29.5</v>
+        <v>8.9</v>
       </c>
       <c r="K58" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="L58" t="n">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="M58" t="n">
-        <v>21.8</v>
+        <v>9.9</v>
       </c>
       <c r="N58" t="n">
-        <v>15.4</v>
+        <v>16.2</v>
       </c>
       <c r="O58" t="n">
+        <v>14</v>
+      </c>
+      <c r="P58" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="R58" t="n">
+        <v>97</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U58" t="n">
         <v>81</v>
       </c>
-      <c r="P58" t="n">
-        <v>100.69</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>37.76</v>
-      </c>
-      <c r="R58" t="n">
-        <v>94</v>
-      </c>
-      <c r="S58" t="n">
-        <v>21.95</v>
-      </c>
-      <c r="T58" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="U58" t="n">
-        <v>96</v>
-      </c>
       <c r="V58" t="n">
-        <v>0.4</v>
+        <v>1.48</v>
       </c>
       <c r="W58" t="n">
-        <v>3.12</v>
+        <v>3.46</v>
       </c>
       <c r="X58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -14472,77 +14616,77 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>30.1</v>
+        <v>18.3</v>
       </c>
       <c r="E60" t="n">
-        <v>33.6</v>
+        <v>19.5</v>
       </c>
       <c r="F60" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="G60" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="H60" t="n">
-        <v>15.8</v>
+        <v>7.9</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J60" t="n">
-        <v>8.9</v>
+        <v>29.5</v>
       </c>
       <c r="K60" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="L60" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="M60" t="n">
-        <v>9.9</v>
+        <v>21.8</v>
       </c>
       <c r="N60" t="n">
-        <v>16.2</v>
+        <v>15.4</v>
       </c>
       <c r="O60" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="P60" t="n">
-        <v>40.16</v>
+        <v>100.69</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.01</v>
+        <v>37.76</v>
       </c>
       <c r="R60" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="S60" t="n">
-        <v>4.01</v>
+        <v>21.95</v>
       </c>
       <c r="T60" t="n">
-        <v>3.06</v>
+        <v>4.44</v>
       </c>
       <c r="U60" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="V60" t="n">
-        <v>1.48</v>
+        <v>0.4</v>
       </c>
       <c r="W60" t="n">
-        <v>3.46</v>
+        <v>3.12</v>
       </c>
       <c r="X60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -15308,153 +15452,153 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>台特化</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>51.8</v>
+        <v>40.2</v>
       </c>
       <c r="E71" t="n">
-        <v>49.7</v>
+        <v>40</v>
       </c>
       <c r="F71" t="n">
         <v>55</v>
       </c>
       <c r="G71" t="n">
-        <v>41.2</v>
+        <v>21.6</v>
       </c>
       <c r="H71" t="n">
-        <v>38</v>
+        <v>22.2</v>
       </c>
       <c r="I71" t="n">
         <v>55</v>
       </c>
       <c r="J71" t="n">
-        <v>34.1</v>
+        <v>27.2</v>
       </c>
       <c r="K71" t="n">
-        <v>38</v>
+        <v>22.8</v>
       </c>
       <c r="L71" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="M71" t="n">
-        <v>20.7</v>
+        <v>14.7</v>
       </c>
       <c r="N71" t="n">
-        <v>17.2</v>
+        <v>14.1</v>
       </c>
       <c r="O71" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="P71" t="n">
-        <v>58.47</v>
+        <v>38.15</v>
       </c>
       <c r="Q71" t="n">
-        <v>61.81</v>
+        <v>25.2</v>
       </c>
       <c r="R71" t="n">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="S71" t="n">
-        <v>12.02</v>
+        <v>5.71</v>
       </c>
       <c r="T71" t="n">
-        <v>11.9</v>
+        <v>3.66</v>
       </c>
       <c r="U71" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="V71" t="n">
-        <v>1.06</v>
+        <v>1.57</v>
       </c>
       <c r="W71" t="n">
-        <v>0.77</v>
+        <v>2.38</v>
       </c>
       <c r="X71" t="n">
-        <v>92</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>台特化</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>40.2</v>
+        <v>51.8</v>
       </c>
       <c r="E72" t="n">
-        <v>40</v>
+        <v>49.7</v>
       </c>
       <c r="F72" t="n">
         <v>55</v>
       </c>
       <c r="G72" t="n">
-        <v>21.6</v>
+        <v>41.2</v>
       </c>
       <c r="H72" t="n">
-        <v>22.2</v>
+        <v>38</v>
       </c>
       <c r="I72" t="n">
         <v>55</v>
       </c>
       <c r="J72" t="n">
-        <v>27.2</v>
+        <v>34.1</v>
       </c>
       <c r="K72" t="n">
-        <v>22.8</v>
+        <v>38</v>
       </c>
       <c r="L72" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="M72" t="n">
-        <v>14.7</v>
+        <v>20.7</v>
       </c>
       <c r="N72" t="n">
-        <v>14.1</v>
+        <v>17.2</v>
       </c>
       <c r="O72" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="P72" t="n">
-        <v>38.15</v>
+        <v>58.47</v>
       </c>
       <c r="Q72" t="n">
-        <v>25.2</v>
+        <v>61.81</v>
       </c>
       <c r="R72" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="S72" t="n">
-        <v>5.71</v>
+        <v>12.02</v>
       </c>
       <c r="T72" t="n">
-        <v>3.66</v>
+        <v>11.9</v>
       </c>
       <c r="U72" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="V72" t="n">
-        <v>1.57</v>
+        <v>1.06</v>
       </c>
       <c r="W72" t="n">
-        <v>2.38</v>
+        <v>0.77</v>
       </c>
       <c r="X72" t="n">
-        <v>4</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73">
@@ -16524,153 +16668,153 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>世禾</t>
+          <t>遠雄港</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>35.6</v>
+        <v>50.4</v>
       </c>
       <c r="E87" t="n">
-        <v>36.7</v>
+        <v>53.4</v>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="G87" t="n">
-        <v>17.5</v>
+        <v>39.3</v>
       </c>
       <c r="H87" t="n">
-        <v>17.6</v>
+        <v>37.6</v>
       </c>
       <c r="I87" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="J87" t="n">
-        <v>16.3</v>
+        <v>27</v>
       </c>
       <c r="K87" t="n">
-        <v>15.3</v>
+        <v>29.4</v>
       </c>
       <c r="L87" t="n">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="M87" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="N87" t="n">
         <v>10.5</v>
       </c>
       <c r="O87" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="P87" t="n">
-        <v>24.45</v>
+        <v>16.11</v>
       </c>
       <c r="Q87" t="n">
-        <v>15.15</v>
+        <v>18.42</v>
       </c>
       <c r="R87" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="S87" t="n">
-        <v>2.57</v>
+        <v>1.69</v>
       </c>
       <c r="T87" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="U87" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="V87" t="n">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="W87" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="X87" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>遠雄港</t>
+          <t>世禾</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>50.4</v>
+        <v>35.6</v>
       </c>
       <c r="E88" t="n">
-        <v>53.4</v>
+        <v>36.7</v>
       </c>
       <c r="F88" t="n">
+        <v>5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I88" t="n">
         <v>45</v>
       </c>
-      <c r="G88" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="H88" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="I88" t="n">
-        <v>64</v>
-      </c>
       <c r="J88" t="n">
-        <v>27</v>
+        <v>16.3</v>
       </c>
       <c r="K88" t="n">
-        <v>29.4</v>
+        <v>15.3</v>
       </c>
       <c r="L88" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="M88" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="N88" t="n">
         <v>10.5</v>
       </c>
       <c r="O88" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="P88" t="n">
-        <v>16.11</v>
+        <v>24.45</v>
       </c>
       <c r="Q88" t="n">
-        <v>18.42</v>
+        <v>15.15</v>
       </c>
       <c r="R88" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="S88" t="n">
-        <v>1.69</v>
+        <v>2.57</v>
       </c>
       <c r="T88" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="U88" t="n">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="V88" t="n">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="W88" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="X88" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89">
@@ -17856,530 +18000,530 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>17</v>
+        <v>29.3</v>
       </c>
       <c r="E105" t="n">
-        <v>21.9</v>
+        <v>32</v>
       </c>
       <c r="F105" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G105" t="n">
-        <v>-2</v>
+        <v>7.5</v>
       </c>
       <c r="H105" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J105" t="n">
-        <v>-6</v>
+        <v>6.1</v>
       </c>
       <c r="K105" t="n">
-        <v>-0.4</v>
+        <v>9.5</v>
       </c>
       <c r="L105" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="M105" t="n">
-        <v>-7.2</v>
+        <v>4</v>
       </c>
       <c r="N105" t="n">
-        <v>-4.6</v>
+        <v>7.8</v>
       </c>
       <c r="O105" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P105" t="n">
-        <v>65.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="Q105" t="n">
-        <v>92.16</v>
+        <v>36.22</v>
       </c>
       <c r="R105" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="S105" t="n">
-        <v>8.01</v>
+        <v>3.16</v>
       </c>
       <c r="T105" t="n">
-        <v>4.98</v>
+        <v>2.9</v>
       </c>
       <c r="U105" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="V105" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W105" t="n">
-        <v>0.38</v>
+        <v>1.41</v>
       </c>
       <c r="X105" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>6.9</v>
+        <v>17</v>
       </c>
       <c r="E106" t="n">
-        <v>4.9</v>
+        <v>21.9</v>
       </c>
       <c r="F106" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="G106" t="n">
-        <v>5.1</v>
+        <v>-2</v>
       </c>
       <c r="H106" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="I106" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
-        <v>4.3</v>
+        <v>-6</v>
       </c>
       <c r="K106" t="n">
-        <v>3.5</v>
+        <v>-0.4</v>
       </c>
       <c r="L106" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="M106" t="n">
-        <v>7</v>
+        <v>-7.2</v>
       </c>
       <c r="N106" t="n">
-        <v>6.1</v>
+        <v>-4.6</v>
       </c>
       <c r="O106" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="P106" t="n">
-        <v>19.35</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="Q106" t="n">
-        <v>48.34</v>
+        <v>92.16</v>
       </c>
       <c r="R106" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="S106" t="n">
-        <v>1.36</v>
+        <v>8.01</v>
       </c>
       <c r="T106" t="n">
-        <v>2.23</v>
+        <v>4.98</v>
       </c>
       <c r="U106" t="n">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="V106" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>2.65</v>
+        <v>0.38</v>
       </c>
       <c r="X106" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>健喬</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>42.8</v>
+        <v>23.7</v>
       </c>
       <c r="E107" t="n">
-        <v>41.4</v>
+        <v>24.1</v>
       </c>
       <c r="F107" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="G107" t="n">
-        <v>11.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H107" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I107" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="J107" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="K107" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="L107" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="M107" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="N107" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="O107" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="P107" t="n">
-        <v>19.22</v>
+        <v>30.21</v>
       </c>
       <c r="Q107" t="n">
-        <v>19.73</v>
+        <v>20.24</v>
       </c>
       <c r="R107" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="S107" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="T107" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="U107" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="V107" t="n">
-        <v>5.33</v>
+        <v>2.86</v>
       </c>
       <c r="W107" t="n">
-        <v>4.69</v>
+        <v>3.7</v>
       </c>
       <c r="X107" t="n">
-        <v>75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>奈米醫材</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>58.6</v>
+        <v>6.9</v>
       </c>
       <c r="E108" t="n">
-        <v>75.8</v>
+        <v>4.9</v>
       </c>
       <c r="F108" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="G108" t="n">
-        <v>10.2</v>
+        <v>5.1</v>
       </c>
       <c r="H108" t="n">
-        <v>18.7</v>
+        <v>3.2</v>
       </c>
       <c r="I108" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.9</v>
+        <v>4.3</v>
       </c>
       <c r="K108" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="L108" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="M108" t="n">
-        <v>-0.5</v>
+        <v>7</v>
       </c>
       <c r="N108" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="O108" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="P108" t="n">
-        <v>85.76000000000001</v>
+        <v>19.35</v>
       </c>
       <c r="Q108" t="n">
-        <v>50.34</v>
+        <v>48.34</v>
       </c>
       <c r="R108" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="S108" t="n">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="T108" t="n">
-        <v>3.53</v>
+        <v>2.23</v>
       </c>
       <c r="U108" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="V108" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="W108" t="n">
-        <v>0.8</v>
+        <v>2.65</v>
       </c>
       <c r="X108" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>健喬</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>48.8</v>
+        <v>42.8</v>
       </c>
       <c r="E109" t="n">
-        <v>32.3</v>
+        <v>41.4</v>
       </c>
       <c r="F109" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G109" t="n">
-        <v>31.7</v>
+        <v>11.9</v>
       </c>
       <c r="H109" t="n">
-        <v>8.4</v>
+        <v>10.1</v>
       </c>
       <c r="I109" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="J109" t="n">
-        <v>26.7</v>
+        <v>9.4</v>
       </c>
       <c r="K109" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L109" t="n">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="M109" t="n">
-        <v>16.6</v>
+        <v>5.9</v>
       </c>
       <c r="N109" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O109" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="P109" t="n">
-        <v>310.86</v>
+        <v>19.22</v>
       </c>
       <c r="Q109" t="n">
-        <v>186.74</v>
+        <v>19.73</v>
       </c>
       <c r="R109" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="S109" t="n">
-        <v>51.83</v>
+        <v>1.76</v>
       </c>
       <c r="T109" t="n">
-        <v>7.67</v>
+        <v>1.93</v>
       </c>
       <c r="U109" t="n">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="V109" t="n">
-        <v>0.17</v>
+        <v>5.33</v>
       </c>
       <c r="W109" t="n">
-        <v>1.57</v>
+        <v>4.69</v>
       </c>
       <c r="X109" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>奈米醫材</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>18</v>
+        <v>58.6</v>
       </c>
       <c r="E110" t="n">
-        <v>19.1</v>
+        <v>75.8</v>
       </c>
       <c r="F110" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>10.2</v>
       </c>
       <c r="H110" t="n">
-        <v>2.8</v>
+        <v>18.7</v>
       </c>
       <c r="I110" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="J110" t="n">
-        <v>0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="K110" t="n">
-        <v>5.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L110" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="M110" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="N110" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="O110" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="P110" t="n">
-        <v>2019.23</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="Q110" t="n">
-        <v>157.97</v>
+        <v>50.34</v>
       </c>
       <c r="R110" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="S110" t="n">
-        <v>9.34</v>
+        <v>1.84</v>
       </c>
       <c r="T110" t="n">
-        <v>2.47</v>
+        <v>3.53</v>
       </c>
       <c r="U110" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="V110" t="n">
-        <v>0.04</v>
+        <v>1.78</v>
       </c>
       <c r="W110" t="n">
-        <v>2.17</v>
+        <v>0.8</v>
       </c>
       <c r="X110" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>矽統</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>28.5</v>
+        <v>48.8</v>
       </c>
       <c r="E111" t="n">
-        <v>26.9</v>
+        <v>32.3</v>
       </c>
       <c r="F111" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="G111" t="n">
-        <v>0.5</v>
+        <v>31.7</v>
       </c>
       <c r="H111" t="n">
-        <v>-163.4</v>
+        <v>8.4</v>
       </c>
       <c r="I111" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="J111" t="n">
-        <v>25.3</v>
+        <v>26.7</v>
       </c>
       <c r="K111" t="n">
-        <v>110.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L111" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="M111" t="n">
-        <v>4.2</v>
+        <v>16.6</v>
       </c>
       <c r="N111" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="O111" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P111" t="n">
-        <v>40.65</v>
+        <v>310.86</v>
       </c>
       <c r="Q111" t="n">
-        <v>54.61</v>
+        <v>186.74</v>
       </c>
       <c r="R111" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="S111" t="n">
-        <v>1.75</v>
+        <v>51.83</v>
       </c>
       <c r="T111" t="n">
-        <v>1.26</v>
+        <v>7.67</v>
       </c>
       <c r="U111" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="V111" t="n">
-        <v>0.87</v>
+        <v>0.17</v>
       </c>
       <c r="W111" t="n">
-        <v>5.46</v>
+        <v>1.57</v>
       </c>
       <c r="X111" t="n">
         <v>21</v>
@@ -18388,400 +18532,392 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>15.7</v>
+        <v>18</v>
       </c>
       <c r="E112" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="F112" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G112" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="H112" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="J112" t="n">
-        <v>-4.9</v>
+        <v>0.5</v>
       </c>
       <c r="K112" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="L112" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="M112" t="n">
-        <v>-1.6</v>
+        <v>0.5</v>
       </c>
       <c r="N112" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O112" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P112" t="n">
-        <v>5637.5</v>
+        <v>2019.23</v>
       </c>
       <c r="Q112" t="n">
-        <v>1022.54</v>
+        <v>157.97</v>
       </c>
       <c r="R112" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="S112" t="n">
-        <v>14.11</v>
+        <v>9.34</v>
       </c>
       <c r="T112" t="n">
-        <v>5.67</v>
+        <v>2.47</v>
       </c>
       <c r="U112" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="W112" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="X112" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>精確</t>
+          <t>矽統</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>28.5</v>
       </c>
       <c r="E113" t="n">
-        <v>13</v>
+        <v>26.9</v>
       </c>
       <c r="F113" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G113" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>-163.4</v>
       </c>
       <c r="I113" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="J113" t="n">
-        <v>2.1</v>
+        <v>25.3</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>110.7</v>
       </c>
       <c r="L113" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="M113" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N113" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O113" t="n">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="P113" t="n">
-        <v>69.34</v>
+        <v>40.65</v>
       </c>
       <c r="Q113" t="n">
-        <v>74.56999999999999</v>
+        <v>54.61</v>
       </c>
       <c r="R113" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="S113" t="n">
-        <v>3.17</v>
+        <v>1.75</v>
       </c>
       <c r="T113" t="n">
-        <v>3.24</v>
+        <v>1.26</v>
       </c>
       <c r="U113" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="V113" t="n">
-        <v>1.18</v>
+        <v>0.87</v>
       </c>
       <c r="W113" t="n">
-        <v>0.21</v>
+        <v>5.46</v>
       </c>
       <c r="X113" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>84</v>
+        <v>15.7</v>
       </c>
       <c r="E114" t="n">
-        <v>85.7</v>
+        <v>17.4</v>
       </c>
       <c r="F114" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G114" t="n">
-        <v>15.3</v>
+        <v>-8</v>
       </c>
       <c r="H114" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="I114" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J114" t="n">
-        <v>11.7</v>
+        <v>-4.9</v>
       </c>
       <c r="K114" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="L114" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="M114" t="n">
-        <v>6.1</v>
+        <v>-1.6</v>
       </c>
       <c r="N114" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="O114" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="P114" t="n">
-        <v>18.75</v>
+        <v>5637.5</v>
       </c>
       <c r="Q114" t="n">
-        <v>35.61</v>
+        <v>1022.54</v>
       </c>
       <c r="R114" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="S114" t="n">
-        <v>1.14</v>
+        <v>14.11</v>
       </c>
       <c r="T114" t="n">
-        <v>1.9</v>
+        <v>5.67</v>
       </c>
       <c r="U114" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="V114" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>2.99</v>
+        <v>2.36</v>
       </c>
       <c r="X114" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
+          <t>精確</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F115" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O115" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="P115" t="n">
-        <v>16.78</v>
+        <v>69.34</v>
       </c>
       <c r="Q115" t="n">
-        <v>14.04</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="R115" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="S115" t="n">
-        <v>1.41</v>
+        <v>3.17</v>
       </c>
       <c r="T115" t="n">
-        <v>1.05</v>
+        <v>3.24</v>
       </c>
       <c r="U115" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="V115" t="n">
-        <v>3.43</v>
+        <v>1.18</v>
       </c>
       <c r="W115" t="n">
-        <v>5.66</v>
+        <v>0.21</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>🏦</t>
-        </is>
-      </c>
+          <t>訊連</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="F116" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="I116" t="n">
         <v>100</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L116" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O116" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="P116" t="n">
-        <v>20.2</v>
+        <v>18.75</v>
       </c>
       <c r="Q116" t="n">
-        <v>12.83</v>
+        <v>35.61</v>
       </c>
       <c r="R116" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="S116" t="n">
-        <v>2.17</v>
+        <v>1.14</v>
       </c>
       <c r="T116" t="n">
-        <v>1.26</v>
+        <v>1.9</v>
       </c>
       <c r="U116" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="V116" t="n">
-        <v>3.27</v>
+        <v>5.22</v>
       </c>
       <c r="W116" t="n">
-        <v>4.93</v>
+        <v>2.99</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -18826,42 +18962,42 @@
         <v>100</v>
       </c>
       <c r="P117" t="n">
-        <v>17.44</v>
+        <v>19.79</v>
       </c>
       <c r="Q117" t="n">
-        <v>10.92</v>
+        <v>16.99</v>
       </c>
       <c r="R117" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S117" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="T117" t="n">
-        <v>0.99</v>
+        <v>1.55</v>
       </c>
       <c r="U117" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V117" t="n">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="W117" t="n">
-        <v>4.53</v>
+        <v>4.35</v>
       </c>
       <c r="X117" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -18906,42 +19042,42 @@
         <v>100</v>
       </c>
       <c r="P118" t="n">
-        <v>16.55</v>
+        <v>20.2</v>
       </c>
       <c r="Q118" t="n">
-        <v>16.68</v>
+        <v>12.83</v>
       </c>
       <c r="R118" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="S118" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="T118" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="U118" t="n">
         <v>100</v>
       </c>
       <c r="V118" t="n">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
       <c r="W118" t="n">
-        <v>4.12</v>
+        <v>4.93</v>
       </c>
       <c r="X118" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -18986,42 +19122,42 @@
         <v>100</v>
       </c>
       <c r="P119" t="n">
-        <v>19.79</v>
+        <v>25.11</v>
       </c>
       <c r="Q119" t="n">
-        <v>16.99</v>
+        <v>12.49</v>
       </c>
       <c r="R119" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="S119" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="T119" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="U119" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="V119" t="n">
-        <v>3.86</v>
+        <v>3.24</v>
       </c>
       <c r="W119" t="n">
-        <v>4.35</v>
+        <v>5.23</v>
       </c>
       <c r="X119" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -19029,55 +19165,79 @@
           <t>🏦</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>100</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>100</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>100</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>100</v>
+      </c>
       <c r="P120" t="n">
-        <v>12.84</v>
+        <v>16.55</v>
       </c>
       <c r="Q120" t="n">
-        <v>12.67</v>
+        <v>16.68</v>
       </c>
       <c r="R120" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="S120" t="n">
-        <v>1.26</v>
+        <v>2.11</v>
       </c>
       <c r="T120" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="U120" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="V120" t="n">
-        <v>5.39</v>
+        <v>3.08</v>
       </c>
       <c r="W120" t="n">
-        <v>5.67</v>
+        <v>4.12</v>
       </c>
       <c r="X120" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -19122,42 +19282,42 @@
         <v>100</v>
       </c>
       <c r="P121" t="n">
-        <v>16.01</v>
+        <v>16.78</v>
       </c>
       <c r="Q121" t="n">
-        <v>15.79</v>
+        <v>14.04</v>
       </c>
       <c r="R121" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S121" t="n">
-        <v>2.31</v>
+        <v>1.41</v>
       </c>
       <c r="T121" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="U121" t="n">
         <v>100</v>
       </c>
       <c r="V121" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="W121" t="n">
-        <v>4.53</v>
+        <v>5.66</v>
       </c>
       <c r="X121" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -19165,79 +19325,55 @@
           <t>🏦</t>
         </is>
       </c>
-      <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="n">
-        <v>100</v>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>100</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>100</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>100</v>
-      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
       <c r="P122" t="n">
-        <v>23.89</v>
+        <v>12.84</v>
       </c>
       <c r="Q122" t="n">
-        <v>21.57</v>
+        <v>12.67</v>
       </c>
       <c r="R122" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="S122" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T122" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="U122" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="V122" t="n">
-        <v>3.92</v>
+        <v>5.39</v>
       </c>
       <c r="W122" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="X122" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -19282,42 +19418,42 @@
         <v>100</v>
       </c>
       <c r="P123" t="n">
-        <v>17.28</v>
+        <v>17.44</v>
       </c>
       <c r="Q123" t="n">
-        <v>11.6</v>
+        <v>10.92</v>
       </c>
       <c r="R123" t="n">
         <v>95</v>
       </c>
       <c r="S123" t="n">
-        <v>2.52</v>
+        <v>1.54</v>
       </c>
       <c r="T123" t="n">
-        <v>1.39</v>
+        <v>0.99</v>
       </c>
       <c r="U123" t="n">
         <v>100</v>
       </c>
       <c r="V123" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="W123" t="n">
-        <v>4.76</v>
+        <v>4.53</v>
       </c>
       <c r="X123" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -19362,42 +19498,42 @@
         <v>100</v>
       </c>
       <c r="P124" t="n">
-        <v>16.89</v>
+        <v>17.28</v>
       </c>
       <c r="Q124" t="n">
-        <v>18.88</v>
+        <v>11.6</v>
       </c>
       <c r="R124" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="S124" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="T124" t="n">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="U124" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="V124" t="n">
-        <v>3.91</v>
+        <v>3.55</v>
       </c>
       <c r="W124" t="n">
-        <v>4.5</v>
+        <v>4.76</v>
       </c>
       <c r="X124" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -19442,616 +19578,776 @@
         <v>100</v>
       </c>
       <c r="P125" t="n">
-        <v>25.11</v>
+        <v>16.89</v>
       </c>
       <c r="Q125" t="n">
-        <v>12.49</v>
+        <v>18.88</v>
       </c>
       <c r="R125" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="S125" t="n">
-        <v>2.53</v>
+        <v>2.03</v>
       </c>
       <c r="T125" t="n">
-        <v>1.22</v>
+        <v>1.86</v>
       </c>
       <c r="U125" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="V125" t="n">
-        <v>3.24</v>
+        <v>3.91</v>
       </c>
       <c r="W125" t="n">
-        <v>5.23</v>
+        <v>4.5</v>
       </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>今國光</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>國票金</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D126" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
         <v>100</v>
       </c>
       <c r="G126" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-3.7</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
         <v>100</v>
       </c>
       <c r="J126" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="L126" t="n">
         <v>100</v>
       </c>
       <c r="M126" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>100</v>
       </c>
       <c r="P126" t="n">
-        <v>56.18</v>
+        <v>23.89</v>
       </c>
       <c r="Q126" t="n">
-        <v>159.72</v>
+        <v>21.57</v>
       </c>
       <c r="R126" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="S126" t="n">
-        <v>4.97</v>
+        <v>1.17</v>
       </c>
       <c r="T126" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="U126" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="V126" t="n">
-        <v>0.51</v>
+        <v>3.92</v>
       </c>
       <c r="W126" t="n">
-        <v>1.06</v>
+        <v>5.65</v>
       </c>
       <c r="X126" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>揚明光</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D127" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>15.1</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G127" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>-4.6</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>-3.7</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="M127" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>-3.1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="P127" t="n">
-        <v>132.75</v>
+        <v>16.01</v>
       </c>
       <c r="Q127" t="n">
-        <v>122.39</v>
+        <v>15.79</v>
       </c>
       <c r="R127" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="S127" t="n">
-        <v>3.69</v>
+        <v>2.31</v>
       </c>
       <c r="T127" t="n">
-        <v>2.6</v>
+        <v>1.11</v>
       </c>
       <c r="U127" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="V127" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="W127" t="n">
-        <v>0.06</v>
+        <v>4.53</v>
       </c>
       <c r="X127" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>新鉅科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>8.9</v>
+        <v>24.3</v>
       </c>
       <c r="E128" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="F128" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G128" t="n">
-        <v>-18.8</v>
+        <v>9.5</v>
       </c>
       <c r="H128" t="n">
-        <v>-30.8</v>
+        <v>-3.7</v>
       </c>
       <c r="I128" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="J128" t="n">
-        <v>18</v>
+        <v>7.5</v>
       </c>
       <c r="K128" t="n">
-        <v>-19.4</v>
+        <v>-1.9</v>
       </c>
       <c r="L128" t="n">
         <v>100</v>
       </c>
       <c r="M128" t="n">
-        <v>14.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N128" t="n">
-        <v>-10.6</v>
+        <v>-1.7</v>
       </c>
       <c r="O128" t="n">
         <v>100</v>
       </c>
       <c r="P128" t="n">
-        <v>16.02</v>
+        <v>56.18</v>
       </c>
       <c r="Q128" t="n">
-        <v>23.86</v>
+        <v>159.72</v>
       </c>
       <c r="R128" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S128" t="n">
-        <v>2.3</v>
+        <v>4.97</v>
       </c>
       <c r="T128" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="U128" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="V128" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="W128" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X128" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>51.5</v>
+        <v>18</v>
       </c>
       <c r="E129" t="n">
-        <v>31.4</v>
+        <v>15.1</v>
       </c>
       <c r="F129" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G129" t="n">
-        <v>22.6</v>
+        <v>-1.9</v>
       </c>
       <c r="H129" t="n">
-        <v>0.6</v>
+        <v>-4.6</v>
       </c>
       <c r="I129" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="J129" t="n">
-        <v>12</v>
+        <v>-0.3</v>
       </c>
       <c r="K129" t="n">
-        <v>-33.3</v>
+        <v>-3.7</v>
       </c>
       <c r="L129" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="M129" t="n">
-        <v>6.9</v>
+        <v>-0.3</v>
       </c>
       <c r="N129" t="n">
-        <v>-12.4</v>
+        <v>-3.1</v>
       </c>
       <c r="O129" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="P129" t="n">
-        <v>222.92</v>
+        <v>132.75</v>
       </c>
       <c r="Q129" t="n">
-        <v>1255.25</v>
+        <v>122.39</v>
       </c>
       <c r="R129" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="S129" t="n">
-        <v>16</v>
+        <v>3.69</v>
       </c>
       <c r="T129" t="n">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="U129" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="X129" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>新鉅科</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>88.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="E130" t="n">
-        <v>70.2</v>
+        <v>5.1</v>
       </c>
       <c r="F130" t="n">
+        <v>82</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="I130" t="n">
         <v>86</v>
       </c>
-      <c r="G130" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="H130" t="n">
-        <v>-118.6</v>
-      </c>
-      <c r="I130" t="n">
+      <c r="J130" t="n">
+        <v>18</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="L130" t="n">
         <v>100</v>
       </c>
-      <c r="J130" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="K130" t="n">
-        <v>-115.3</v>
-      </c>
-      <c r="L130" t="n">
-        <v>91</v>
-      </c>
       <c r="M130" t="n">
-        <v>17.2</v>
+        <v>14.4</v>
       </c>
       <c r="N130" t="n">
-        <v>-25.6</v>
+        <v>-10.6</v>
       </c>
       <c r="O130" t="n">
         <v>100</v>
       </c>
       <c r="P130" t="n">
-        <v>65.19</v>
+        <v>16.02</v>
       </c>
       <c r="Q130" t="n">
-        <v>110.65</v>
+        <v>23.86</v>
       </c>
       <c r="R130" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="S130" t="n">
-        <v>11.44</v>
+        <v>2.3</v>
       </c>
       <c r="T130" t="n">
-        <v>11.69</v>
+        <v>1.94</v>
       </c>
       <c r="U130" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="V130" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>博晟生醫</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>74.3</v>
+        <v>51.5</v>
       </c>
       <c r="E131" t="n">
-        <v>78.8</v>
+        <v>31.4</v>
       </c>
       <c r="F131" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="G131" t="n">
-        <v>-40.7</v>
+        <v>22.6</v>
       </c>
       <c r="H131" t="n">
-        <v>-342.9</v>
+        <v>0.6</v>
       </c>
       <c r="I131" t="n">
         <v>100</v>
       </c>
       <c r="J131" t="n">
-        <v>-34.8</v>
+        <v>12</v>
       </c>
       <c r="K131" t="n">
-        <v>-299.4</v>
+        <v>-33.3</v>
       </c>
       <c r="L131" t="n">
         <v>100</v>
       </c>
       <c r="M131" t="n">
-        <v>-6.9</v>
+        <v>6.9</v>
       </c>
       <c r="N131" t="n">
-        <v>-16.2</v>
+        <v>-12.4</v>
       </c>
       <c r="O131" t="n">
         <v>100</v>
       </c>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>222.92</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>1255.25</v>
+      </c>
+      <c r="R131" t="n">
+        <v>5</v>
+      </c>
       <c r="S131" t="n">
-        <v>2.98</v>
+        <v>16</v>
       </c>
       <c r="T131" t="n">
-        <v>4.25</v>
+        <v>2.93</v>
       </c>
       <c r="U131" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="X131" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>7.6</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E132" t="n">
-        <v>14.6</v>
+        <v>70.2</v>
       </c>
       <c r="F132" t="n">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="G132" t="n">
-        <v>-30.3</v>
+        <v>33.8</v>
       </c>
       <c r="H132" t="n">
-        <v>-22.6</v>
+        <v>-118.6</v>
       </c>
       <c r="I132" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="J132" t="n">
-        <v>-31.3</v>
+        <v>33.9</v>
       </c>
       <c r="K132" t="n">
-        <v>-26.1</v>
+        <v>-115.3</v>
       </c>
       <c r="L132" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="M132" t="n">
-        <v>-27.9</v>
+        <v>17.2</v>
       </c>
       <c r="N132" t="n">
-        <v>-23</v>
+        <v>-25.6</v>
       </c>
       <c r="O132" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="P132" t="n">
-        <v>308.33</v>
+        <v>65.19</v>
       </c>
       <c r="Q132" t="n">
-        <v>407.98</v>
+        <v>110.65</v>
       </c>
       <c r="R132" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="S132" t="n">
-        <v>21.75</v>
+        <v>11.44</v>
       </c>
       <c r="T132" t="n">
-        <v>4.12</v>
+        <v>11.69</v>
       </c>
       <c r="U132" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W132" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="X132" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>晶瑞光</t>
+          <t>博晟生醫</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>-52.9</v>
+        <v>74.3</v>
       </c>
       <c r="E133" t="n">
-        <v>-146.5</v>
+        <v>78.8</v>
       </c>
       <c r="F133" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="G133" t="n">
-        <v>-137</v>
+        <v>-40.7</v>
       </c>
       <c r="H133" t="n">
-        <v>-285.2</v>
+        <v>-342.9</v>
       </c>
       <c r="I133" t="n">
         <v>100</v>
       </c>
       <c r="J133" t="n">
-        <v>-152.1</v>
+        <v>-34.8</v>
       </c>
       <c r="K133" t="n">
-        <v>-280</v>
+        <v>-299.4</v>
       </c>
       <c r="L133" t="n">
         <v>100</v>
       </c>
       <c r="M133" t="n">
-        <v>-66.09999999999999</v>
+        <v>-6.9</v>
       </c>
       <c r="N133" t="n">
-        <v>-48.1</v>
+        <v>-16.2</v>
       </c>
       <c r="O133" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr"/>
+      <c r="S133" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T133" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U133" t="n">
+        <v>25</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>光環</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E134" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F134" t="n">
+        <v>27</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="I134" t="n">
+        <v>32</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="L134" t="n">
+        <v>32</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-23</v>
+      </c>
+      <c r="O134" t="n">
+        <v>33</v>
+      </c>
+      <c r="P134" t="n">
+        <v>308.33</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>407.98</v>
+      </c>
+      <c r="R134" t="n">
+        <v>3</v>
+      </c>
+      <c r="S134" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="T134" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="U134" t="n">
+        <v>100</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>晶瑞光</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="n">
+        <v>-52.9</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-146.5</v>
+      </c>
+      <c r="F135" t="n">
+        <v>100</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-137</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-285.2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>100</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-152.1</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-280</v>
+      </c>
+      <c r="L135" t="n">
+        <v>100</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-66.09999999999999</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-48.1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>11</v>
+      </c>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20064,7 +20360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22950,6 +23246,50 @@
       </c>
       <c r="F132" t="n">
         <v>6261.7</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>1504 東元</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>525.6</v>
+      </c>
+      <c r="C133" t="n">
+        <v>583.2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>593.9</v>
+      </c>
+      <c r="E133" t="n">
+        <v>552.4</v>
+      </c>
+      <c r="F133" t="n">
+        <v>590.9</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>2049 上銀</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>272.7</v>
+      </c>
+      <c r="C134" t="n">
+        <v>293.2</v>
+      </c>
+      <c r="D134" t="n">
+        <v>246.3</v>
+      </c>
+      <c r="E134" t="n">
+        <v>244</v>
+      </c>
+      <c r="F134" t="n">
+        <v>242.7</v>
       </c>
     </row>
   </sheetData>
@@ -22963,7 +23303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25851,6 +26191,50 @@
         <v>1.04</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>1504 東元</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>2049 上銀</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C134" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="D134" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E134" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="F134" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/台股財報估值.xlsx
+++ b/data/台股財報估值.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="相對歷史水位" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐年營收(億)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐年EPS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐季毛利率" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42268,4 +42269,7171 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M204"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>6721 信實</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6.16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>6741 91APP*-KY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>72.72</v>
+      </c>
+      <c r="H3" t="n">
+        <v>76.72</v>
+      </c>
+      <c r="I3" t="n">
+        <v>73.43000000000001</v>
+      </c>
+      <c r="J3" t="n">
+        <v>71.87</v>
+      </c>
+      <c r="K3" t="n">
+        <v>72.83</v>
+      </c>
+      <c r="L3" t="n">
+        <v>77.73999999999999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>74.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>4953 緯軟</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="G4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="L4" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14.23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>3293 鈊象</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>96.17</v>
+      </c>
+      <c r="G5" t="n">
+        <v>96.45999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>97.68000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>97.27</v>
+      </c>
+      <c r="L5" t="n">
+        <v>97.58</v>
+      </c>
+      <c r="M5" t="n">
+        <v>97.81999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>3587 閎康</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="G6" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="H6" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="M6" t="n">
+        <v>30.89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2753 八方雲集</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="H7" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="I7" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="J7" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="K7" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="L7" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="M7" t="n">
+        <v>36.45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6690 安碁資訊</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="G8" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="I8" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="K8" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="L8" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="M8" t="n">
+        <v>37.48</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2947 振宇五金</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="G9" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="H9" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="I9" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>39.32</v>
+      </c>
+      <c r="K9" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="L9" t="n">
+        <v>38.82</v>
+      </c>
+      <c r="M9" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>6223 旺矽</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="G10" t="n">
+        <v>56.69</v>
+      </c>
+      <c r="H10" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="I10" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="J10" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="K10" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="L10" t="n">
+        <v>53.78</v>
+      </c>
+      <c r="M10" t="n">
+        <v>59.45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2453 凌群</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="G11" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="H11" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="L11" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="M11" t="n">
+        <v>24.72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>3017 奇鋐</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="G12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="I12" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="J12" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="K12" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="L12" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="M12" t="n">
+        <v>29.77</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>3004 豐達科</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="J13" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="L13" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="M13" t="n">
+        <v>25.24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>3583 辛耘</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="G14" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="H14" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="I14" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="K14" t="n">
+        <v>32.11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="M14" t="n">
+        <v>33.58</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6279 胡連</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="G15" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="H15" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="I15" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="L15" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="M15" t="n">
+        <v>26.65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6803 崑鼎</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="G16" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="J16" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="M16" t="n">
+        <v>19.82</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2755 揚秦</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="G17" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="H17" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="I17" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="K17" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="L17" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27.31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4129 聯合</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>77.44</v>
+      </c>
+      <c r="G18" t="n">
+        <v>79.47</v>
+      </c>
+      <c r="H18" t="n">
+        <v>76.63</v>
+      </c>
+      <c r="I18" t="n">
+        <v>80.64</v>
+      </c>
+      <c r="J18" t="n">
+        <v>76.08</v>
+      </c>
+      <c r="K18" t="n">
+        <v>75.87</v>
+      </c>
+      <c r="L18" t="n">
+        <v>78.77</v>
+      </c>
+      <c r="M18" t="n">
+        <v>79.59</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6446 藥華藥</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="G19" t="n">
+        <v>87.92</v>
+      </c>
+      <c r="H19" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="I19" t="n">
+        <v>88.87</v>
+      </c>
+      <c r="J19" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>91.58</v>
+      </c>
+      <c r="L19" t="n">
+        <v>88.86</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.87</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>2912 統一超</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="G20" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="H20" t="n">
+        <v>34.39</v>
+      </c>
+      <c r="I20" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="K20" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="L20" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="M20" t="n">
+        <v>34.58</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2345 智邦</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="G21" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="J21" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="K21" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="L21" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="M21" t="n">
+        <v>19.55</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>2376 技嘉</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="H22" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="I22" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="K22" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="L22" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>6752 叡揚</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="H23" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="I23" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="J23" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="K23" t="n">
+        <v>50.51</v>
+      </c>
+      <c r="L23" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="M23" t="n">
+        <v>46.36</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>6733 博晟生醫</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="G24" t="n">
+        <v>75.36</v>
+      </c>
+      <c r="H24" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="I24" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>72.14</v>
+      </c>
+      <c r="K24" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>69.14</v>
+      </c>
+      <c r="M24" t="n">
+        <v>72.37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2640 大車隊</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="G25" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="H25" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="I25" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="J25" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="K25" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="L25" t="n">
+        <v>51.63</v>
+      </c>
+      <c r="M25" t="n">
+        <v>50.31</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2480 敦陽科</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="H26" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="I26" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="J26" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="K26" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="L26" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="M26" t="n">
+        <v>23.46</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>2308 台達電</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="G27" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="H27" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="I27" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="J27" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="K27" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="L27" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="M27" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>2752 豆府</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>52.31</v>
+      </c>
+      <c r="G28" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="H28" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="J28" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="K28" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="L28" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>53.04</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>2937 集雅社</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="G29" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="H29" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="I29" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="J29" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="K29" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="L29" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20.66</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>2402 毅嘉</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="G30" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="H30" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="I30" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="J30" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="K30" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="L30" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>12.82</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>5278 尚凡*</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="G31" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="H31" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="J31" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="K31" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="L31" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="M31" t="n">
+        <v>53.91</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>9917 中保科</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="G32" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="H32" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="I32" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="J32" t="n">
+        <v>33.12</v>
+      </c>
+      <c r="K32" t="n">
+        <v>32.77</v>
+      </c>
+      <c r="L32" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="M32" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>8284 三竹</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="G33" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="H33" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="I33" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="J33" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="K33" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="L33" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="M33" t="n">
+        <v>24.19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>6612 奈米醫材</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>67.27</v>
+      </c>
+      <c r="I34" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="J34" t="n">
+        <v>59.57</v>
+      </c>
+      <c r="K34" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="L34" t="n">
+        <v>63.39</v>
+      </c>
+      <c r="M34" t="n">
+        <v>55.79</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>3265 台星科</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="H35" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="I35" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="J35" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="K35" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="L35" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="M35" t="n">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>4114 健喬</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>43.26</v>
+      </c>
+      <c r="G36" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="H36" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="I36" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="J36" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="K36" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="L36" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="M36" t="n">
+        <v>42.33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>3653 健策</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="G37" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="I37" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="J37" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="K37" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="L37" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="M37" t="n">
+        <v>41.78</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>5903 全家</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="G38" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="H38" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="I38" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="J38" t="n">
+        <v>36.84</v>
+      </c>
+      <c r="K38" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="L38" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="M38" t="n">
+        <v>34.69</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>9911 櫻花</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="H39" t="n">
+        <v>34.63</v>
+      </c>
+      <c r="I39" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="J39" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="K39" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="L39" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="M39" t="n">
+        <v>35.66</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>3130 一零四</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>88.06999999999999</v>
+      </c>
+      <c r="G40" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="H40" t="n">
+        <v>85.76000000000001</v>
+      </c>
+      <c r="I40" t="n">
+        <v>86.34999999999999</v>
+      </c>
+      <c r="J40" t="n">
+        <v>86.53</v>
+      </c>
+      <c r="K40" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="L40" t="n">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.45999999999999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>1513 中興電</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="G41" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="H41" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="I41" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="J41" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="K41" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="L41" t="n">
+        <v>27</v>
+      </c>
+      <c r="M41" t="n">
+        <v>25.98</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>4116 明基醫</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="G42" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="H42" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="I42" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="J42" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="K42" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="L42" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="M42" t="n">
+        <v>32.25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>2330 台積電</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="G43" t="n">
+        <v>57.83</v>
+      </c>
+      <c r="H43" t="n">
+        <v>59</v>
+      </c>
+      <c r="I43" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="J43" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="K43" t="n">
+        <v>59.45</v>
+      </c>
+      <c r="L43" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="M43" t="n">
+        <v>66.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>1736 喬山</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="G44" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="H44" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="I44" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="J44" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="K44" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="L44" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="M44" t="n">
+        <v>51.33</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>5904 寶雅</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="G45" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="I45" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="J45" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="K45" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="L45" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="M45" t="n">
+        <v>45.13</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>3036 文曄</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>3162 精確</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="G47" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H47" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="I47" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="J47" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="K47" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="L47" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="M47" t="n">
+        <v>10.41</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>3029 零壹</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>13</v>
+      </c>
+      <c r="G48" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="H48" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="I48" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="J48" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="L48" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="M48" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>5493 三聯</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="G49" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="H49" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="I49" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="J49" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="K49" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="L49" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="M49" t="n">
+        <v>12.89</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>2059 川湖</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="G50" t="n">
+        <v>70.54000000000001</v>
+      </c>
+      <c r="H50" t="n">
+        <v>71.81</v>
+      </c>
+      <c r="I50" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="J50" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>74.58</v>
+      </c>
+      <c r="L50" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="M50" t="n">
+        <v>77.73999999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>2368 金像電</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="G51" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="H51" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="I51" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="K51" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="L51" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="M51" t="n">
+        <v>34.81</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>8462 柏文</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="G52" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="H52" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="I52" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="J52" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="K52" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="L52" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="M52" t="n">
+        <v>33.57</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>2383 台光電</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="G53" t="n">
+        <v>27</v>
+      </c>
+      <c r="H53" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="I53" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="K53" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="L53" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="M53" t="n">
+        <v>29.42</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>5607 遠雄港</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="G54" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="H54" t="n">
+        <v>45.67</v>
+      </c>
+      <c r="I54" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="J54" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="K54" t="n">
+        <v>53.11</v>
+      </c>
+      <c r="L54" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="M54" t="n">
+        <v>51.33</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>5274 信驊</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>63.36</v>
+      </c>
+      <c r="G55" t="n">
+        <v>64.28</v>
+      </c>
+      <c r="H55" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="I55" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="J55" t="n">
+        <v>67.88</v>
+      </c>
+      <c r="K55" t="n">
+        <v>69.26000000000001</v>
+      </c>
+      <c r="L55" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="M55" t="n">
+        <v>69.18000000000001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>5312 寶島科</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="G56" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="H56" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="I56" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="J56" t="n">
+        <v>64.51000000000001</v>
+      </c>
+      <c r="K56" t="n">
+        <v>63.81</v>
+      </c>
+      <c r="L56" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="M56" t="n">
+        <v>63.85</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>6112 邁達特</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="G57" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="H57" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="I57" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="K57" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="L57" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="M57" t="n">
+        <v>13.87</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>8210 勤誠</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="G58" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="I58" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="J58" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="K58" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="L58" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="M58" t="n">
+        <v>32.83</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>6449 鈺邦</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="G59" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="H59" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="I59" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="J59" t="n">
+        <v>36.49</v>
+      </c>
+      <c r="K59" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="L59" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="M59" t="n">
+        <v>36.79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>3687 歐買尬</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="G60" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="H60" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="I60" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="J60" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="K60" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="L60" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="M60" t="n">
+        <v>40.71</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>6257 矽格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="G61" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="H61" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="I61" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="J61" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="K61" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="L61" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="M61" t="n">
+        <v>31.66</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>6683 雍智科技</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>46.94</v>
+      </c>
+      <c r="G62" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="H62" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="I62" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="J62" t="n">
+        <v>43.28</v>
+      </c>
+      <c r="K62" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="L62" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>3551 世禾</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="G63" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="H63" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="I63" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="J63" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="K63" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="L63" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="M63" t="n">
+        <v>37.44</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>6776 展碁國際</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="G64" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="H64" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I64" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="J64" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="K64" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="L64" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="M64" t="n">
+        <v>6.26</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>7556 意德士</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="G65" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="H65" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="I65" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="J65" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="K65" t="n">
+        <v>41.08</v>
+      </c>
+      <c r="L65" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="M65" t="n">
+        <v>39.22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>6138 茂達</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="G66" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="H66" t="n">
+        <v>35.31</v>
+      </c>
+      <c r="I66" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="K66" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="L66" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="M66" t="n">
+        <v>38.39</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>6525 捷敏-KY</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="G67" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="H67" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I67" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="J67" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="K67" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="L67" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="M67" t="n">
+        <v>26.14</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>3044 健鼎</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="G68" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="H68" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="I68" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="J68" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="K68" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="L68" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="M68" t="n">
+        <v>26.51</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>1519 華城</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="G69" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="H69" t="n">
+        <v>36.42</v>
+      </c>
+      <c r="I69" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="J69" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="K69" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="L69" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>43.61</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>2353 宏碁</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="G70" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="H70" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="I70" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J70" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="K70" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="L70" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="M70" t="n">
+        <v>11.16</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>2357 華碩</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="G71" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H71" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="I71" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="J71" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="K71" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="L71" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="M71" t="n">
+        <v>14.86</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>2363 矽統</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="G72" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="H72" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="I72" t="n">
+        <v>44.66</v>
+      </c>
+      <c r="J72" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="K72" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="L72" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="M72" t="n">
+        <v>28.79</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>2645 長榮航太</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="G73" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H73" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="I73" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="J73" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="K73" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="L73" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="M73" t="n">
+        <v>27.54</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>3019 亞光</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="G74" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="H74" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="J74" t="n">
+        <v>20</v>
+      </c>
+      <c r="K74" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="L74" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="M74" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>3324 雙鴻</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="G75" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="H75" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="I75" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="J75" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="L75" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>29.66</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>3630 新鉅科</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I76" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="J76" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="K76" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M76" t="n">
+        <v>11.07</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>3702 大聯大</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="K77" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L77" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="M77" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>3715 定穎投控</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="G78" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="H78" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="I78" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="J78" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="K78" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="L78" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="M78" t="n">
+        <v>16.12</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>4772 台特化</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="G79" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="H79" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="I79" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="J79" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="K79" t="n">
+        <v>54.16</v>
+      </c>
+      <c r="L79" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="M79" t="n">
+        <v>50.96</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>4904 遠傳</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="H80" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="I80" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="J80" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="K80" t="n">
+        <v>31</v>
+      </c>
+      <c r="L80" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="M80" t="n">
+        <v>33.02</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>5203 訊連</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>86.02</v>
+      </c>
+      <c r="G81" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="H81" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="I81" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="J81" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="K81" t="n">
+        <v>83.48999999999999</v>
+      </c>
+      <c r="L81" t="n">
+        <v>83.44</v>
+      </c>
+      <c r="M81" t="n">
+        <v>84.51000000000001</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>5269 祥碩</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>52.05</v>
+      </c>
+      <c r="G82" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="H82" t="n">
+        <v>52.79</v>
+      </c>
+      <c r="I82" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="J82" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="K82" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="L82" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="M82" t="n">
+        <v>50.83</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>6274 台燿</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="G83" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="H83" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="I83" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="J83" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="K83" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="L83" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="M83" t="n">
+        <v>25.15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>6469 大樹</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="G84" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="H84" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="I84" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="J84" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="K84" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="L84" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="M84" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>6712 長聖</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="G85" t="n">
+        <v>71.41</v>
+      </c>
+      <c r="H85" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="I85" t="n">
+        <v>71.39</v>
+      </c>
+      <c r="J85" t="n">
+        <v>72.41</v>
+      </c>
+      <c r="K85" t="n">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="L85" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="M85" t="n">
+        <v>80.23999999999999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>6739 竹陞科技</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="G86" t="n">
+        <v>59.94</v>
+      </c>
+      <c r="H86" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="I86" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="J86" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="K86" t="n">
+        <v>66.48</v>
+      </c>
+      <c r="L86" t="n">
+        <v>68.05</v>
+      </c>
+      <c r="M86" t="n">
+        <v>68.38</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>6787 晶瑞光</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>-143.37</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-178.4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-292.8</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-54.82</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-53.61</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="n">
+        <v>-65.45999999999999</v>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>-43.71</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="n">
+        <v>-53.76</v>
+      </c>
+      <c r="M87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>6788 華景電</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="G88" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="H88" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="I88" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="J88" t="n">
+        <v>56.27</v>
+      </c>
+      <c r="K88" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="L88" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="M88" t="n">
+        <v>60.33</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>6791 虎門科技</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="G89" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="H89" t="n">
+        <v>42.54</v>
+      </c>
+      <c r="I89" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="J89" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="K89" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="L89" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="M89" t="n">
+        <v>41.69</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>8016 矽創</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="G90" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="H90" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="I90" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="J90" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="K90" t="n">
+        <v>28.91</v>
+      </c>
+      <c r="L90" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="M90" t="n">
+        <v>31.33</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>1268 漢來美食</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="G91" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="H91" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="I91" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="J91" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="K91" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="L91" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="M91" t="n">
+        <v>48.89</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>2727 王品</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="G92" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="H92" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="I92" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="J92" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="K92" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="L92" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="M92" t="n">
+        <v>47.64</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>8996 高力</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="G93" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="H93" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="I93" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="J93" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="K93" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="L93" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="M93" t="n">
+        <v>29.02</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>3013 晟銘電</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="G94" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="H94" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="I94" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="J94" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="K94" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="L94" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="M94" t="n">
+        <v>21.15</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>1560 中砂</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="G95" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="H95" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="I95" t="n">
+        <v>30.91</v>
+      </c>
+      <c r="J95" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="K95" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="L95" t="n">
+        <v>34.18</v>
+      </c>
+      <c r="M95" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>2360 致茂</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="G96" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="H96" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="I96" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="J96" t="n">
+        <v>65.44</v>
+      </c>
+      <c r="K96" t="n">
+        <v>59.83</v>
+      </c>
+      <c r="L96" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="M96" t="n">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>2379 瑞昱</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>50.88</v>
+      </c>
+      <c r="G97" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="H97" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="I97" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="J97" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="K97" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="L97" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="M97" t="n">
+        <v>49.66</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>3008 大立光</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="G98" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="H98" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="I98" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="J98" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="K98" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="L98" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="M98" t="n">
+        <v>49.41</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>3406 玉晶光</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="G99" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="H99" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="I99" t="n">
+        <v>30.93</v>
+      </c>
+      <c r="J99" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="K99" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="L99" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="M99" t="n">
+        <v>33.56</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>3362 先進光</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G100" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="H100" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="I100" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="J100" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="K100" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="L100" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="M100" t="n">
+        <v>13.11</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>6209 今國光</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="G101" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="H101" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="I101" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="J101" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K101" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="L101" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="M101" t="n">
+        <v>30.93</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>3504 揚明光</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G102" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="H102" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="I102" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="J102" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="K102" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="L102" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="M102" t="n">
+        <v>18.23</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>3081 聯亞</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="G103" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="H103" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="J103" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="K103" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="L103" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="M103" t="n">
+        <v>54.76</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>2455 全新</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="G104" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="H104" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="I104" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.39</v>
+      </c>
+      <c r="K104" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="L104" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="M104" t="n">
+        <v>38.09</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>4991 環宇-KY</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="G105" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="H105" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I105" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="J105" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="K105" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="L105" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="M105" t="n">
+        <v>54.53</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>3363 上詮</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="G106" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="H106" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="I106" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="J106" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="K106" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="L106" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>4979 華星光</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="G107" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="H107" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="I107" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="J107" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="K107" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="L107" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M107" t="n">
+        <v>25.42</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>6442 光聖</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="G108" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="H108" t="n">
+        <v>54.13</v>
+      </c>
+      <c r="I108" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J108" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="K108" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="L108" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="M108" t="n">
+        <v>55.41</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>3163 波若威</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G109" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="H109" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="I109" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J109" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="K109" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="L109" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="M109" t="n">
+        <v>18.86</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>4977 眾達-KY</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="G110" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="H110" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="I110" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="J110" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="K110" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="L110" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="M110" t="n">
+        <v>19.73</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>3234 光環</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="G111" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="H111" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I111" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="J111" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K111" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L111" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="M111" t="n">
+        <v>9.789999999999999</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>3711 日月光投控</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="G112" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="H112" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="I112" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J112" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="K112" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="L112" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="M112" t="n">
+        <v>20.07</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>6451 訊芯-KY</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="G113" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="H113" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="I113" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J113" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="K113" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="L113" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="M113" t="n">
+        <v>11.96</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>3450 聯鈞</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="G114" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="H114" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="I114" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="J114" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="K114" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="L114" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="M114" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>6515 穎崴</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="G115" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="H115" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="I115" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="J115" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="K115" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="L115" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="M115" t="n">
+        <v>43.01</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>9942 茂順</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G116" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="I116" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="J116" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="K116" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="L116" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="M116" t="n">
+        <v>39.96</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>8926 台汽電</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="G117" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="H117" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="I117" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="J117" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="K117" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="L117" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="M117" t="n">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>6505 台塑化</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I118" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="J118" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="K118" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="L118" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="M118" t="n">
+        <v>16.79</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>1504 東元</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="G119" t="n">
+        <v>25.96</v>
+      </c>
+      <c r="H119" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="I119" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="J119" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="K119" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="L119" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="M119" t="n">
+        <v>23.47</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>2049 上銀</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="G120" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="H120" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="I120" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="J120" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="K120" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="L120" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="M120" t="n">
+        <v>31.94</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>8341 日友</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="G121" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="H121" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="I121" t="n">
+        <v>44</v>
+      </c>
+      <c r="J121" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="K121" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="L121" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="M121" t="n">
+        <v>49.32</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>8422 可寧衛*</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="G122" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="H122" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="I122" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="J122" t="n">
+        <v>59.61</v>
+      </c>
+      <c r="K122" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="L122" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="M122" t="n">
+        <v>48.21</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>9933 中鼎</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G123" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="H123" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="I123" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="J123" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="K123" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="L123" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="M123" t="n">
+        <v>13.05</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>2313 華通</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="G124" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H124" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="I124" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="J124" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="K124" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="L124" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="M124" t="n">
+        <v>17.98</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>3481 群創</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="G125" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I125" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="J125" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="L125" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="M125" t="n">
+        <v>14.43</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>3189 景碩</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="G126" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="H126" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="I126" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="J126" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="K126" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="L126" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="M126" t="n">
+        <v>21.16</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>4174 浩鼎</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="n">
+        <v>-73.20999999999999</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-65.62</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-182.78</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-111.93</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-182.05</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-211.59</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-76.09999999999999</v>
+      </c>
+      <c r="M127" t="n">
+        <v>-497.41</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>4746 台耀</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="G128" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="H128" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="I128" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="J128" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="K128" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="L128" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="M128" t="n">
+        <v>42.98</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>1784 訊聯</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="G129" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="H129" t="n">
+        <v>58.08</v>
+      </c>
+      <c r="I129" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="J129" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="K129" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="L129" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="M129" t="n">
+        <v>53.81</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>6589 台康生技</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="G130" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="H130" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="I130" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="J130" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="K130" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="L130" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="M130" t="n">
+        <v>21.06</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>8299 群聯</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="G131" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="H131" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="I131" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="J131" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="K131" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="L131" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="M131" t="n">
+        <v>61.82</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>2408 南亞科</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="G132" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-10.56</v>
+      </c>
+      <c r="I132" t="n">
+        <v>-14.95</v>
+      </c>
+      <c r="J132" t="n">
+        <v>-20.56</v>
+      </c>
+      <c r="K132" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="L132" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="M132" t="n">
+        <v>67.89</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>2344 華邦電</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="G133" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="H133" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="I133" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="J133" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="K133" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="L133" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="M133" t="n">
+        <v>53.37</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>2337 旺宏</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="G134" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="H134" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I134" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J134" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="K134" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="L134" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="M134" t="n">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>6770 力積電</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-11.12</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-6.53</v>
+      </c>
+      <c r="L135" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="M135" t="n">
+        <v>10.23</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>5289 宜鼎</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="G136" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="H136" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="I136" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="J136" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="K136" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="L136" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="M136" t="n">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>2329 華泰</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G137" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="H137" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="I137" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="J137" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="K137" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="L137" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="M137" t="n">
+        <v>12.79</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>3260 威剛</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="G138" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="H138" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="I138" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="J138" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="K138" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="L138" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="M138" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>2451 創見</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="G139" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="I139" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="K139" t="n">
+        <v>45.21</v>
+      </c>
+      <c r="L139" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="M139" t="n">
+        <v>76.39</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>8150 南茂</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="G140" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H140" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="I140" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="J140" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K140" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="L140" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="M140" t="n">
+        <v>13.78</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>2395 研華</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G141" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="H141" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="I141" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="J141" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="K141" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="L141" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="M141" t="n">
+        <v>39.15</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>2065 世豐</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="G142" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="H142" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="I142" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="J142" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="K142" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="L142" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="M142" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>4967 十銓</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="G143" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="H143" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="I143" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="J143" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K143" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="L143" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="M143" t="n">
+        <v>38.01</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>8271 宇瞻</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="G144" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H144" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="I144" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="J144" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K144" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="L144" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="M144" t="n">
+        <v>49.27</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>5227 立凱-KY</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="G145" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="H145" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I145" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="J145" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="K145" t="n">
+        <v>-47.38</v>
+      </c>
+      <c r="L145" t="n">
+        <v>-30.86</v>
+      </c>
+      <c r="M145" t="n">
+        <v>-70.7</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>6863 永道-KY</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="G146" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="H146" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="I146" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J146" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="K146" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="L146" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="M146" t="n">
+        <v>19.32</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>6441 廣錠</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="G147" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="H147" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="I147" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K147" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="L147" t="n">
+        <v>-99</v>
+      </c>
+      <c r="M147" t="n">
+        <v>-113.66</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>2327 國巨*</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="G148" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="H148" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="I148" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="J148" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="K148" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="L148" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="M148" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>4583 台灣精銳</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="G149" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="H149" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="I149" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="J149" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="K149" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="L149" t="n">
+        <v>51.18</v>
+      </c>
+      <c r="M149" t="n">
+        <v>53.13</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>2915 潤泰全</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="n">
+        <v>38</v>
+      </c>
+      <c r="G150" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="H150" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="I150" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="J150" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="K150" t="n">
+        <v>46.74</v>
+      </c>
+      <c r="L150" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="M150" t="n">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>3105 穩懋</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="G151" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="H151" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="I151" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="J151" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="K151" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="L151" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="M151" t="n">
+        <v>26.34</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>1723 中碳</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="n">
+        <v>24.94</v>
+      </c>
+      <c r="G152" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="H152" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="I152" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="J152" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="K152" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="L152" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="M152" t="n">
+        <v>25.02</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>3023 信邦</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="G153" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="H153" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="I153" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="J153" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="K153" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="L153" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="M153" t="n">
+        <v>24.51</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>3016 嘉晶</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G154" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="H154" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="I154" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="J154" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="K154" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="L154" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="M154" t="n">
+        <v>17.77</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>6488 環球晶</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="G155" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="H155" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="I155" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="J155" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="K155" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="L155" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="M155" t="n">
+        <v>20.83</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>6182 合晶</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="G156" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H156" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="I156" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="J156" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="K156" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="L156" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="M156" t="n">
+        <v>19.03</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>6435 大中</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="G157" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="H157" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="I157" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J157" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="K157" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="L157" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="M157" t="n">
+        <v>26.78</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>2634 漢翔</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="G158" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="H158" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="I158" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="J158" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="K158" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L158" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="M158" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>1503 士電</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="G159" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="H159" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="I159" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="J159" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="K159" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="L159" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="M159" t="n">
+        <v>23.77</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>1514 亞力</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="G160" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="H160" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="I160" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="J160" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="K160" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="L160" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="M160" t="n">
+        <v>17.54</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>8027 鈦昇</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="G161" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="H161" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="I161" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="J161" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="K161" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="L161" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="M161" t="n">
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>3673 TPK-KY</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="G162" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="I162" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="J162" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="K162" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="L162" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="M162" t="n">
+        <v>9.380000000000001</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>8064 東捷</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="G163" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="H163" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="I163" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="J163" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="K163" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="L163" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="M163" t="n">
+        <v>24.66</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>3131 弘塑</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="G164" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="H164" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="I164" t="n">
+        <v>40.81</v>
+      </c>
+      <c r="J164" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="K164" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="L164" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>33.78</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>3455 由田</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="G165" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="H165" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="I165" t="n">
+        <v>50.79</v>
+      </c>
+      <c r="J165" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="K165" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="L165" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="M165" t="n">
+        <v>54.54</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>3055 蔚華科</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="n">
+        <v>27.61</v>
+      </c>
+      <c r="G166" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="H166" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I166" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="J166" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="K166" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L166" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="M166" t="n">
+        <v>31.88</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>3535 晶彩科</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="n">
+        <v>44.63</v>
+      </c>
+      <c r="G167" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="I167" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="J167" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="K167" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="L167" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="M167" t="n">
+        <v>46.09</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>4760 勤凱</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="G168" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="H168" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="I168" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="J168" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="K168" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="L168" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="M168" t="n">
+        <v>19.74</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>4768 晶呈科技</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="G169" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="H169" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="I169" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="J169" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="K169" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="L169" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="M169" t="n">
+        <v>13.39</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>3037 欣興</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="G170" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="H170" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="I170" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="J170" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="K170" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="L170" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="M170" t="n">
+        <v>17.96</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>2467 志聖</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="G171" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="H171" t="n">
+        <v>41.85</v>
+      </c>
+      <c r="I171" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="J171" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="K171" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="L171" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>49.47</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>1802 台玻</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="G172" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H172" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I172" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="J172" t="n">
+        <v>10</v>
+      </c>
+      <c r="K172" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="L172" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="M172" t="n">
+        <v>19.23</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>4416 三圓</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="G173" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="H173" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="I173" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="J173" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="K173" t="n">
+        <v>217.26</v>
+      </c>
+      <c r="L173" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="M173" t="n">
+        <v>45.88</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>2412 中華電</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="G174" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="H174" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="I174" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="J174" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="K174" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="L174" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="M174" t="n">
+        <v>37.92</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>3045 台灣大</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="G175" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="H175" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="I175" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="J175" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="K175" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="L175" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="M175" t="n">
+        <v>21.56</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>2404 漢唐</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="G176" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="H176" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I176" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="J176" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="K176" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="L176" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="M176" t="n">
+        <v>23.32</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>4749 新應材</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="G177" t="n">
+        <v>37.66</v>
+      </c>
+      <c r="H177" t="n">
+        <v>38.03</v>
+      </c>
+      <c r="I177" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="J177" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="K177" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="L177" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="M177" t="n">
+        <v>45.41</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>9931 欣高</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="G178" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="H178" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="I178" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="J178" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="K178" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="L178" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="M178" t="n">
+        <v>16.69</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>9918 欣天然</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G179" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="I179" t="n">
+        <v>33.26</v>
+      </c>
+      <c r="J179" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="K179" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="L179" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="M179" t="n">
+        <v>30.74</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>9908 大台北</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="G180" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="H180" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="I180" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="J180" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="K180" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="L180" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="M180" t="n">
+        <v>21.44</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>3026 禾伸堂</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="G181" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="H181" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="I181" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="J181" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="K181" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="L181" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="M181" t="n">
+        <v>24.24</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>6949 沛爾生醫-創</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="n">
+        <v>-59.47</v>
+      </c>
+      <c r="G182" t="n">
+        <v>-53.8</v>
+      </c>
+      <c r="H182" t="n">
+        <v>-77.48999999999999</v>
+      </c>
+      <c r="I182" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="J182" t="n">
+        <v>-56.46</v>
+      </c>
+      <c r="K182" t="n">
+        <v>-88.26000000000001</v>
+      </c>
+      <c r="L182" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="M182" t="n">
+        <v>-18.92</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>2371 大同</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="G183" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="H183" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="I183" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="J183" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="K183" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="L183" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="M183" t="n">
+        <v>16.44</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>6239 力成</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="G184" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="H184" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="I184" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="J184" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="K184" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="L184" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="M184" t="n">
+        <v>19.44</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>2425 承啟</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G185" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="H185" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="I185" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J185" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="K185" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L185" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M185" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>7703 銳澤</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="G186" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="H186" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I186" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="J186" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="K186" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="L186" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="M186" t="n">
+        <v>20.59</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>7730 暉盛-創</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="F187" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="I187" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="J187" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="K187" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="L187" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="M187" t="n">
+        <v>45.85</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>3030 德律</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="n">
+        <v>58.08</v>
+      </c>
+      <c r="G188" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="H188" t="n">
+        <v>61.52</v>
+      </c>
+      <c r="I188" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="J188" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="K188" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="L188" t="n">
+        <v>60.64</v>
+      </c>
+      <c r="M188" t="n">
+        <v>60.27</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>7825 和亞智慧</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="n">
+        <v>60.19</v>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="M189" t="n">
+        <v>63.01</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>7828 創新服務</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="K190" t="n">
+        <v>79.41</v>
+      </c>
+      <c r="L190" t="n">
+        <v>79.36</v>
+      </c>
+      <c r="M190" t="n">
+        <v>80.18000000000001</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>1595 川寶</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="G191" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="H191" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="I191" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="J191" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="K191" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="L191" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="M191" t="n">
+        <v>14.17</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>4542 科嶠</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="G192" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="H192" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="I192" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="J192" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="K192" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="L192" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="M192" t="n">
+        <v>39.18</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>3149 正達</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="G193" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H193" t="n">
+        <v>-10.84</v>
+      </c>
+      <c r="I193" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="J193" t="n">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="K193" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="L193" t="n">
+        <v>-12.37</v>
+      </c>
+      <c r="M193" t="n">
+        <v>-4.14</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>4728 雙美</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="G194" t="n">
+        <v>79.42</v>
+      </c>
+      <c r="H194" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="I194" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="J194" t="n">
+        <v>79.11</v>
+      </c>
+      <c r="K194" t="n">
+        <v>77.89</v>
+      </c>
+      <c r="L194" t="n">
+        <v>77.03</v>
+      </c>
+      <c r="M194" t="n">
+        <v>78.91</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>2421 建準</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="G195" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="H195" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="I195" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="J195" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="K195" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="L195" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="M195" t="n">
+        <v>31.66</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>3005 神基</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="G196" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="H196" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="I196" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J196" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="K196" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="L196" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="M196" t="n">
+        <v>31.06</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>4506 崇友</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="G197" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="H197" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="I197" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="J197" t="n">
+        <v>32.12</v>
+      </c>
+      <c r="K197" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="L197" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="M197" t="n">
+        <v>33.53</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>2535 達欣工</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="G198" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="H198" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="I198" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="J198" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="K198" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="L198" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="M198" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>1215 卜蜂</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="G199" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H199" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="I199" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="J199" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="K199" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="L199" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="M199" t="n">
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>1232 大統益</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="G200" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="H200" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="I200" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="J200" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="K200" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="L200" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="M200" t="n">
+        <v>13.69</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>5434 崇越</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="n">
+        <v>14</v>
+      </c>
+      <c r="G201" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H201" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="I201" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="J201" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="K201" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="L201" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="M201" t="n">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>1773 勝一</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="G202" t="n">
+        <v>31.94</v>
+      </c>
+      <c r="H202" t="n">
+        <v>31.94</v>
+      </c>
+      <c r="I202" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="J202" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="K202" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="L202" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="M202" t="n">
+        <v>37.55</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>2301 光寶科</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="G203" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="H203" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="I203" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="J203" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="K203" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="L203" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="M203" t="n">
+        <v>21.66</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>8081 致新</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="G204" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="H204" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="I204" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="J204" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="K204" t="n">
+        <v>35.27</v>
+      </c>
+      <c r="L204" t="n">
+        <v>38.12</v>
+      </c>
+      <c r="M204" t="n">
+        <v>39.61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/台股財報估值.xlsx
+++ b/data/台股財報估值.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V225"/>
+  <dimension ref="A1:W225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,25 +520,30 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>市值(億)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>PER(自算)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PE位階%</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PBR</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>殖利率%</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>最新月營收年增%</t>
         </is>
@@ -601,18 +606,21 @@
         <v>793</v>
       </c>
       <c r="R2" t="n">
+        <v>2234.7</v>
+      </c>
+      <c r="S2" t="n">
         <v>19.64</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>67</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>18.56</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>4.54</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -673,18 +681,21 @@
         <v>24.2</v>
       </c>
       <c r="R3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="S3" t="n">
         <v>25</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>94</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1.88</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5.04</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>15</v>
       </c>
     </row>
@@ -745,18 +756,21 @@
         <v>19275</v>
       </c>
       <c r="R4" t="n">
+        <v>7286.5</v>
+      </c>
+      <c r="S4" t="n">
         <v>163.53</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>99</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>122.24</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0.42</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>68.7</v>
       </c>
     </row>
@@ -817,18 +831,21 @@
         <v>376.5</v>
       </c>
       <c r="R5" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="S5" t="n">
         <v>28.33</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>74</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>17.29</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>3.21</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>23.8</v>
       </c>
     </row>
@@ -889,18 +906,21 @@
         <v>1280</v>
       </c>
       <c r="R6" t="n">
+        <v>2439.5</v>
+      </c>
+      <c r="S6" t="n">
         <v>23.77</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>96</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>16.81</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3.13</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>85</v>
       </c>
     </row>
@@ -961,18 +981,21 @@
         <v>636</v>
       </c>
       <c r="R7" t="n">
+        <v>677</v>
+      </c>
+      <c r="S7" t="n">
         <v>20.22</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>42</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>10.6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>4.01</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>19.2</v>
       </c>
     </row>
@@ -1033,18 +1056,21 @@
         <v>2595</v>
       </c>
       <c r="R8" t="n">
+        <v>14561</v>
+      </c>
+      <c r="S8" t="n">
         <v>49.07</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>99</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>22.2</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>0.58</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>56.6</v>
       </c>
     </row>
@@ -1105,18 +1131,21 @@
         <v>4725</v>
       </c>
       <c r="R9" t="n">
+        <v>6332.1</v>
+      </c>
+      <c r="S9" t="n">
         <v>142.15</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>98</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>43.42</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>0.42</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>132.1</v>
       </c>
     </row>
@@ -1177,18 +1206,21 @@
         <v>831</v>
       </c>
       <c r="R10" t="n">
+        <v>2625</v>
+      </c>
+      <c r="S10" t="n">
         <v>57.11</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>84</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>31.86</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>1.44</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>-9.300000000000001</v>
       </c>
     </row>
@@ -1249,18 +1281,21 @@
         <v>900</v>
       </c>
       <c r="R11" t="n">
+        <v>4639.6</v>
+      </c>
+      <c r="S11" t="n">
         <v>32.22</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>99</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>10.26</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>2.78</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>21.9</v>
       </c>
     </row>
@@ -1321,18 +1356,21 @@
         <v>2510</v>
       </c>
       <c r="R12" t="n">
+        <v>650902.5</v>
+      </c>
+      <c r="S12" t="n">
         <v>33.74</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>99</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>11.05</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>0.88</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>30.1</v>
       </c>
     </row>
@@ -1393,18 +1431,21 @@
         <v>2400</v>
       </c>
       <c r="R13" t="n">
+        <v>9458.5</v>
+      </c>
+      <c r="S13" t="n">
         <v>39.31</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>83</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>1.34</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>3.76</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>60.6</v>
       </c>
     </row>
@@ -1465,18 +1506,21 @@
         <v>180</v>
       </c>
       <c r="R14" t="n">
+        <v>48</v>
+      </c>
+      <c r="S14" t="n">
         <v>11.78</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>4.25</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>7.5</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1537,18 +1581,21 @@
         <v>1395</v>
       </c>
       <c r="R15" t="n">
+        <v>7212.8</v>
+      </c>
+      <c r="S15" t="n">
         <v>61.45</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>98</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>20.46</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0.7</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>87.3</v>
       </c>
     </row>
@@ -1609,18 +1656,21 @@
         <v>224</v>
       </c>
       <c r="R16" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="S16" t="n">
         <v>14.85</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>12</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>3.67</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>6.69</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>10.5</v>
       </c>
     </row>
@@ -1681,18 +1731,21 @@
         <v>5600</v>
       </c>
       <c r="R17" t="n">
+        <v>20066</v>
+      </c>
+      <c r="S17" t="n">
         <v>120.3</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>100</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>2.68</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>4.97</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>114.6</v>
       </c>
     </row>
@@ -1753,18 +1806,21 @@
         <v>1190</v>
       </c>
       <c r="R18" t="n">
+        <v>278.4</v>
+      </c>
+      <c r="S18" t="n">
         <v>62.01</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>83</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>32.45</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>1.09</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>99.3</v>
       </c>
     </row>
@@ -1825,18 +1881,21 @@
         <v>223.5</v>
       </c>
       <c r="R19" t="n">
+        <v>2323.6</v>
+      </c>
+      <c r="S19" t="n">
         <v>20.39</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>10.19</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>2.83</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -1897,18 +1956,21 @@
         <v>7550</v>
       </c>
       <c r="R20" t="n">
+        <v>7194.9</v>
+      </c>
+      <c r="S20" t="n">
         <v>66.54000000000001</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>100</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>22.82</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>0.68</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>172.1</v>
       </c>
     </row>
@@ -1969,18 +2031,21 @@
         <v>2310</v>
       </c>
       <c r="R21" t="n">
+        <v>9823.200000000001</v>
+      </c>
+      <c r="S21" t="n">
         <v>72.70999999999999</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>98</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>35.28</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>0.84</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>133.1</v>
       </c>
     </row>
@@ -2041,18 +2106,21 @@
         <v>315</v>
       </c>
       <c r="R22" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="S22" t="n">
         <v>19.94</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>95</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>3.24</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>3.65</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>39.8</v>
       </c>
     </row>
@@ -2113,18 +2181,21 @@
         <v>142</v>
       </c>
       <c r="R23" t="n">
+        <v>227.2</v>
+      </c>
+      <c r="S23" t="n">
         <v>16.42</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>3.62</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>5.07</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>9.9</v>
       </c>
     </row>
@@ -2185,18 +2256,21 @@
         <v>154.5</v>
       </c>
       <c r="R24" t="n">
+        <v>164.3</v>
+      </c>
+      <c r="S24" t="n">
         <v>18.41</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>79</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>5.5</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>5.05</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>16.4</v>
       </c>
     </row>
@@ -2257,18 +2331,21 @@
         <v>188</v>
       </c>
       <c r="R25" t="n">
+        <v>419.7</v>
+      </c>
+      <c r="S25" t="n">
         <v>27.01</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>61</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>5.1</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>3.46</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>7.4</v>
       </c>
     </row>
@@ -2329,18 +2406,21 @@
         <v>394</v>
       </c>
       <c r="R26" t="n">
+        <v>298</v>
+      </c>
+      <c r="S26" t="n">
         <v>27.9</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>91</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>8.57</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>2.79</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>15.4</v>
       </c>
     </row>
@@ -2401,18 +2481,21 @@
         <v>1370</v>
       </c>
       <c r="R27" t="n">
+        <v>1716.9</v>
+      </c>
+      <c r="S27" t="n">
         <v>40.04</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>89</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>13.61</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>1.02</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>37.3</v>
       </c>
     </row>
@@ -2473,18 +2556,21 @@
         <v>318</v>
       </c>
       <c r="R28" t="n">
+        <v>274</v>
+      </c>
+      <c r="S28" t="n">
         <v>18.11</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>97</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>3.76</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>5.03</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>-3.3</v>
       </c>
     </row>
@@ -2545,18 +2631,21 @@
         <v>333</v>
       </c>
       <c r="R29" t="n">
+        <v>799.4</v>
+      </c>
+      <c r="S29" t="n">
         <v>26.08</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>81</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>4.57</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>3</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>17.5</v>
       </c>
     </row>
@@ -2617,18 +2706,21 @@
         <v>1075</v>
       </c>
       <c r="R30" t="n">
+        <v>1000.6</v>
+      </c>
+      <c r="S30" t="n">
         <v>30.58</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>64</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>7.45</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1.11</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>93.8</v>
       </c>
     </row>
@@ -2689,18 +2781,21 @@
         <v>9460</v>
       </c>
       <c r="R31" t="n">
+        <v>3409.2</v>
+      </c>
+      <c r="S31" t="n">
         <v>192.04</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>98</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>52.47</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.53</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>119.8</v>
       </c>
     </row>
@@ -2761,18 +2856,21 @@
         <v>3840</v>
       </c>
       <c r="R32" t="n">
+        <v>5634.5</v>
+      </c>
+      <c r="S32" t="n">
         <v>104.63</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>97</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>26.6</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.57</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>37.7</v>
       </c>
     </row>
@@ -2833,18 +2931,21 @@
         <v>350</v>
       </c>
       <c r="R33" t="n">
+        <v>826.8</v>
+      </c>
+      <c r="S33" t="n">
         <v>30.33</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>94</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>7.9</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>2</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>14.7</v>
       </c>
     </row>
@@ -2905,18 +3006,21 @@
         <v>344</v>
       </c>
       <c r="R34" t="n">
+        <v>2304.4</v>
+      </c>
+      <c r="S34" t="n">
         <v>16.07</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>52</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>1.43</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>4.99</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2977,18 +3081,21 @@
         <v>142.5</v>
       </c>
       <c r="R35" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="S35" t="n">
         <v>27.04</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>21</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>4.87</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>2.81</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3049,18 +3156,21 @@
         <v>74.3</v>
       </c>
       <c r="R36" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="S36" t="n">
         <v>19</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>5</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>3.12</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>5.06</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -3121,18 +3231,21 @@
         <v>116.5</v>
       </c>
       <c r="R37" t="n">
+        <v>525.6</v>
+      </c>
+      <c r="S37" t="n">
         <v>17.18</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>32</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>3.61</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>5.32</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -3193,18 +3306,21 @@
         <v>1115</v>
       </c>
       <c r="R38" t="n">
+        <v>5331</v>
+      </c>
+      <c r="S38" t="n">
         <v>68.73999999999999</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>100</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>5.71</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>-3.3</v>
       </c>
     </row>
@@ -3265,18 +3381,21 @@
         <v>1970</v>
       </c>
       <c r="R39" t="n">
+        <v>1897.8</v>
+      </c>
+      <c r="S39" t="n">
         <v>26.04</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>86</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>13.09</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>0.87</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>640.8</v>
       </c>
     </row>
@@ -3337,18 +3456,21 @@
         <v>499.5</v>
       </c>
       <c r="R40" t="n">
+        <v>4336.9</v>
+      </c>
+      <c r="S40" t="n">
         <v>38.63</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>91</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>8.74</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>2.24</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>32.1</v>
       </c>
     </row>
@@ -3409,18 +3531,21 @@
         <v>3585</v>
       </c>
       <c r="R41" t="n">
+        <v>1048.9</v>
+      </c>
+      <c r="S41" t="n">
         <v>67.83</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>94</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>26.13</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>1.29</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>7.2</v>
       </c>
     </row>
@@ -3481,18 +3606,21 @@
         <v>506</v>
       </c>
       <c r="R42" t="n">
+        <v>979.9</v>
+      </c>
+      <c r="S42" t="n">
         <v>21.31</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>100</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>5.1</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>2.67</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>18.6</v>
       </c>
     </row>
@@ -3553,18 +3681,21 @@
         <v>178.5</v>
       </c>
       <c r="R43" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="S43" t="n">
         <v>24.65</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>86</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>4.52</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>2.24</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>28.4</v>
       </c>
     </row>
@@ -3625,18 +3756,21 @@
         <v>443.5</v>
       </c>
       <c r="R44" t="n">
+        <v>171.8</v>
+      </c>
+      <c r="S44" t="n">
         <v>23.99</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>90</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>7.1</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>3.38</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3697,18 +3831,21 @@
         <v>52.6</v>
       </c>
       <c r="R45" t="n">
+        <v>580.9</v>
+      </c>
+      <c r="S45" t="n">
         <v>6.03</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>62</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>0.49</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>3.61</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>-21.8</v>
       </c>
     </row>
@@ -3769,18 +3906,21 @@
         <v>152.5</v>
       </c>
       <c r="R46" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="S46" t="n">
         <v>16.54</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>56</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>4.87</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>5.25</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>7.7</v>
       </c>
     </row>
@@ -3841,18 +3981,21 @@
         <v>288</v>
       </c>
       <c r="R47" t="n">
+        <v>209.6</v>
+      </c>
+      <c r="S47" t="n">
         <v>15.6</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>2</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>3.33</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>5.48</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>-4.3</v>
       </c>
     </row>
@@ -3913,18 +4056,21 @@
         <v>349</v>
       </c>
       <c r="R48" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="S48" t="n">
         <v>32.26</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>100</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>6.87</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>2.15</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>22.2</v>
       </c>
     </row>
@@ -3985,18 +4131,21 @@
         <v>150</v>
       </c>
       <c r="R49" t="n">
+        <v>430.4</v>
+      </c>
+      <c r="S49" t="n">
         <v>17.5</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>34</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>3.79</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>3.49</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>14.9</v>
       </c>
     </row>
@@ -4057,18 +4206,21 @@
         <v>115</v>
       </c>
       <c r="R50" t="n">
+        <v>339</v>
+      </c>
+      <c r="S50" t="n">
         <v>12.39</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>10</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>3.2</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>6.09</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -4129,18 +4281,21 @@
         <v>118.5</v>
       </c>
       <c r="R51" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="S51" t="n">
         <v>14.43</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>69</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>2.18</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>5.91</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>10.8</v>
       </c>
     </row>
@@ -4201,18 +4356,21 @@
         <v>105</v>
       </c>
       <c r="R52" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="S52" t="n">
         <v>21.52</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>47</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>4.87</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>3.34</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -4273,18 +4431,21 @@
         <v>409.5</v>
       </c>
       <c r="R53" t="n">
+        <v>757.2</v>
+      </c>
+      <c r="S53" t="n">
         <v>129.18</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>99</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>20.65</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>0.64</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>46.5</v>
       </c>
     </row>
@@ -4345,18 +4506,21 @@
         <v>82.5</v>
       </c>
       <c r="R54" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="S54" t="n">
         <v>12.91</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>3</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>2.12</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>6.75</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>8.699999999999999</v>
       </c>
     </row>
@@ -4417,18 +4581,21 @@
         <v>1605</v>
       </c>
       <c r="R55" t="n">
+        <v>442.3</v>
+      </c>
+      <c r="S55" t="n">
         <v>89.70999999999999</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>96</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>15.26</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>12.3</v>
       </c>
     </row>
@@ -4489,18 +4656,21 @@
         <v>6415</v>
       </c>
       <c r="R56" t="n">
+        <v>6285.5</v>
+      </c>
+      <c r="S56" t="n">
         <v>167.32</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>100</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>39.89</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>0.34</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>57.8</v>
       </c>
     </row>
@@ -4561,18 +4731,21 @@
         <v>66.5</v>
       </c>
       <c r="R57" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="S57" t="n">
         <v>14.55</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>80</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>2.2</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>6.02</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>8.699999999999999</v>
       </c>
     </row>
@@ -4633,18 +4806,21 @@
         <v>382</v>
       </c>
       <c r="R58" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="S58" t="n">
         <v>49.55</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>99</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>12.31</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>1.23</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>64.8</v>
       </c>
     </row>
@@ -4705,18 +4881,21 @@
         <v>100.5</v>
       </c>
       <c r="R59" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="S59" t="n">
         <v>13.26</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>25</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>2.91</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>4.78</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -4777,18 +4956,21 @@
         <v>138.5</v>
       </c>
       <c r="R60" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="S60" t="n">
         <v>19.79</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>58</v>
       </c>
-      <c r="T60" t="n">
+      <c r="U60" t="n">
         <v>4.51</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>4.33</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>15.5</v>
       </c>
     </row>
@@ -4849,18 +5031,21 @@
         <v>118.5</v>
       </c>
       <c r="R61" t="n">
+        <v>4412.1</v>
+      </c>
+      <c r="S61" t="n">
         <v>24.04</v>
       </c>
-      <c r="S61" t="n">
+      <c r="T61" t="n">
         <v>28</v>
       </c>
-      <c r="T61" t="n">
+      <c r="U61" t="n">
         <v>3.94</v>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
         <v>4.05</v>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>3.9</v>
       </c>
     </row>
@@ -4921,18 +5106,21 @@
         <v>119</v>
       </c>
       <c r="R62" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="S62" t="n">
         <v>17.12</v>
       </c>
-      <c r="S62" t="n">
+      <c r="T62" t="n">
         <v>55</v>
       </c>
-      <c r="T62" t="n">
+      <c r="U62" t="n">
         <v>3.39</v>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
         <v>4.45</v>
       </c>
-      <c r="V62" t="n">
+      <c r="W62" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -4993,18 +5181,21 @@
         <v>630</v>
       </c>
       <c r="R63" t="n">
+        <v>987.6</v>
+      </c>
+      <c r="S63" t="n">
         <v>83.44</v>
       </c>
-      <c r="S63" t="n">
+      <c r="T63" t="n">
         <v>98</v>
       </c>
-      <c r="T63" t="n">
+      <c r="U63" t="n">
         <v>11.82</v>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
         <v>0.87</v>
       </c>
-      <c r="V63" t="n">
+      <c r="W63" t="n">
         <v>74.59999999999999</v>
       </c>
     </row>
@@ -5065,18 +5256,21 @@
         <v>187</v>
       </c>
       <c r="R64" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="S64" t="n">
         <v>13.87</v>
       </c>
-      <c r="S64" t="n">
+      <c r="T64" t="n">
         <v>15</v>
       </c>
-      <c r="T64" t="n">
+      <c r="U64" t="n">
         <v>3.51</v>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
         <v>6.42</v>
       </c>
-      <c r="V64" t="n">
+      <c r="W64" t="n">
         <v>13.3</v>
       </c>
     </row>
@@ -5137,18 +5331,21 @@
         <v>246.5</v>
       </c>
       <c r="R65" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="S65" t="n">
         <v>14.81</v>
       </c>
-      <c r="S65" t="n">
+      <c r="T65" t="n">
         <v>50</v>
       </c>
-      <c r="T65" t="n">
+      <c r="U65" t="n">
         <v>5.33</v>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
         <v>6.54</v>
       </c>
-      <c r="V65" t="n">
+      <c r="W65" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5209,18 +5406,21 @@
         <v>100.5</v>
       </c>
       <c r="R66" t="n">
+        <v>627.4</v>
+      </c>
+      <c r="S66" t="n">
         <v>12.27</v>
       </c>
-      <c r="S66" t="n">
+      <c r="T66" t="n">
         <v>36</v>
       </c>
-      <c r="T66" t="n">
+      <c r="U66" t="n">
         <v>2.68</v>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
         <v>6.76</v>
       </c>
-      <c r="V66" t="n">
+      <c r="W66" t="n">
         <v>15.1</v>
       </c>
     </row>
@@ -5281,18 +5481,21 @@
         <v>132.5</v>
       </c>
       <c r="R67" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="S67" t="n">
         <v>14.31</v>
       </c>
-      <c r="S67" t="n">
+      <c r="T67" t="n">
         <v>56</v>
       </c>
-      <c r="T67" t="n">
+      <c r="U67" t="n">
         <v>2.22</v>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
         <v>3.88</v>
       </c>
-      <c r="V67" t="n">
+      <c r="W67" t="n">
         <v>29.2</v>
       </c>
     </row>
@@ -5353,18 +5556,21 @@
         <v>155</v>
       </c>
       <c r="R68" t="n">
+        <v>200</v>
+      </c>
+      <c r="S68" t="n">
         <v>25.54</v>
       </c>
-      <c r="S68" t="n">
+      <c r="T68" t="n">
         <v>100</v>
       </c>
-      <c r="T68" t="n">
+      <c r="U68" t="n">
         <v>4.56</v>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
         <v>3.23</v>
       </c>
-      <c r="V68" t="n">
+      <c r="W68" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5425,18 +5631,21 @@
         <v>966</v>
       </c>
       <c r="R69" t="n">
+        <v>895.8</v>
+      </c>
+      <c r="S69" t="n">
         <v>76.06</v>
       </c>
-      <c r="S69" t="n">
+      <c r="T69" t="n">
         <v>78</v>
       </c>
-      <c r="T69" t="n">
+      <c r="U69" t="n">
         <v>10.02</v>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
         <v>0.83</v>
       </c>
-      <c r="V69" t="n">
+      <c r="W69" t="n">
         <v>10.4</v>
       </c>
     </row>
@@ -5497,18 +5706,21 @@
         <v>26.7</v>
       </c>
       <c r="R70" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="S70" t="n">
         <v>20.54</v>
       </c>
-      <c r="S70" t="n">
+      <c r="T70" t="n">
         <v>84</v>
       </c>
-      <c r="T70" t="n">
+      <c r="U70" t="n">
         <v>3.04</v>
       </c>
-      <c r="U70" t="n">
+      <c r="V70" t="n">
         <v>4.15</v>
       </c>
-      <c r="V70" t="n">
+      <c r="W70" t="n">
         <v>199.6</v>
       </c>
     </row>
@@ -5569,18 +5781,21 @@
         <v>1555</v>
       </c>
       <c r="R71" t="n">
+        <v>1452.2</v>
+      </c>
+      <c r="S71" t="n">
         <v>109.82</v>
       </c>
-      <c r="S71" t="n">
+      <c r="T71" t="n">
         <v>95</v>
       </c>
-      <c r="T71" t="n">
+      <c r="U71" t="n">
         <v>31.14</v>
       </c>
-      <c r="U71" t="n">
+      <c r="V71" t="n">
         <v>0.29</v>
       </c>
-      <c r="V71" t="n">
+      <c r="W71" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5641,18 +5856,21 @@
         <v>79.3</v>
       </c>
       <c r="R72" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="S72" t="n">
         <v>16.87</v>
       </c>
-      <c r="S72" t="n">
+      <c r="T72" t="n">
         <v>12</v>
       </c>
-      <c r="T72" t="n">
+      <c r="U72" t="n">
         <v>2.02</v>
       </c>
-      <c r="U72" t="n">
+      <c r="V72" t="n">
         <v>5.04</v>
       </c>
-      <c r="V72" t="n">
+      <c r="W72" t="n">
         <v>35.3</v>
       </c>
     </row>
@@ -5713,18 +5931,21 @@
         <v>181</v>
       </c>
       <c r="R73" t="n">
+        <v>910.6</v>
+      </c>
+      <c r="S73" t="n">
         <v>21.99</v>
       </c>
-      <c r="S73" t="n">
+      <c r="T73" t="n">
         <v>66</v>
       </c>
-      <c r="T73" t="n">
+      <c r="U73" t="n">
         <v>4.15</v>
       </c>
-      <c r="U73" t="n">
+      <c r="V73" t="n">
         <v>3.31</v>
       </c>
-      <c r="V73" t="n">
+      <c r="W73" t="n">
         <v>3.6</v>
       </c>
     </row>
@@ -5785,18 +6006,21 @@
         <v>2085</v>
       </c>
       <c r="R74" t="n">
+        <v>1627.8</v>
+      </c>
+      <c r="S74" t="n">
         <v>77.11</v>
       </c>
-      <c r="S74" t="n">
+      <c r="T74" t="n">
         <v>86</v>
       </c>
-      <c r="T74" t="n">
+      <c r="U74" t="n">
         <v>23.04</v>
       </c>
-      <c r="U74" t="n">
+      <c r="V74" t="n">
         <v>0.57</v>
       </c>
-      <c r="V74" t="n">
+      <c r="W74" t="n">
         <v>116</v>
       </c>
     </row>
@@ -5857,18 +6081,21 @@
         <v>2150</v>
       </c>
       <c r="R75" t="n">
+        <v>55847.2</v>
+      </c>
+      <c r="S75" t="n">
         <v>79.31</v>
       </c>
-      <c r="S75" t="n">
+      <c r="T75" t="n">
         <v>97</v>
       </c>
-      <c r="T75" t="n">
+      <c r="U75" t="n">
         <v>18.64</v>
       </c>
-      <c r="U75" t="n">
+      <c r="V75" t="n">
         <v>0.54</v>
       </c>
-      <c r="V75" t="n">
+      <c r="W75" t="n">
         <v>43.7</v>
       </c>
     </row>
@@ -5929,18 +6156,21 @@
         <v>223.5</v>
       </c>
       <c r="R76" t="n">
+        <v>5176.5</v>
+      </c>
+      <c r="S76" t="n">
         <v>32.87</v>
       </c>
-      <c r="S76" t="n">
+      <c r="T76" t="n">
         <v>99</v>
       </c>
-      <c r="T76" t="n">
+      <c r="U76" t="n">
         <v>5.76</v>
       </c>
-      <c r="U76" t="n">
+      <c r="V76" t="n">
         <v>2.24</v>
       </c>
-      <c r="V76" t="n">
+      <c r="W76" t="n">
         <v>29.6</v>
       </c>
     </row>
@@ -6001,18 +6231,21 @@
         <v>889</v>
       </c>
       <c r="R77" t="n">
+        <v>714.3</v>
+      </c>
+      <c r="S77" t="n">
         <v>60.23</v>
       </c>
-      <c r="S77" t="n">
+      <c r="T77" t="n">
         <v>99</v>
       </c>
-      <c r="T77" t="n">
+      <c r="U77" t="n">
         <v>3.08</v>
       </c>
-      <c r="U77" t="n">
+      <c r="V77" t="n">
         <v>2.48</v>
       </c>
-      <c r="V77" t="n">
+      <c r="W77" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -6073,18 +6306,21 @@
         <v>434</v>
       </c>
       <c r="R78" t="n">
+        <v>1413.7</v>
+      </c>
+      <c r="S78" t="n">
         <v>8.43</v>
       </c>
-      <c r="S78" t="n">
+      <c r="T78" t="n">
         <v>22</v>
       </c>
-      <c r="T78" t="n">
+      <c r="U78" t="n">
         <v>5</v>
       </c>
-      <c r="U78" t="n">
+      <c r="V78" t="n">
         <v>3.92</v>
       </c>
-      <c r="V78" t="n">
+      <c r="W78" t="n">
         <v>210.4</v>
       </c>
     </row>
@@ -6145,18 +6381,21 @@
         <v>909</v>
       </c>
       <c r="R79" t="n">
+        <v>5873.6</v>
+      </c>
+      <c r="S79" t="n">
         <v>192.58</v>
       </c>
-      <c r="S79" t="n">
+      <c r="T79" t="n">
         <v>85</v>
       </c>
-      <c r="T79" t="n">
+      <c r="U79" t="n">
         <v>12.58</v>
       </c>
-      <c r="U79" t="n">
+      <c r="V79" t="n">
         <v>0.22</v>
       </c>
-      <c r="V79" t="n">
+      <c r="W79" t="n">
         <v>35.8</v>
       </c>
     </row>
@@ -6217,18 +6456,21 @@
         <v>1005</v>
       </c>
       <c r="R80" t="n">
+        <v>15971.9</v>
+      </c>
+      <c r="S80" t="n">
         <v>142.35</v>
       </c>
-      <c r="S80" t="n">
+      <c r="T80" t="n">
         <v>94</v>
       </c>
-      <c r="T80" t="n">
+      <c r="U80" t="n">
         <v>14.08</v>
       </c>
-      <c r="U80" t="n">
+      <c r="V80" t="n">
         <v>0.2</v>
       </c>
-      <c r="V80" t="n">
+      <c r="W80" t="n">
         <v>32.4</v>
       </c>
     </row>
@@ -6289,18 +6531,21 @@
         <v>122</v>
       </c>
       <c r="R81" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="S81" t="n">
         <v>12.96</v>
       </c>
-      <c r="S81" t="n">
+      <c r="T81" t="n">
         <v>24</v>
       </c>
-      <c r="T81" t="n">
+      <c r="U81" t="n">
         <v>1.55</v>
       </c>
-      <c r="U81" t="n">
+      <c r="V81" t="n">
         <v>4.51</v>
       </c>
-      <c r="V81" t="n">
+      <c r="W81" t="n">
         <v>28.9</v>
       </c>
     </row>
@@ -6361,18 +6606,21 @@
         <v>143</v>
       </c>
       <c r="R82" t="n">
+        <v>451.8</v>
+      </c>
+      <c r="S82" t="n">
         <v>11.64</v>
       </c>
-      <c r="S82" t="n">
+      <c r="T82" t="n">
         <v>99</v>
       </c>
-      <c r="T82" t="n">
+      <c r="U82" t="n">
         <v>2.07</v>
       </c>
-      <c r="U82" t="n">
+      <c r="V82" t="n">
         <v>5.08</v>
       </c>
-      <c r="V82" t="n">
+      <c r="W82" t="n">
         <v>46.6</v>
       </c>
     </row>
@@ -6433,18 +6681,21 @@
         <v>59.1</v>
       </c>
       <c r="R83" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="S83" t="n">
         <v>13.65</v>
       </c>
-      <c r="S83" t="n">
+      <c r="T83" t="n">
         <v>87</v>
       </c>
-      <c r="T83" t="n">
+      <c r="U83" t="n">
         <v>2.05</v>
       </c>
-      <c r="U83" t="n">
+      <c r="V83" t="n">
         <v>5.08</v>
       </c>
-      <c r="V83" t="n">
+      <c r="W83" t="n">
         <v>52.1</v>
       </c>
     </row>
@@ -6505,18 +6756,21 @@
         <v>713</v>
       </c>
       <c r="R84" t="n">
+        <v>1061.8</v>
+      </c>
+      <c r="S84" t="n">
         <v>69.48999999999999</v>
       </c>
-      <c r="S84" t="n">
+      <c r="T84" t="n">
         <v>99</v>
       </c>
-      <c r="T84" t="n">
+      <c r="U84" t="n">
         <v>12.89</v>
       </c>
-      <c r="U84" t="n">
+      <c r="V84" t="n">
         <v>0.7</v>
       </c>
-      <c r="V84" t="n">
+      <c r="W84" t="n">
         <v>17.8</v>
       </c>
     </row>
@@ -6577,18 +6831,21 @@
         <v>1065</v>
       </c>
       <c r="R85" t="n">
+        <v>5519.3</v>
+      </c>
+      <c r="S85" t="n">
         <v>53.17</v>
       </c>
-      <c r="S85" t="n">
+      <c r="T85" t="n">
         <v>100</v>
       </c>
-      <c r="T85" t="n">
+      <c r="U85" t="n">
         <v>13.12</v>
       </c>
-      <c r="U85" t="n">
+      <c r="V85" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="V85" t="n">
+      <c r="W85" t="n">
         <v>47.5</v>
       </c>
     </row>
@@ -6649,18 +6906,21 @@
         <v>566</v>
       </c>
       <c r="R86" t="n">
+        <v>2974.9</v>
+      </c>
+      <c r="S86" t="n">
         <v>27.5</v>
       </c>
-      <c r="S86" t="n">
+      <c r="T86" t="n">
         <v>100</v>
       </c>
-      <c r="T86" t="n">
+      <c r="U86" t="n">
         <v>5.1</v>
       </c>
-      <c r="U86" t="n">
+      <c r="V86" t="n">
         <v>2.24</v>
       </c>
-      <c r="V86" t="n">
+      <c r="W86" t="n">
         <v>46.6</v>
       </c>
     </row>
@@ -6721,18 +6981,21 @@
         <v>101.5</v>
       </c>
       <c r="R87" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="S87" t="n">
         <v>14.95</v>
       </c>
-      <c r="S87" t="n">
+      <c r="T87" t="n">
         <v>50</v>
       </c>
-      <c r="T87" t="n">
+      <c r="U87" t="n">
         <v>3.34</v>
       </c>
-      <c r="U87" t="n">
+      <c r="V87" t="n">
         <v>5.42</v>
       </c>
-      <c r="V87" t="n">
+      <c r="W87" t="n">
         <v>27.4</v>
       </c>
     </row>
@@ -6793,18 +7056,21 @@
         <v>870</v>
       </c>
       <c r="R88" t="n">
+        <v>700.7</v>
+      </c>
+      <c r="S88" t="n">
         <v>100.69</v>
       </c>
-      <c r="S88" t="n">
+      <c r="T88" t="n">
         <v>94</v>
       </c>
-      <c r="T88" t="n">
+      <c r="U88" t="n">
         <v>21.95</v>
       </c>
-      <c r="U88" t="n">
+      <c r="V88" t="n">
         <v>0.4</v>
       </c>
-      <c r="V88" t="n">
+      <c r="W88" t="n">
         <v>30</v>
       </c>
     </row>
@@ -6865,18 +7131,21 @@
         <v>304</v>
       </c>
       <c r="R89" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="S89" t="n">
         <v>40.16</v>
       </c>
-      <c r="S89" t="n">
+      <c r="T89" t="n">
         <v>97</v>
       </c>
-      <c r="T89" t="n">
+      <c r="U89" t="n">
         <v>4.01</v>
       </c>
-      <c r="U89" t="n">
+      <c r="V89" t="n">
         <v>1.48</v>
       </c>
-      <c r="V89" t="n">
+      <c r="W89" t="n">
         <v>26.9</v>
       </c>
     </row>
@@ -6937,18 +7206,21 @@
         <v>774</v>
       </c>
       <c r="R90" t="n">
+        <v>872.6</v>
+      </c>
+      <c r="S90" t="n">
         <v>23.45</v>
       </c>
-      <c r="S90" t="n">
+      <c r="T90" t="n">
         <v>96</v>
       </c>
-      <c r="T90" t="n">
+      <c r="U90" t="n">
         <v>3.34</v>
       </c>
-      <c r="U90" t="n">
+      <c r="V90" t="n">
         <v>2.2</v>
       </c>
-      <c r="V90" t="n">
+      <c r="W90" t="n">
         <v>30.2</v>
       </c>
     </row>
@@ -7009,18 +7281,21 @@
         <v>266</v>
       </c>
       <c r="R91" t="n">
+        <v>159.2</v>
+      </c>
+      <c r="S91" t="n">
         <v>149.44</v>
       </c>
-      <c r="S91" t="n">
+      <c r="T91" t="n">
         <v>99</v>
       </c>
-      <c r="T91" t="n">
+      <c r="U91" t="n">
         <v>6.89</v>
       </c>
-      <c r="U91" t="n">
+      <c r="V91" t="n">
         <v>1.32</v>
       </c>
-      <c r="V91" t="n">
+      <c r="W91" t="n">
         <v>14</v>
       </c>
     </row>
@@ -7081,18 +7356,21 @@
         <v>49.4</v>
       </c>
       <c r="R92" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="S92" t="n">
         <v>12.97</v>
       </c>
-      <c r="S92" t="n">
+      <c r="T92" t="n">
         <v>88</v>
       </c>
-      <c r="T92" t="n">
+      <c r="U92" t="n">
         <v>2.03</v>
       </c>
-      <c r="U92" t="n">
+      <c r="V92" t="n">
         <v>6.28</v>
       </c>
-      <c r="V92" t="n">
+      <c r="W92" t="n">
         <v>17.2</v>
       </c>
     </row>
@@ -7153,18 +7431,21 @@
         <v>674</v>
       </c>
       <c r="R93" t="n">
+        <v>30069.7</v>
+      </c>
+      <c r="S93" t="n">
         <v>62.06</v>
       </c>
-      <c r="S93" t="n">
+      <c r="T93" t="n">
         <v>100</v>
       </c>
-      <c r="T93" t="n">
+      <c r="U93" t="n">
         <v>8.44</v>
       </c>
-      <c r="U93" t="n">
+      <c r="V93" t="n">
         <v>0.98</v>
       </c>
-      <c r="V93" t="n">
+      <c r="W93" t="n">
         <v>28.6</v>
       </c>
     </row>
@@ -7225,18 +7506,21 @@
         <v>89.5</v>
       </c>
       <c r="R94" t="n">
+        <v>212</v>
+      </c>
+      <c r="S94" t="n">
         <v>36.09</v>
       </c>
-      <c r="S94" t="n">
+      <c r="T94" t="n">
         <v>98</v>
       </c>
-      <c r="T94" t="n">
+      <c r="U94" t="n">
         <v>2.58</v>
       </c>
-      <c r="U94" t="n">
+      <c r="V94" t="n">
         <v>2.07</v>
       </c>
-      <c r="V94" t="n">
+      <c r="W94" t="n">
         <v>58.4</v>
       </c>
     </row>
@@ -7297,18 +7581,21 @@
         <v>108</v>
       </c>
       <c r="R95" t="n">
+        <v>3895.6</v>
+      </c>
+      <c r="S95" t="n">
         <v>27.34</v>
       </c>
-      <c r="S95" t="n">
+      <c r="T95" t="n">
         <v>95</v>
       </c>
-      <c r="T95" t="n">
+      <c r="U95" t="n">
         <v>4.06</v>
       </c>
-      <c r="U95" t="n">
+      <c r="V95" t="n">
         <v>3.53</v>
       </c>
-      <c r="V95" t="n">
+      <c r="W95" t="n">
         <v>13.7</v>
       </c>
     </row>
@@ -7369,18 +7656,21 @@
         <v>2580</v>
       </c>
       <c r="R96" t="n">
+        <v>5704</v>
+      </c>
+      <c r="S96" t="n">
         <v>24.52</v>
       </c>
-      <c r="S96" t="n">
+      <c r="T96" t="n">
         <v>73</v>
       </c>
-      <c r="T96" t="n">
+      <c r="U96" t="n">
         <v>7.7</v>
       </c>
-      <c r="U96" t="n">
+      <c r="V96" t="n">
         <v>0.9</v>
       </c>
-      <c r="V96" t="n">
+      <c r="W96" t="n">
         <v>301.2</v>
       </c>
     </row>
@@ -7441,18 +7731,21 @@
         <v>1450</v>
       </c>
       <c r="R97" t="n">
+        <v>1084.3</v>
+      </c>
+      <c r="S97" t="n">
         <v>17.87</v>
       </c>
-      <c r="S97" t="n">
+      <c r="T97" t="n">
         <v>10</v>
       </c>
-      <c r="T97" t="n">
+      <c r="U97" t="n">
         <v>2.91</v>
       </c>
-      <c r="U97" t="n">
+      <c r="V97" t="n">
         <v>3.1</v>
       </c>
-      <c r="V97" t="n">
+      <c r="W97" t="n">
         <v>-19.4</v>
       </c>
     </row>
@@ -7513,18 +7806,21 @@
         <v>259.5</v>
       </c>
       <c r="R98" t="n">
+        <v>3092.8</v>
+      </c>
+      <c r="S98" t="n">
         <v>45.77</v>
       </c>
-      <c r="S98" t="n">
+      <c r="T98" t="n">
         <v>97</v>
       </c>
-      <c r="T98" t="n">
+      <c r="U98" t="n">
         <v>6.6</v>
       </c>
-      <c r="U98" t="n">
+      <c r="V98" t="n">
         <v>1.08</v>
       </c>
-      <c r="V98" t="n">
+      <c r="W98" t="n">
         <v>13</v>
       </c>
     </row>
@@ -7585,18 +7881,21 @@
         <v>58.5</v>
       </c>
       <c r="R99" t="n">
+        <v>385.5</v>
+      </c>
+      <c r="S99" t="n">
         <v>23.31</v>
       </c>
-      <c r="S99" t="n">
+      <c r="T99" t="n">
         <v>66</v>
       </c>
-      <c r="T99" t="n">
+      <c r="U99" t="n">
         <v>3.37</v>
       </c>
-      <c r="U99" t="n">
+      <c r="V99" t="n">
         <v>1.71</v>
       </c>
-      <c r="V99" t="n">
+      <c r="W99" t="n">
         <v>3.7</v>
       </c>
     </row>
@@ -7657,18 +7956,21 @@
         <v>242.5</v>
       </c>
       <c r="R100" t="n">
+        <v>1173.5</v>
+      </c>
+      <c r="S100" t="n">
         <v>36.3</v>
       </c>
-      <c r="S100" t="n">
+      <c r="T100" t="n">
         <v>100</v>
       </c>
-      <c r="T100" t="n">
+      <c r="U100" t="n">
         <v>5.37</v>
       </c>
-      <c r="U100" t="n">
+      <c r="V100" t="n">
         <v>1.73</v>
       </c>
-      <c r="V100" t="n">
+      <c r="W100" t="n">
         <v>23.7</v>
       </c>
     </row>
@@ -7729,18 +8031,21 @@
         <v>173.5</v>
       </c>
       <c r="R101" t="n">
+        <v>649.9</v>
+      </c>
+      <c r="S101" t="n">
         <v>26.49</v>
       </c>
-      <c r="S101" t="n">
+      <c r="T101" t="n">
         <v>80</v>
       </c>
-      <c r="T101" t="n">
+      <c r="U101" t="n">
         <v>5.13</v>
       </c>
-      <c r="U101" t="n">
+      <c r="V101" t="n">
         <v>2.88</v>
       </c>
-      <c r="V101" t="n">
+      <c r="W101" t="n">
         <v>10.6</v>
       </c>
     </row>
@@ -7801,18 +8106,21 @@
         <v>2000</v>
       </c>
       <c r="R102" t="n">
+        <v>3901.6</v>
+      </c>
+      <c r="S102" t="n">
         <v>40.17</v>
       </c>
-      <c r="S102" t="n">
+      <c r="T102" t="n">
         <v>94</v>
       </c>
-      <c r="T102" t="n">
+      <c r="U102" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="U102" t="n">
+      <c r="V102" t="n">
         <v>0.75</v>
       </c>
-      <c r="V102" t="n">
+      <c r="W102" t="n">
         <v>41.3</v>
       </c>
     </row>
@@ -7873,18 +8181,21 @@
         <v>56</v>
       </c>
       <c r="R103" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="S103" t="n">
         <v>11.76</v>
       </c>
-      <c r="S103" t="n">
+      <c r="T103" t="n">
         <v>23</v>
       </c>
-      <c r="T103" t="n">
+      <c r="U103" t="n">
         <v>1.82</v>
       </c>
-      <c r="U103" t="n">
+      <c r="V103" t="n">
         <v>5.89</v>
       </c>
-      <c r="V103" t="n">
+      <c r="W103" t="n">
         <v>9.199999999999999</v>
       </c>
     </row>
@@ -7945,18 +8256,21 @@
         <v>62</v>
       </c>
       <c r="R104" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="S104" t="n">
         <v>14.06</v>
       </c>
-      <c r="S104" t="n">
+      <c r="T104" t="n">
         <v>2</v>
       </c>
-      <c r="T104" t="n">
+      <c r="U104" t="n">
         <v>2.28</v>
       </c>
-      <c r="U104" t="n">
+      <c r="V104" t="n">
         <v>3.31</v>
       </c>
-      <c r="V104" t="n">
+      <c r="W104" t="n">
         <v>31.8</v>
       </c>
     </row>
@@ -8017,18 +8331,21 @@
         <v>309.5</v>
       </c>
       <c r="R105" t="n">
+        <v>1333</v>
+      </c>
+      <c r="S105" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="S105" t="n">
+      <c r="T105" t="n">
         <v>11</v>
       </c>
-      <c r="T105" t="n">
+      <c r="U105" t="n">
         <v>5.09</v>
       </c>
-      <c r="U105" t="n">
+      <c r="V105" t="n">
         <v>3.81</v>
       </c>
-      <c r="V105" t="n">
+      <c r="W105" t="n">
         <v>469.8</v>
       </c>
     </row>
@@ -8089,18 +8406,21 @@
         <v>366</v>
       </c>
       <c r="R106" t="n">
+        <v>2778.5</v>
+      </c>
+      <c r="S106" t="n">
         <v>43.57</v>
       </c>
-      <c r="S106" t="n">
+      <c r="T106" t="n">
         <v>100</v>
       </c>
-      <c r="T106" t="n">
+      <c r="U106" t="n">
         <v>4.63</v>
       </c>
-      <c r="U106" t="n">
+      <c r="V106" t="n">
         <v>1.23</v>
       </c>
-      <c r="V106" t="n">
+      <c r="W106" t="n">
         <v>30.2</v>
       </c>
     </row>
@@ -8161,18 +8481,21 @@
         <v>127</v>
       </c>
       <c r="R107" t="n">
+        <v>346.8</v>
+      </c>
+      <c r="S107" t="n">
         <v>36.92</v>
       </c>
-      <c r="S107" t="n">
+      <c r="T107" t="n">
         <v>80</v>
       </c>
-      <c r="T107" t="n">
+      <c r="U107" t="n">
         <v>5.26</v>
       </c>
-      <c r="U107" t="n">
+      <c r="V107" t="n">
         <v>1.73</v>
       </c>
-      <c r="V107" t="n">
+      <c r="W107" t="n">
         <v>-30.8</v>
       </c>
     </row>
@@ -8233,18 +8556,21 @@
         <v>33.7</v>
       </c>
       <c r="R108" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="S108" t="n">
         <v>27.62</v>
       </c>
-      <c r="S108" t="n">
+      <c r="T108" t="n">
         <v>86</v>
       </c>
-      <c r="T108" t="n">
+      <c r="U108" t="n">
         <v>1.22</v>
       </c>
-      <c r="U108" t="n">
+      <c r="V108" t="n">
         <v>4.45</v>
       </c>
-      <c r="V108" t="n">
+      <c r="W108" t="n">
         <v>18.6</v>
       </c>
     </row>
@@ -8305,18 +8631,21 @@
         <v>1900</v>
       </c>
       <c r="R109" t="n">
+        <v>5487.5</v>
+      </c>
+      <c r="S109" t="n">
         <v>135.14</v>
       </c>
-      <c r="S109" t="n">
+      <c r="T109" t="n">
         <v>100</v>
       </c>
-      <c r="T109" t="n">
+      <c r="U109" t="n">
         <v>30.38</v>
       </c>
-      <c r="U109" t="n">
+      <c r="V109" t="n">
         <v>0.4</v>
       </c>
-      <c r="V109" t="n">
+      <c r="W109" t="n">
         <v>124.4</v>
       </c>
     </row>
@@ -8377,18 +8706,21 @@
         <v>91.7</v>
       </c>
       <c r="R110" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="S110" t="n">
         <v>22.26</v>
       </c>
-      <c r="S110" t="n">
+      <c r="T110" t="n">
         <v>94</v>
       </c>
-      <c r="T110" t="n">
+      <c r="U110" t="n">
         <v>2.18</v>
       </c>
-      <c r="U110" t="n">
+      <c r="V110" t="n">
         <v>2.94</v>
       </c>
-      <c r="V110" t="n">
+      <c r="W110" t="n">
         <v>18.6</v>
       </c>
     </row>
@@ -8449,18 +8781,21 @@
         <v>293</v>
       </c>
       <c r="R111" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="S111" t="n">
         <v>38.15</v>
       </c>
-      <c r="S111" t="n">
+      <c r="T111" t="n">
         <v>97</v>
       </c>
-      <c r="T111" t="n">
+      <c r="U111" t="n">
         <v>5.71</v>
       </c>
-      <c r="U111" t="n">
+      <c r="V111" t="n">
         <v>1.57</v>
       </c>
-      <c r="V111" t="n">
+      <c r="W111" t="n">
         <v>16.6</v>
       </c>
     </row>
@@ -8521,18 +8856,21 @@
         <v>283</v>
       </c>
       <c r="R112" t="n">
+        <v>417.9</v>
+      </c>
+      <c r="S112" t="n">
         <v>58.47</v>
       </c>
-      <c r="S112" t="n">
+      <c r="T112" t="n">
         <v>41</v>
       </c>
-      <c r="T112" t="n">
+      <c r="U112" t="n">
         <v>12.02</v>
       </c>
-      <c r="U112" t="n">
+      <c r="V112" t="n">
         <v>1.06</v>
       </c>
-      <c r="V112" t="n">
+      <c r="W112" t="n">
         <v>241.2</v>
       </c>
     </row>
@@ -8593,18 +8931,21 @@
         <v>215.5</v>
       </c>
       <c r="R113" t="n">
+        <v>276.1</v>
+      </c>
+      <c r="S113" t="n">
         <v>10.5</v>
       </c>
-      <c r="S113" t="n">
+      <c r="T113" t="n">
         <v>28</v>
       </c>
-      <c r="T113" t="n">
+      <c r="U113" t="n">
         <v>4.37</v>
       </c>
-      <c r="U113" t="n">
+      <c r="V113" t="n">
         <v>2.09</v>
       </c>
-      <c r="V113" t="n">
+      <c r="W113" t="n">
         <v>224.4</v>
       </c>
     </row>
@@ -8665,18 +9006,21 @@
         <v>93.8</v>
       </c>
       <c r="R114" t="n">
+        <v>254</v>
+      </c>
+      <c r="S114" t="n">
         <v>11.25</v>
       </c>
-      <c r="S114" t="n">
+      <c r="T114" t="n">
         <v>66</v>
       </c>
-      <c r="T114" t="n">
+      <c r="U114" t="n">
         <v>2.46</v>
       </c>
-      <c r="U114" t="n">
+      <c r="V114" t="n">
         <v>4.9</v>
       </c>
-      <c r="V114" t="n">
+      <c r="W114" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -8737,18 +9081,21 @@
         <v>56.6</v>
       </c>
       <c r="R115" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="S115" t="n">
         <v>18.03</v>
       </c>
-      <c r="S115" t="n">
+      <c r="T115" t="n">
         <v>50</v>
       </c>
-      <c r="T115" t="n">
+      <c r="U115" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="U115" t="n">
+      <c r="V115" t="n">
         <v>3.61</v>
       </c>
-      <c r="V115" t="n">
+      <c r="W115" t="n">
         <v>6.8</v>
       </c>
     </row>
@@ -8809,18 +9156,21 @@
         <v>5185</v>
       </c>
       <c r="R116" t="n">
+        <v>6920.3</v>
+      </c>
+      <c r="S116" t="n">
         <v>32.87</v>
       </c>
-      <c r="S116" t="n">
+      <c r="T116" t="n">
         <v>100</v>
       </c>
-      <c r="T116" t="n">
+      <c r="U116" t="n">
         <v>3.67</v>
       </c>
-      <c r="U116" t="n">
+      <c r="V116" t="n">
         <v>1.54</v>
       </c>
-      <c r="V116" t="n">
+      <c r="W116" t="n">
         <v>41.8</v>
       </c>
     </row>
@@ -8881,18 +9231,21 @@
         <v>213</v>
       </c>
       <c r="R117" t="n">
+        <v>74</v>
+      </c>
+      <c r="S117" t="n">
         <v>27.17</v>
       </c>
-      <c r="S117" t="n">
+      <c r="T117" t="n">
         <v>96</v>
       </c>
-      <c r="T117" t="n">
+      <c r="U117" t="n">
         <v>3.82</v>
       </c>
-      <c r="U117" t="n">
+      <c r="V117" t="n">
         <v>3.29</v>
       </c>
-      <c r="V117" t="n">
+      <c r="W117" t="n">
         <v>-5.3</v>
       </c>
     </row>
@@ -8953,18 +9306,21 @@
         <v>170</v>
       </c>
       <c r="R118" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="S118" t="n">
         <v>14.66</v>
       </c>
-      <c r="S118" t="n">
+      <c r="T118" t="n">
         <v>5</v>
       </c>
-      <c r="T118" t="n">
+      <c r="U118" t="n">
         <v>2.81</v>
       </c>
-      <c r="U118" t="n">
+      <c r="V118" t="n">
         <v>4.71</v>
       </c>
-      <c r="V118" t="n">
+      <c r="W118" t="n">
         <v>10.9</v>
       </c>
     </row>
@@ -9025,18 +9381,21 @@
         <v>193.5</v>
       </c>
       <c r="R119" t="n">
+        <v>263.7</v>
+      </c>
+      <c r="S119" t="n">
         <v>33.95</v>
       </c>
-      <c r="S119" t="n">
+      <c r="T119" t="n">
         <v>100</v>
       </c>
-      <c r="T119" t="n">
+      <c r="U119" t="n">
         <v>4.37</v>
       </c>
-      <c r="U119" t="n">
+      <c r="V119" t="n">
         <v>2.12</v>
       </c>
-      <c r="V119" t="n">
+      <c r="W119" t="n">
         <v>22.1</v>
       </c>
     </row>
@@ -9097,18 +9456,21 @@
         <v>43.8</v>
       </c>
       <c r="R120" t="n">
+        <v>393.9</v>
+      </c>
+      <c r="S120" t="n">
         <v>10.15</v>
       </c>
-      <c r="S120" t="n">
+      <c r="T120" t="n">
         <v>2</v>
       </c>
-      <c r="T120" t="n">
+      <c r="U120" t="n">
         <v>1.89</v>
       </c>
-      <c r="U120" t="n">
+      <c r="V120" t="n">
         <v>2.29</v>
       </c>
-      <c r="V120" t="n">
+      <c r="W120" t="n">
         <v>-2.6</v>
       </c>
     </row>
@@ -9169,18 +9531,21 @@
         <v>433</v>
       </c>
       <c r="R121" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="S121" t="n">
         <v>54.47</v>
       </c>
-      <c r="S121" t="n">
+      <c r="T121" t="n">
         <v>100</v>
       </c>
-      <c r="T121" t="n">
+      <c r="U121" t="n">
         <v>2.76</v>
       </c>
-      <c r="U121" t="n">
+      <c r="V121" t="n">
         <v>3.5</v>
       </c>
-      <c r="V121" t="n">
+      <c r="W121" t="n">
         <v>12.3</v>
       </c>
     </row>
@@ -9241,18 +9606,21 @@
         <v>552</v>
       </c>
       <c r="R122" t="n">
+        <v>785.8</v>
+      </c>
+      <c r="S122" t="n">
         <v>99.81999999999999</v>
       </c>
-      <c r="S122" t="n">
+      <c r="T122" t="n">
         <v>96</v>
       </c>
-      <c r="T122" t="n">
+      <c r="U122" t="n">
         <v>19.01</v>
       </c>
-      <c r="U122" t="n">
+      <c r="V122" t="n">
         <v>0.39</v>
       </c>
-      <c r="V122" t="n">
+      <c r="W122" t="n">
         <v>21.1</v>
       </c>
     </row>
@@ -9313,18 +9681,21 @@
         <v>788</v>
       </c>
       <c r="R123" t="n">
+        <v>5853</v>
+      </c>
+      <c r="S123" t="n">
         <v>14.08</v>
       </c>
-      <c r="S123" t="n">
+      <c r="T123" t="n">
         <v>70</v>
       </c>
-      <c r="T123" t="n">
+      <c r="U123" t="n">
         <v>2.04</v>
       </c>
-      <c r="U123" t="n">
+      <c r="V123" t="n">
         <v>5.33</v>
       </c>
-      <c r="V123" t="n">
+      <c r="W123" t="n">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -9385,18 +9756,21 @@
         <v>112.5</v>
       </c>
       <c r="R124" t="n">
+        <v>1889</v>
+      </c>
+      <c r="S124" t="n">
         <v>14.17</v>
       </c>
-      <c r="S124" t="n">
+      <c r="T124" t="n">
         <v>62</v>
       </c>
-      <c r="T124" t="n">
+      <c r="U124" t="n">
         <v>2.1</v>
       </c>
-      <c r="U124" t="n">
+      <c r="V124" t="n">
         <v>3.38</v>
       </c>
-      <c r="V124" t="n">
+      <c r="W124" t="n">
         <v>82.90000000000001</v>
       </c>
     </row>
@@ -9457,18 +9831,21 @@
         <v>194.5</v>
       </c>
       <c r="R125" t="n">
+        <v>551.6</v>
+      </c>
+      <c r="S125" t="n">
         <v>194.5</v>
       </c>
-      <c r="S125" t="n">
+      <c r="T125" t="n">
         <v>100</v>
       </c>
-      <c r="T125" t="n">
+      <c r="U125" t="n">
         <v>5.13</v>
       </c>
-      <c r="U125" t="n">
+      <c r="V125" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="V125" t="n">
+      <c r="W125" t="n">
         <v>69.09999999999999</v>
       </c>
     </row>
@@ -9529,18 +9906,21 @@
         <v>78</v>
       </c>
       <c r="R126" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S126" t="n">
         <v>17.61</v>
       </c>
-      <c r="S126" t="n">
+      <c r="T126" t="n">
         <v>11</v>
       </c>
-      <c r="T126" t="n">
+      <c r="U126" t="n">
         <v>1.51</v>
       </c>
-      <c r="U126" t="n">
+      <c r="V126" t="n">
         <v>2.57</v>
       </c>
-      <c r="V126" t="n">
+      <c r="W126" t="n">
         <v>15.5</v>
       </c>
     </row>
@@ -9601,18 +9981,21 @@
         <v>97.59999999999999</v>
       </c>
       <c r="R127" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="S127" t="n">
         <v>16.57</v>
       </c>
-      <c r="S127" t="n">
+      <c r="T127" t="n">
         <v>84</v>
       </c>
-      <c r="T127" t="n">
+      <c r="U127" t="n">
         <v>1.51</v>
       </c>
-      <c r="U127" t="n">
+      <c r="V127" t="n">
         <v>6.66</v>
       </c>
-      <c r="V127" t="n">
+      <c r="W127" t="n">
         <v>17.4</v>
       </c>
     </row>
@@ -9673,18 +10056,21 @@
         <v>557</v>
       </c>
       <c r="R128" t="n">
+        <v>811.4</v>
+      </c>
+      <c r="S128" t="n">
         <v>165.77</v>
       </c>
-      <c r="S128" t="n">
+      <c r="T128" t="n">
         <v>82</v>
       </c>
-      <c r="T128" t="n">
+      <c r="U128" t="n">
         <v>15.56</v>
       </c>
-      <c r="U128" t="n">
+      <c r="V128" t="n">
         <v>0.18</v>
       </c>
-      <c r="V128" t="n">
+      <c r="W128" t="n">
         <v>49.9</v>
       </c>
     </row>
@@ -9745,18 +10131,21 @@
         <v>897</v>
       </c>
       <c r="R129" t="n">
+        <v>1488</v>
+      </c>
+      <c r="S129" t="n">
         <v>115.59</v>
       </c>
-      <c r="S129" t="n">
+      <c r="T129" t="n">
         <v>100</v>
       </c>
-      <c r="T129" t="n">
+      <c r="U129" t="n">
         <v>15.36</v>
       </c>
-      <c r="U129" t="n">
+      <c r="V129" t="n">
         <v>0.65</v>
       </c>
-      <c r="V129" t="n">
+      <c r="W129" t="n">
         <v>21.3</v>
       </c>
     </row>
@@ -9817,18 +10206,21 @@
         <v>225</v>
       </c>
       <c r="R130" t="n">
+        <v>2855.6</v>
+      </c>
+      <c r="S130" t="n">
         <v>15.52</v>
       </c>
-      <c r="S130" t="n">
+      <c r="T130" t="n">
         <v>68</v>
       </c>
-      <c r="T130" t="n">
+      <c r="U130" t="n">
         <v>2.53</v>
       </c>
-      <c r="U130" t="n">
+      <c r="V130" t="n">
         <v>3.47</v>
       </c>
-      <c r="V130" t="n">
+      <c r="W130" t="n">
         <v>152.7</v>
       </c>
     </row>
@@ -9889,18 +10281,21 @@
         <v>179</v>
       </c>
       <c r="R131" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="S131" t="n">
         <v>16.85</v>
       </c>
-      <c r="S131" t="n">
+      <c r="T131" t="n">
         <v>15</v>
       </c>
-      <c r="T131" t="n">
+      <c r="U131" t="n">
         <v>1.83</v>
       </c>
-      <c r="U131" t="n">
+      <c r="V131" t="n">
         <v>5.03</v>
       </c>
-      <c r="V131" t="n">
+      <c r="W131" t="n">
         <v>10</v>
       </c>
     </row>
@@ -9961,18 +10356,21 @@
         <v>212.5</v>
       </c>
       <c r="R132" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="S132" t="n">
         <v>24.45</v>
       </c>
-      <c r="S132" t="n">
+      <c r="T132" t="n">
         <v>95</v>
       </c>
-      <c r="T132" t="n">
+      <c r="U132" t="n">
         <v>2.57</v>
       </c>
-      <c r="U132" t="n">
+      <c r="V132" t="n">
         <v>2.26</v>
       </c>
-      <c r="V132" t="n">
+      <c r="W132" t="n">
         <v>21.5</v>
       </c>
     </row>
@@ -10033,18 +10431,21 @@
         <v>163</v>
       </c>
       <c r="R133" t="n">
+        <v>455.2</v>
+      </c>
+      <c r="S133" t="n">
         <v>23.76</v>
       </c>
-      <c r="S133" t="n">
+      <c r="T133" t="n">
         <v>72</v>
       </c>
-      <c r="T133" t="n">
+      <c r="U133" t="n">
         <v>3.19</v>
       </c>
-      <c r="U133" t="n">
+      <c r="V133" t="n">
         <v>2.82</v>
       </c>
-      <c r="V133" t="n">
+      <c r="W133" t="n">
         <v>16.2</v>
       </c>
     </row>
@@ -10105,18 +10506,21 @@
         <v>52.2</v>
       </c>
       <c r="R134" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="S134" t="n">
         <v>16.11</v>
       </c>
-      <c r="S134" t="n">
+      <c r="T134" t="n">
         <v>33</v>
       </c>
-      <c r="T134" t="n">
+      <c r="U134" t="n">
         <v>1.69</v>
       </c>
-      <c r="U134" t="n">
+      <c r="V134" t="n">
         <v>3.45</v>
       </c>
-      <c r="V134" t="n">
+      <c r="W134" t="n">
         <v>39</v>
       </c>
     </row>
@@ -10171,18 +10575,21 @@
         <v>39.8</v>
       </c>
       <c r="R135" t="n">
+        <v>864</v>
+      </c>
+      <c r="S135" t="n">
         <v>11.12</v>
       </c>
-      <c r="S135" t="n">
+      <c r="T135" t="n">
         <v>61</v>
       </c>
-      <c r="T135" t="n">
+      <c r="U135" t="n">
         <v>1.8</v>
       </c>
-      <c r="U135" t="n">
+      <c r="V135" t="n">
         <v>4.3</v>
       </c>
-      <c r="V135" t="n">
+      <c r="W135" t="n">
         <v>155.5</v>
       </c>
     </row>
@@ -10243,18 +10650,21 @@
         <v>630</v>
       </c>
       <c r="R136" t="n">
+        <v>505.1</v>
+      </c>
+      <c r="S136" t="n">
         <v>55.26</v>
       </c>
-      <c r="S136" t="n">
+      <c r="T136" t="n">
         <v>72</v>
       </c>
-      <c r="T136" t="n">
+      <c r="U136" t="n">
         <v>5.22</v>
       </c>
-      <c r="U136" t="n">
+      <c r="V136" t="n">
         <v>1.59</v>
       </c>
-      <c r="V136" t="n">
+      <c r="W136" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -10315,18 +10725,21 @@
         <v>39.3</v>
       </c>
       <c r="R137" t="n">
+        <v>314.6</v>
+      </c>
+      <c r="S137" t="n">
         <v>10.74</v>
       </c>
-      <c r="S137" t="n">
+      <c r="T137" t="n">
         <v>66</v>
       </c>
-      <c r="T137" t="n">
+      <c r="U137" t="n">
         <v>1.33</v>
       </c>
-      <c r="U137" t="n">
+      <c r="V137" t="n">
         <v>5.64</v>
       </c>
-      <c r="V137" t="n">
+      <c r="W137" t="n">
         <v>170.2</v>
       </c>
     </row>
@@ -10387,18 +10800,21 @@
         <v>119.5</v>
       </c>
       <c r="R138" t="n">
+        <v>362.6</v>
+      </c>
+      <c r="S138" t="n">
         <v>14.5</v>
       </c>
-      <c r="S138" t="n">
+      <c r="T138" t="n">
         <v>6</v>
       </c>
-      <c r="T138" t="n">
+      <c r="U138" t="n">
         <v>1.38</v>
       </c>
-      <c r="U138" t="n">
+      <c r="V138" t="n">
         <v>3.19</v>
       </c>
-      <c r="V138" t="n">
+      <c r="W138" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10459,18 +10875,21 @@
         <v>191</v>
       </c>
       <c r="R139" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="S139" t="n">
         <v>41.43</v>
       </c>
-      <c r="S139" t="n">
+      <c r="T139" t="n">
         <v>77</v>
       </c>
-      <c r="T139" t="n">
+      <c r="U139" t="n">
         <v>3.94</v>
       </c>
-      <c r="U139" t="n">
+      <c r="V139" t="n">
         <v>1.18</v>
       </c>
-      <c r="V139" t="n">
+      <c r="W139" t="n">
         <v>-11.2</v>
       </c>
     </row>
@@ -10531,18 +10950,21 @@
         <v>587</v>
       </c>
       <c r="R140" t="n">
+        <v>6284.4</v>
+      </c>
+      <c r="S140" t="n">
         <v>77.84999999999999</v>
       </c>
-      <c r="S140" t="n">
+      <c r="T140" t="n">
         <v>100</v>
       </c>
-      <c r="T140" t="n">
+      <c r="U140" t="n">
         <v>5</v>
       </c>
-      <c r="U140" t="n">
+      <c r="V140" t="n">
         <v>0.58</v>
       </c>
-      <c r="V140" t="n">
+      <c r="W140" t="n">
         <v>37.4</v>
       </c>
     </row>
@@ -10603,18 +11025,21 @@
         <v>114</v>
       </c>
       <c r="R141" t="n">
+        <v>803.2</v>
+      </c>
+      <c r="S141" t="n">
         <v>96.61</v>
       </c>
-      <c r="S141" t="n">
+      <c r="T141" t="n">
         <v>87</v>
       </c>
-      <c r="T141" t="n">
+      <c r="U141" t="n">
         <v>3.24</v>
       </c>
-      <c r="U141" t="n">
+      <c r="V141" t="n">
         <v>1.08</v>
       </c>
-      <c r="V141" t="n">
+      <c r="W141" t="n">
         <v>17.7</v>
       </c>
     </row>
@@ -10675,18 +11100,21 @@
         <v>144.5</v>
       </c>
       <c r="R142" t="n">
+        <v>11209.5</v>
+      </c>
+      <c r="S142" t="n">
         <v>28.73</v>
       </c>
-      <c r="S142" t="n">
+      <c r="T142" t="n">
         <v>100</v>
       </c>
-      <c r="T142" t="n">
+      <c r="U142" t="n">
         <v>2.83</v>
       </c>
-      <c r="U142" t="n">
+      <c r="V142" t="n">
         <v>3.6</v>
       </c>
-      <c r="V142" t="n">
+      <c r="W142" t="n">
         <v>5.4</v>
       </c>
     </row>
@@ -10747,18 +11175,21 @@
         <v>139</v>
       </c>
       <c r="R143" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="S143" t="n">
         <v>14.85</v>
       </c>
-      <c r="S143" t="n">
+      <c r="T143" t="n">
         <v>1</v>
       </c>
-      <c r="T143" t="n">
+      <c r="U143" t="n">
         <v>4.06</v>
       </c>
-      <c r="U143" t="n">
+      <c r="V143" t="n">
         <v>5.24</v>
       </c>
-      <c r="V143" t="n">
+      <c r="W143" t="n">
         <v>20.1</v>
       </c>
     </row>
@@ -10813,18 +11244,21 @@
         <v>52</v>
       </c>
       <c r="R144" t="n">
+        <v>832.7</v>
+      </c>
+      <c r="S144" t="n">
         <v>17.33</v>
       </c>
-      <c r="S144" t="n">
+      <c r="T144" t="n">
         <v>82</v>
       </c>
-      <c r="T144" t="n">
+      <c r="U144" t="n">
         <v>2</v>
       </c>
-      <c r="U144" t="n">
+      <c r="V144" t="n">
         <v>4.04</v>
       </c>
-      <c r="V144" t="n">
+      <c r="W144" t="n">
         <v>428.4</v>
       </c>
     </row>
@@ -10885,18 +11319,21 @@
         <v>37.8</v>
       </c>
       <c r="R145" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="S145" t="n">
         <v>24.71</v>
       </c>
-      <c r="S145" t="n">
+      <c r="T145" t="n">
         <v>69</v>
       </c>
-      <c r="T145" t="n">
+      <c r="U145" t="n">
         <v>1.61</v>
       </c>
-      <c r="U145" t="n">
+      <c r="V145" t="n">
         <v>5.29</v>
       </c>
-      <c r="V145" t="n">
+      <c r="W145" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -10957,18 +11394,21 @@
         <v>462</v>
       </c>
       <c r="R146" t="n">
+        <v>219.4</v>
+      </c>
+      <c r="S146" t="n">
         <v>1184.62</v>
       </c>
-      <c r="S146" t="n">
+      <c r="T146" t="n">
         <v>97</v>
       </c>
-      <c r="T146" t="n">
+      <c r="U146" t="n">
         <v>12.21</v>
       </c>
-      <c r="U146" t="n">
+      <c r="V146" t="n">
         <v>0.26</v>
       </c>
-      <c r="V146" t="n">
+      <c r="W146" t="n">
         <v>64.2</v>
       </c>
     </row>
@@ -11029,18 +11469,21 @@
         <v>43</v>
       </c>
       <c r="R147" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="S147" t="n">
         <v>25.32</v>
       </c>
-      <c r="S147" t="n">
+      <c r="T147" t="n">
         <v>67</v>
       </c>
-      <c r="T147" t="n">
+      <c r="U147" t="n">
         <v>2.43</v>
       </c>
-      <c r="U147" t="n">
+      <c r="V147" t="n">
         <v>3.48</v>
       </c>
-      <c r="V147" t="n">
+      <c r="W147" t="n">
         <v>11.2</v>
       </c>
     </row>
@@ -11101,18 +11544,21 @@
         <v>796</v>
       </c>
       <c r="R148" t="n">
+        <v>4194.2</v>
+      </c>
+      <c r="S148" t="n">
         <v>195.58</v>
       </c>
-      <c r="S148" t="n">
+      <c r="T148" t="n">
         <v>84</v>
       </c>
-      <c r="T148" t="n">
+      <c r="U148" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="U148" t="n">
+      <c r="V148" t="n">
         <v>0.22</v>
       </c>
-      <c r="V148" t="n">
+      <c r="W148" t="n">
         <v>33</v>
       </c>
     </row>
@@ -11173,18 +11619,21 @@
         <v>79.09999999999999</v>
       </c>
       <c r="R149" t="n">
+        <v>17</v>
+      </c>
+      <c r="S149" t="n">
         <v>26.63</v>
       </c>
-      <c r="S149" t="n">
+      <c r="T149" t="n">
         <v>64</v>
       </c>
-      <c r="T149" t="n">
+      <c r="U149" t="n">
         <v>2.14</v>
       </c>
-      <c r="U149" t="n">
+      <c r="V149" t="n">
         <v>3.92</v>
       </c>
-      <c r="V149" t="n">
+      <c r="W149" t="n">
         <v>10.9</v>
       </c>
     </row>
@@ -11245,18 +11694,21 @@
         <v>90.90000000000001</v>
       </c>
       <c r="R150" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="S150" t="n">
         <v>19.1</v>
       </c>
-      <c r="S150" t="n">
+      <c r="T150" t="n">
         <v>21</v>
       </c>
-      <c r="T150" t="n">
+      <c r="U150" t="n">
         <v>2.08</v>
       </c>
-      <c r="U150" t="n">
+      <c r="V150" t="n">
         <v>4.95</v>
       </c>
-      <c r="V150" t="n">
+      <c r="W150" t="n">
         <v>19.5</v>
       </c>
     </row>
@@ -11317,18 +11769,21 @@
         <v>34</v>
       </c>
       <c r="R151" t="n">
+        <v>1036.3</v>
+      </c>
+      <c r="S151" t="n">
         <v>25.76</v>
       </c>
-      <c r="S151" t="n">
+      <c r="T151" t="n">
         <v>78</v>
       </c>
-      <c r="T151" t="n">
+      <c r="U151" t="n">
         <v>1.4</v>
       </c>
-      <c r="U151" t="n">
+      <c r="V151" t="n">
         <v>3.82</v>
       </c>
-      <c r="V151" t="n">
+      <c r="W151" t="n">
         <v>36.5</v>
       </c>
     </row>
@@ -11389,18 +11844,21 @@
         <v>35.1</v>
       </c>
       <c r="R152" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="S152" t="n">
         <v>14.75</v>
       </c>
-      <c r="S152" t="n">
+      <c r="T152" t="n">
         <v>26</v>
       </c>
-      <c r="T152" t="n">
+      <c r="U152" t="n">
         <v>1.22</v>
       </c>
-      <c r="U152" t="n">
+      <c r="V152" t="n">
         <v>5.13</v>
       </c>
-      <c r="V152" t="n">
+      <c r="W152" t="n">
         <v>13.2</v>
       </c>
     </row>
@@ -11461,18 +11919,21 @@
         <v>284.5</v>
       </c>
       <c r="R153" t="n">
+        <v>241.7</v>
+      </c>
+      <c r="S153" t="n">
         <v>7.28</v>
       </c>
-      <c r="S153" t="n">
+      <c r="T153" t="n">
         <v>4</v>
       </c>
-      <c r="T153" t="n">
+      <c r="U153" t="n">
         <v>3.41</v>
       </c>
-      <c r="U153" t="n">
+      <c r="V153" t="n">
         <v>3.51</v>
       </c>
-      <c r="V153" t="n">
+      <c r="W153" t="n">
         <v>112.6</v>
       </c>
     </row>
@@ -11533,18 +11994,21 @@
         <v>79</v>
       </c>
       <c r="R154" t="n">
+        <v>576.9</v>
+      </c>
+      <c r="S154" t="n">
         <v>19.36</v>
       </c>
-      <c r="S154" t="n">
+      <c r="T154" t="n">
         <v>26</v>
       </c>
-      <c r="T154" t="n">
+      <c r="U154" t="n">
         <v>3.31</v>
       </c>
-      <c r="U154" t="n">
+      <c r="V154" t="n">
         <v>3.05</v>
       </c>
-      <c r="V154" t="n">
+      <c r="W154" t="n">
         <v>768.2</v>
       </c>
     </row>
@@ -11605,18 +12069,21 @@
         <v>95.40000000000001</v>
       </c>
       <c r="R155" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="S155" t="n">
         <v>87.52</v>
       </c>
-      <c r="S155" t="n">
+      <c r="T155" t="n">
         <v>97</v>
       </c>
-      <c r="T155" t="n">
+      <c r="U155" t="n">
         <v>1.16</v>
       </c>
-      <c r="U155" t="n">
+      <c r="V155" t="n">
         <v>1.57</v>
       </c>
-      <c r="V155" t="n">
+      <c r="W155" t="n">
         <v>73.8</v>
       </c>
     </row>
@@ -11677,18 +12144,21 @@
         <v>50.1</v>
       </c>
       <c r="R156" t="n">
+        <v>471.9</v>
+      </c>
+      <c r="S156" t="n">
         <v>61.85</v>
       </c>
-      <c r="S156" t="n">
+      <c r="T156" t="n">
         <v>77</v>
       </c>
-      <c r="T156" t="n">
+      <c r="U156" t="n">
         <v>2.6</v>
       </c>
-      <c r="U156" t="n">
+      <c r="V156" t="n">
         <v>1.56</v>
       </c>
-      <c r="V156" t="n">
+      <c r="W156" t="n">
         <v>18.9</v>
       </c>
     </row>
@@ -11749,18 +12219,21 @@
         <v>165.5</v>
       </c>
       <c r="R157" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="S157" t="n">
         <v>70.13</v>
       </c>
-      <c r="S157" t="n">
+      <c r="T157" t="n">
         <v>79</v>
       </c>
-      <c r="T157" t="n">
+      <c r="U157" t="n">
         <v>7.07</v>
       </c>
-      <c r="U157" t="n">
+      <c r="V157" t="n">
         <v>0.59</v>
       </c>
-      <c r="V157" t="n">
+      <c r="W157" t="n">
         <v>-17.5</v>
       </c>
     </row>
@@ -11821,18 +12294,21 @@
         <v>45.4</v>
       </c>
       <c r="R158" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="S158" t="n">
         <v>26.86</v>
       </c>
-      <c r="S158" t="n">
+      <c r="T158" t="n">
         <v>76</v>
       </c>
-      <c r="T158" t="n">
+      <c r="U158" t="n">
         <v>2.13</v>
       </c>
-      <c r="U158" t="n">
+      <c r="V158" t="n">
         <v>3.63</v>
       </c>
-      <c r="V158" t="n">
+      <c r="W158" t="n">
         <v>13.8</v>
       </c>
     </row>
@@ -11893,18 +12369,21 @@
         <v>113.5</v>
       </c>
       <c r="R159" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="S159" t="n">
         <v>20.2</v>
       </c>
-      <c r="S159" t="n">
+      <c r="T159" t="n">
         <v>5</v>
       </c>
-      <c r="T159" t="n">
+      <c r="U159" t="n">
         <v>4.23</v>
       </c>
-      <c r="U159" t="n">
+      <c r="V159" t="n">
         <v>0.7</v>
       </c>
-      <c r="V159" t="n">
+      <c r="W159" t="n">
         <v>1.7</v>
       </c>
     </row>
@@ -11965,18 +12444,21 @@
         <v>134.5</v>
       </c>
       <c r="R160" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="S160" t="n">
         <v>23.27</v>
       </c>
-      <c r="S160" t="n">
+      <c r="T160" t="n">
         <v>83</v>
       </c>
-      <c r="T160" t="n">
+      <c r="U160" t="n">
         <v>1.82</v>
       </c>
-      <c r="U160" t="n">
+      <c r="V160" t="n">
         <v>2.94</v>
       </c>
-      <c r="V160" t="n">
+      <c r="W160" t="n">
         <v>56.2</v>
       </c>
     </row>
@@ -12037,18 +12519,21 @@
         <v>36.9</v>
       </c>
       <c r="R161" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="S161" t="n">
         <v>35.43</v>
       </c>
-      <c r="S161" t="n">
+      <c r="T161" t="n">
         <v>85</v>
       </c>
-      <c r="T161" t="n">
+      <c r="U161" t="n">
         <v>1.51</v>
       </c>
-      <c r="U161" t="n">
+      <c r="V161" t="n">
         <v>0.25</v>
       </c>
-      <c r="V161" t="n">
+      <c r="W161" t="n">
         <v>95.2</v>
       </c>
     </row>
@@ -12109,18 +12594,21 @@
         <v>245</v>
       </c>
       <c r="R162" t="n">
+        <v>1276.4</v>
+      </c>
+      <c r="S162" t="n">
         <v>36.46</v>
       </c>
-      <c r="S162" t="n">
+      <c r="T162" t="n">
         <v>82</v>
       </c>
-      <c r="T162" t="n">
+      <c r="U162" t="n">
         <v>3.36</v>
       </c>
-      <c r="U162" t="n">
+      <c r="V162" t="n">
         <v>2.04</v>
       </c>
-      <c r="V162" t="n">
+      <c r="W162" t="n">
         <v>8.4</v>
       </c>
     </row>
@@ -12181,18 +12669,21 @@
         <v>71.3</v>
       </c>
       <c r="R163" t="n">
+        <v>219.3</v>
+      </c>
+      <c r="S163" t="n">
         <v>36.38</v>
       </c>
-      <c r="S163" t="n">
+      <c r="T163" t="n">
         <v>94</v>
       </c>
-      <c r="T163" t="n">
+      <c r="U163" t="n">
         <v>3.09</v>
       </c>
-      <c r="U163" t="n">
+      <c r="V163" t="n">
         <v>2.81</v>
       </c>
-      <c r="V163" t="n">
+      <c r="W163" t="n">
         <v>13.6</v>
       </c>
     </row>
@@ -12253,18 +12744,21 @@
         <v>343.5</v>
       </c>
       <c r="R164" t="n">
+        <v>1215.3</v>
+      </c>
+      <c r="S164" t="n">
         <v>75</v>
       </c>
-      <c r="S164" t="n">
+      <c r="T164" t="n">
         <v>98</v>
       </c>
-      <c r="T164" t="n">
+      <c r="U164" t="n">
         <v>3.16</v>
       </c>
-      <c r="U164" t="n">
+      <c r="V164" t="n">
         <v>0.6</v>
       </c>
-      <c r="V164" t="n">
+      <c r="W164" t="n">
         <v>28.2</v>
       </c>
     </row>
@@ -12325,18 +12819,21 @@
         <v>222</v>
       </c>
       <c r="R165" t="n">
+        <v>9990</v>
+      </c>
+      <c r="S165" t="n">
         <v>65.88</v>
       </c>
-      <c r="S165" t="n">
+      <c r="T165" t="n">
         <v>68</v>
       </c>
-      <c r="T165" t="n">
+      <c r="U165" t="n">
         <v>8.56</v>
       </c>
-      <c r="U165" t="n">
+      <c r="V165" t="n">
         <v>0.23</v>
       </c>
-      <c r="V165" t="n">
+      <c r="W165" t="n">
         <v>182</v>
       </c>
     </row>
@@ -12397,18 +12894,21 @@
         <v>116.5</v>
       </c>
       <c r="R166" t="n">
+        <v>668.3</v>
+      </c>
+      <c r="S166" t="n">
         <v>3883.33</v>
       </c>
-      <c r="S166" t="n">
+      <c r="T166" t="n">
         <v>100</v>
       </c>
-      <c r="T166" t="n">
+      <c r="U166" t="n">
         <v>4.38</v>
       </c>
-      <c r="U166" t="n">
+      <c r="V166" t="n">
         <v>0</v>
       </c>
-      <c r="V166" t="n">
+      <c r="W166" t="n">
         <v>11.9</v>
       </c>
     </row>
@@ -12469,18 +12969,21 @@
         <v>29.6</v>
       </c>
       <c r="R167" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="S167" t="n">
         <v>16.69</v>
       </c>
-      <c r="S167" t="n">
+      <c r="T167" t="n">
         <v>33</v>
       </c>
-      <c r="T167" t="n">
+      <c r="U167" t="n">
         <v>1</v>
       </c>
-      <c r="U167" t="n">
+      <c r="V167" t="n">
         <v>4.06</v>
       </c>
-      <c r="V167" t="n">
+      <c r="W167" t="n">
         <v>-2.3</v>
       </c>
     </row>
@@ -12541,18 +13044,21 @@
         <v>129</v>
       </c>
       <c r="R168" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="S168" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="S168" t="n">
+      <c r="T168" t="n">
         <v>52</v>
       </c>
-      <c r="T168" t="n">
+      <c r="U168" t="n">
         <v>8.01</v>
       </c>
-      <c r="U168" t="n">
+      <c r="V168" t="n">
         <v>0</v>
       </c>
-      <c r="V168" t="n">
+      <c r="W168" t="n">
         <v>-13.9</v>
       </c>
     </row>
@@ -12613,18 +13119,21 @@
         <v>72.2</v>
       </c>
       <c r="R169" t="n">
+        <v>1715.8</v>
+      </c>
+      <c r="S169" t="n">
         <v>30.21</v>
       </c>
-      <c r="S169" t="n">
+      <c r="T169" t="n">
         <v>90</v>
       </c>
-      <c r="T169" t="n">
+      <c r="U169" t="n">
         <v>1.95</v>
       </c>
-      <c r="U169" t="n">
+      <c r="V169" t="n">
         <v>2.86</v>
       </c>
-      <c r="V169" t="n">
+      <c r="W169" t="n">
         <v>10.6</v>
       </c>
     </row>
@@ -12683,18 +13192,21 @@
         <v>187.5</v>
       </c>
       <c r="R170" t="n">
+        <v>69</v>
+      </c>
+      <c r="S170" t="n">
         <v>93.28</v>
       </c>
-      <c r="S170" t="n">
+      <c r="T170" t="n">
         <v>92</v>
       </c>
-      <c r="T170" t="n">
+      <c r="U170" t="n">
         <v>7.12</v>
       </c>
-      <c r="U170" t="n">
+      <c r="V170" t="n">
         <v>0.8</v>
       </c>
-      <c r="V170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12753,18 +13265,21 @@
         <v>139</v>
       </c>
       <c r="R171" t="n">
+        <v>401.1</v>
+      </c>
+      <c r="S171" t="n">
         <v>339.02</v>
       </c>
-      <c r="S171" t="n">
+      <c r="T171" t="n">
         <v>80</v>
       </c>
-      <c r="T171" t="n">
+      <c r="U171" t="n">
         <v>8.19</v>
       </c>
-      <c r="U171" t="n">
+      <c r="V171" t="n">
         <v>0.36</v>
       </c>
-      <c r="V171" t="n">
+      <c r="W171" t="n">
         <v>37.3</v>
       </c>
     </row>
@@ -12825,18 +13340,21 @@
         <v>54</v>
       </c>
       <c r="R172" t="n">
+        <v>5144</v>
+      </c>
+      <c r="S172" t="n">
         <v>19.35</v>
       </c>
-      <c r="S172" t="n">
+      <c r="T172" t="n">
         <v>29</v>
       </c>
-      <c r="T172" t="n">
+      <c r="U172" t="n">
         <v>1.36</v>
       </c>
-      <c r="U172" t="n">
+      <c r="V172" t="n">
         <v>2.24</v>
       </c>
-      <c r="V172" t="n">
+      <c r="W172" t="n">
         <v>26.9</v>
       </c>
     </row>
@@ -12897,18 +13415,21 @@
         <v>30.9</v>
       </c>
       <c r="R173" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="S173" t="n">
         <v>19.22</v>
       </c>
-      <c r="S173" t="n">
+      <c r="T173" t="n">
         <v>39</v>
       </c>
-      <c r="T173" t="n">
+      <c r="U173" t="n">
         <v>1.76</v>
       </c>
-      <c r="U173" t="n">
+      <c r="V173" t="n">
         <v>5.33</v>
       </c>
-      <c r="V173" t="n">
+      <c r="W173" t="n">
         <v>12.9</v>
       </c>
     </row>
@@ -12969,18 +13490,21 @@
         <v>128.5</v>
       </c>
       <c r="R174" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="S174" t="n">
         <v>313.41</v>
       </c>
-      <c r="S174" t="n">
+      <c r="T174" t="n">
         <v>99</v>
       </c>
-      <c r="T174" t="n">
+      <c r="U174" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="U174" t="n">
+      <c r="V174" t="n">
         <v>0</v>
       </c>
-      <c r="V174" t="n">
+      <c r="W174" t="n">
         <v>2229</v>
       </c>
     </row>
@@ -13041,18 +13565,21 @@
         <v>10</v>
       </c>
       <c r="R175" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="S175" t="n">
         <v>11.63</v>
       </c>
-      <c r="S175" t="n">
+      <c r="T175" t="n">
         <v>47</v>
       </c>
-      <c r="T175" t="n">
+      <c r="U175" t="n">
         <v>0.43</v>
       </c>
-      <c r="U175" t="n">
+      <c r="V175" t="n">
         <v>0</v>
       </c>
-      <c r="V175" t="n">
+      <c r="W175" t="n">
         <v>-21.5</v>
       </c>
     </row>
@@ -13113,18 +13640,21 @@
         <v>31.6</v>
       </c>
       <c r="R176" t="n">
+        <v>679.7</v>
+      </c>
+      <c r="S176" t="n">
         <v>7.7</v>
       </c>
-      <c r="S176" t="n">
+      <c r="T176" t="n">
         <v>25</v>
       </c>
-      <c r="T176" t="n">
+      <c r="U176" t="n">
         <v>1.25</v>
       </c>
-      <c r="U176" t="n">
+      <c r="V176" t="n">
         <v>0</v>
       </c>
-      <c r="V176" t="n">
+      <c r="W176" t="n">
         <v>-14.3</v>
       </c>
     </row>
@@ -13185,18 +13715,21 @@
         <v>72.90000000000001</v>
       </c>
       <c r="R177" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="S177" t="n">
         <v>85.76000000000001</v>
       </c>
-      <c r="S177" t="n">
+      <c r="T177" t="n">
         <v>96</v>
       </c>
-      <c r="T177" t="n">
+      <c r="U177" t="n">
         <v>1.84</v>
       </c>
-      <c r="U177" t="n">
+      <c r="V177" t="n">
         <v>1.78</v>
       </c>
-      <c r="V177" t="n">
+      <c r="W177" t="n">
         <v>43.3</v>
       </c>
     </row>
@@ -13257,18 +13790,21 @@
         <v>27.6</v>
       </c>
       <c r="R178" t="n">
+        <v>546.8</v>
+      </c>
+      <c r="S178" t="n">
         <v>18.01</v>
       </c>
-      <c r="S178" t="n">
+      <c r="T178" t="n">
         <v>91</v>
       </c>
-      <c r="T178" t="n">
+      <c r="U178" t="n">
         <v>7.25</v>
       </c>
-      <c r="U178" t="n">
+      <c r="V178" t="n">
         <v>0</v>
       </c>
-      <c r="V178" t="n">
+      <c r="W178" t="n">
         <v>175.8</v>
       </c>
     </row>
@@ -13329,18 +13865,21 @@
         <v>52.5</v>
       </c>
       <c r="R179" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="S179" t="n">
         <v>18.49</v>
       </c>
-      <c r="S179" t="n">
+      <c r="T179" t="n">
         <v>45</v>
       </c>
-      <c r="T179" t="n">
+      <c r="U179" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="U179" t="n">
+      <c r="V179" t="n">
         <v>5.71</v>
       </c>
-      <c r="V179" t="n">
+      <c r="W179" t="n">
         <v>-4.9</v>
       </c>
     </row>
@@ -13401,18 +13940,21 @@
         <v>541</v>
       </c>
       <c r="R180" t="n">
+        <v>2293.5</v>
+      </c>
+      <c r="S180" t="n">
         <v>103.64</v>
       </c>
-      <c r="S180" t="n">
+      <c r="T180" t="n">
         <v>82</v>
       </c>
-      <c r="T180" t="n">
+      <c r="U180" t="n">
         <v>5.61</v>
       </c>
-      <c r="U180" t="n">
+      <c r="V180" t="n">
         <v>0.37</v>
       </c>
-      <c r="V180" t="n">
+      <c r="W180" t="n">
         <v>40.3</v>
       </c>
     </row>
@@ -13473,18 +14015,21 @@
         <v>105.5</v>
       </c>
       <c r="R181" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="S181" t="n">
         <v>251.19</v>
       </c>
-      <c r="S181" t="n">
+      <c r="T181" t="n">
         <v>93</v>
       </c>
-      <c r="T181" t="n">
+      <c r="U181" t="n">
         <v>9.4</v>
       </c>
-      <c r="U181" t="n">
+      <c r="V181" t="n">
         <v>0</v>
       </c>
-      <c r="V181" t="n">
+      <c r="W181" t="n">
         <v>140.2</v>
       </c>
     </row>
@@ -13545,18 +14090,21 @@
         <v>400</v>
       </c>
       <c r="R182" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="S182" t="n">
         <v>320</v>
       </c>
-      <c r="S182" t="n">
+      <c r="T182" t="n">
         <v>95</v>
       </c>
-      <c r="T182" t="n">
+      <c r="U182" t="n">
         <v>16.04</v>
       </c>
-      <c r="U182" t="n">
+      <c r="V182" t="n">
         <v>0.23</v>
       </c>
-      <c r="V182" t="n">
+      <c r="W182" t="n">
         <v>57.6</v>
       </c>
     </row>
@@ -13617,18 +14165,21 @@
         <v>2375</v>
       </c>
       <c r="R183" t="n">
+        <v>2197.3</v>
+      </c>
+      <c r="S183" t="n">
         <v>310.86</v>
       </c>
-      <c r="S183" t="n">
+      <c r="T183" t="n">
         <v>84</v>
       </c>
-      <c r="T183" t="n">
+      <c r="U183" t="n">
         <v>51.83</v>
       </c>
-      <c r="U183" t="n">
+      <c r="V183" t="n">
         <v>0.17</v>
       </c>
-      <c r="V183" t="n">
+      <c r="W183" t="n">
         <v>118.8</v>
       </c>
     </row>
@@ -13689,18 +14240,21 @@
         <v>505</v>
       </c>
       <c r="R184" t="n">
+        <v>15648.1</v>
+      </c>
+      <c r="S184" t="n">
         <v>45.21</v>
       </c>
-      <c r="S184" t="n">
+      <c r="T184" t="n">
         <v>95</v>
       </c>
-      <c r="T184" t="n">
+      <c r="U184" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="U184" t="n">
+      <c r="V184" t="n">
         <v>0.27</v>
       </c>
-      <c r="V184" t="n">
+      <c r="W184" t="n">
         <v>730.1</v>
       </c>
     </row>
@@ -13761,18 +14315,21 @@
         <v>525</v>
       </c>
       <c r="R185" t="n">
+        <v>570.4</v>
+      </c>
+      <c r="S185" t="n">
         <v>2019.23</v>
       </c>
-      <c r="S185" t="n">
+      <c r="T185" t="n">
         <v>100</v>
       </c>
-      <c r="T185" t="n">
+      <c r="U185" t="n">
         <v>9.34</v>
       </c>
-      <c r="U185" t="n">
+      <c r="V185" t="n">
         <v>0.04</v>
       </c>
-      <c r="V185" t="n">
+      <c r="W185" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -13833,18 +14390,21 @@
         <v>66.7</v>
       </c>
       <c r="R186" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="S186" t="n">
         <v>68.76000000000001</v>
       </c>
-      <c r="S186" t="n">
+      <c r="T186" t="n">
         <v>51</v>
       </c>
-      <c r="T186" t="n">
+      <c r="U186" t="n">
         <v>2.71</v>
       </c>
-      <c r="U186" t="n">
+      <c r="V186" t="n">
         <v>1.31</v>
       </c>
-      <c r="V186" t="n">
+      <c r="W186" t="n">
         <v>15</v>
       </c>
     </row>
@@ -13905,18 +14465,21 @@
         <v>76.59999999999999</v>
       </c>
       <c r="R187" t="n">
+        <v>2227.6</v>
+      </c>
+      <c r="S187" t="n">
         <v>589.23</v>
       </c>
-      <c r="S187" t="n">
+      <c r="T187" t="n">
         <v>96</v>
       </c>
-      <c r="T187" t="n">
+      <c r="U187" t="n">
         <v>4.48</v>
       </c>
-      <c r="U187" t="n">
+      <c r="V187" t="n">
         <v>0</v>
       </c>
-      <c r="V187" t="n">
+      <c r="W187" t="n">
         <v>17.7</v>
       </c>
     </row>
@@ -13977,18 +14540,21 @@
         <v>69.09999999999999</v>
       </c>
       <c r="R188" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="S188" t="n">
         <v>40.65</v>
       </c>
-      <c r="S188" t="n">
+      <c r="T188" t="n">
         <v>50</v>
       </c>
-      <c r="T188" t="n">
+      <c r="U188" t="n">
         <v>1.75</v>
       </c>
-      <c r="U188" t="n">
+      <c r="V188" t="n">
         <v>0.87</v>
       </c>
-      <c r="V188" t="n">
+      <c r="W188" t="n">
         <v>88.8</v>
       </c>
     </row>
@@ -14049,18 +14615,21 @@
         <v>902</v>
       </c>
       <c r="R189" t="n">
+        <v>1025</v>
+      </c>
+      <c r="S189" t="n">
         <v>5637.5</v>
       </c>
-      <c r="S189" t="n">
+      <c r="T189" t="n">
         <v>90</v>
       </c>
-      <c r="T189" t="n">
+      <c r="U189" t="n">
         <v>14.11</v>
       </c>
-      <c r="U189" t="n">
+      <c r="V189" t="n">
         <v>0</v>
       </c>
-      <c r="V189" t="n">
+      <c r="W189" t="n">
         <v>-24.8</v>
       </c>
     </row>
@@ -14121,18 +14690,21 @@
         <v>58.3</v>
       </c>
       <c r="R190" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="S190" t="n">
         <v>253.48</v>
       </c>
-      <c r="S190" t="n">
+      <c r="T190" t="n">
         <v>98</v>
       </c>
-      <c r="T190" t="n">
+      <c r="U190" t="n">
         <v>1.7</v>
       </c>
-      <c r="U190" t="n">
+      <c r="V190" t="n">
         <v>0.59</v>
       </c>
-      <c r="V190" t="n">
+      <c r="W190" t="n">
         <v>173.8</v>
       </c>
     </row>
@@ -14193,18 +14765,21 @@
         <v>88.5</v>
       </c>
       <c r="R191" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="S191" t="n">
         <v>24.25</v>
       </c>
-      <c r="S191" t="n">
+      <c r="T191" t="n">
         <v>55</v>
       </c>
-      <c r="T191" t="n">
+      <c r="U191" t="n">
         <v>0.89</v>
       </c>
-      <c r="U191" t="n">
+      <c r="V191" t="n">
         <v>2.03</v>
       </c>
-      <c r="V191" t="n">
+      <c r="W191" t="n">
         <v>-2.6</v>
       </c>
     </row>
@@ -14265,18 +14840,21 @@
         <v>84.59999999999999</v>
       </c>
       <c r="R192" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="S192" t="n">
         <v>69.34</v>
       </c>
-      <c r="S192" t="n">
+      <c r="T192" t="n">
         <v>61</v>
       </c>
-      <c r="T192" t="n">
+      <c r="U192" t="n">
         <v>3.17</v>
       </c>
-      <c r="U192" t="n">
+      <c r="V192" t="n">
         <v>1.18</v>
       </c>
-      <c r="V192" t="n">
+      <c r="W192" t="n">
         <v>21.9</v>
       </c>
     </row>
@@ -14337,18 +14915,21 @@
         <v>81.59999999999999</v>
       </c>
       <c r="R193" t="n">
+        <v>3462.9</v>
+      </c>
+      <c r="S193" t="n">
         <v>46.36</v>
       </c>
-      <c r="S193" t="n">
+      <c r="T193" t="n">
         <v>84</v>
       </c>
-      <c r="T193" t="n">
+      <c r="U193" t="n">
         <v>3.59</v>
       </c>
-      <c r="U193" t="n">
+      <c r="V193" t="n">
         <v>0</v>
       </c>
-      <c r="V193" t="n">
+      <c r="W193" t="n">
         <v>58.9</v>
       </c>
     </row>
@@ -14409,18 +14990,21 @@
         <v>66</v>
       </c>
       <c r="R194" t="n">
+        <v>5272.9</v>
+      </c>
+      <c r="S194" t="n">
         <v>600</v>
       </c>
-      <c r="S194" t="n">
+      <c r="T194" t="n">
         <v>96</v>
       </c>
-      <c r="T194" t="n">
+      <c r="U194" t="n">
         <v>2.32</v>
       </c>
-      <c r="U194" t="n">
+      <c r="V194" t="n">
         <v>1.52</v>
       </c>
-      <c r="V194" t="n">
+      <c r="W194" t="n">
         <v>10.3</v>
       </c>
     </row>
@@ -14481,18 +15065,21 @@
         <v>69</v>
       </c>
       <c r="R195" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="S195" t="n">
         <v>18.75</v>
       </c>
-      <c r="S195" t="n">
+      <c r="T195" t="n">
         <v>7</v>
       </c>
-      <c r="T195" t="n">
+      <c r="U195" t="n">
         <v>1.14</v>
       </c>
-      <c r="U195" t="n">
+      <c r="V195" t="n">
         <v>5.22</v>
       </c>
-      <c r="V195" t="n">
+      <c r="W195" t="n">
         <v>-14.8</v>
       </c>
     </row>
@@ -14544,19 +15131,20 @@
       <c r="Q196" t="n">
         <v>113</v>
       </c>
-      <c r="R196" t="n">
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="n">
         <v>16.01</v>
       </c>
-      <c r="S196" t="n">
+      <c r="T196" t="n">
         <v>81</v>
       </c>
-      <c r="T196" t="n">
+      <c r="U196" t="n">
         <v>2.31</v>
       </c>
-      <c r="U196" t="n">
+      <c r="V196" t="n">
         <v>3.03</v>
       </c>
-      <c r="V196" t="n">
+      <c r="W196" t="n">
         <v>28.8</v>
       </c>
     </row>
@@ -14608,19 +15196,20 @@
       <c r="Q197" t="n">
         <v>37.6</v>
       </c>
-      <c r="R197" t="n">
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="n">
         <v>19.79</v>
       </c>
-      <c r="S197" t="n">
+      <c r="T197" t="n">
         <v>96</v>
       </c>
-      <c r="T197" t="n">
+      <c r="U197" t="n">
         <v>2.15</v>
       </c>
-      <c r="U197" t="n">
+      <c r="V197" t="n">
         <v>3.86</v>
       </c>
-      <c r="V197" t="n">
+      <c r="W197" t="n">
         <v>58.3</v>
       </c>
     </row>
@@ -14672,19 +15261,20 @@
       <c r="Q198" t="n">
         <v>39.8</v>
       </c>
-      <c r="R198" t="n">
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="n">
         <v>20.2</v>
       </c>
-      <c r="S198" t="n">
+      <c r="T198" t="n">
         <v>100</v>
       </c>
-      <c r="T198" t="n">
+      <c r="U198" t="n">
         <v>2.17</v>
       </c>
-      <c r="U198" t="n">
+      <c r="V198" t="n">
         <v>3.27</v>
       </c>
-      <c r="V198" t="n">
+      <c r="W198" t="n">
         <v>82.7</v>
       </c>
     </row>
@@ -14736,19 +15326,20 @@
       <c r="Q199" t="n">
         <v>30.4</v>
       </c>
-      <c r="R199" t="n">
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="n">
         <v>17.44</v>
       </c>
-      <c r="S199" t="n">
+      <c r="T199" t="n">
         <v>95</v>
       </c>
-      <c r="T199" t="n">
+      <c r="U199" t="n">
         <v>1.54</v>
       </c>
-      <c r="U199" t="n">
+      <c r="V199" t="n">
         <v>3.25</v>
       </c>
-      <c r="V199" t="n">
+      <c r="W199" t="n">
         <v>-172.7</v>
       </c>
     </row>
@@ -14800,19 +15391,20 @@
       <c r="Q200" t="n">
         <v>15.1</v>
       </c>
-      <c r="R200" t="n">
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="n">
         <v>23.89</v>
       </c>
-      <c r="S200" t="n">
+      <c r="T200" t="n">
         <v>54</v>
       </c>
-      <c r="T200" t="n">
+      <c r="U200" t="n">
         <v>1.17</v>
       </c>
-      <c r="U200" t="n">
+      <c r="V200" t="n">
         <v>3.92</v>
       </c>
-      <c r="V200" t="n">
+      <c r="W200" t="n">
         <v>147.9</v>
       </c>
     </row>
@@ -14864,19 +15456,20 @@
       <c r="Q201" t="n">
         <v>32</v>
       </c>
-      <c r="R201" t="n">
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="n">
         <v>16.78</v>
       </c>
-      <c r="S201" t="n">
+      <c r="T201" t="n">
         <v>82</v>
       </c>
-      <c r="T201" t="n">
+      <c r="U201" t="n">
         <v>1.41</v>
       </c>
-      <c r="U201" t="n">
+      <c r="V201" t="n">
         <v>3.43</v>
       </c>
-      <c r="V201" t="n">
+      <c r="W201" t="n">
         <v>117.9</v>
       </c>
     </row>
@@ -14927,18 +15520,21 @@
         <v>19.6</v>
       </c>
       <c r="R202" t="n">
+        <v>1180.2</v>
+      </c>
+      <c r="S202" t="n">
         <v>12.84</v>
       </c>
-      <c r="S202" t="n">
+      <c r="T202" t="n">
         <v>58</v>
       </c>
-      <c r="T202" t="n">
+      <c r="U202" t="n">
         <v>1.26</v>
       </c>
-      <c r="U202" t="n">
+      <c r="V202" t="n">
         <v>5.39</v>
       </c>
-      <c r="V202" t="n">
+      <c r="W202" t="n">
         <v>28.3</v>
       </c>
     </row>
@@ -14990,19 +15586,20 @@
       <c r="Q203" t="n">
         <v>70.5</v>
       </c>
-      <c r="R203" t="n">
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="n">
         <v>17.28</v>
       </c>
-      <c r="S203" t="n">
+      <c r="T203" t="n">
         <v>95</v>
       </c>
-      <c r="T203" t="n">
+      <c r="U203" t="n">
         <v>2.52</v>
       </c>
-      <c r="U203" t="n">
+      <c r="V203" t="n">
         <v>3.55</v>
       </c>
-      <c r="V203" t="n">
+      <c r="W203" t="n">
         <v>76.09999999999999</v>
       </c>
     </row>
@@ -15054,19 +15651,20 @@
       <c r="Q204" t="n">
         <v>35.8</v>
       </c>
-      <c r="R204" t="n">
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="n">
         <v>16.89</v>
       </c>
-      <c r="S204" t="n">
+      <c r="T204" t="n">
         <v>13</v>
       </c>
-      <c r="T204" t="n">
+      <c r="U204" t="n">
         <v>2.03</v>
       </c>
-      <c r="U204" t="n">
+      <c r="V204" t="n">
         <v>3.91</v>
       </c>
-      <c r="V204" t="n">
+      <c r="W204" t="n">
         <v>24.8</v>
       </c>
     </row>
@@ -15118,19 +15716,20 @@
       <c r="Q205" t="n">
         <v>138.5</v>
       </c>
-      <c r="R205" t="n">
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="n">
         <v>16.55</v>
       </c>
-      <c r="S205" t="n">
+      <c r="T205" t="n">
         <v>82</v>
       </c>
-      <c r="T205" t="n">
+      <c r="U205" t="n">
         <v>2.11</v>
       </c>
-      <c r="U205" t="n">
+      <c r="V205" t="n">
         <v>3.08</v>
       </c>
-      <c r="V205" t="n">
+      <c r="W205" t="n">
         <v>-300.3</v>
       </c>
     </row>
@@ -15182,19 +15781,20 @@
       <c r="Q206" t="n">
         <v>68.8</v>
       </c>
-      <c r="R206" t="n">
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="n">
         <v>25.11</v>
       </c>
-      <c r="S206" t="n">
+      <c r="T206" t="n">
         <v>100</v>
       </c>
-      <c r="T206" t="n">
+      <c r="U206" t="n">
         <v>2.53</v>
       </c>
-      <c r="U206" t="n">
+      <c r="V206" t="n">
         <v>3.24</v>
       </c>
-      <c r="V206" t="n">
+      <c r="W206" t="n">
         <v>227.3</v>
       </c>
     </row>
@@ -15255,18 +15855,21 @@
         <v>97.2</v>
       </c>
       <c r="R207" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="S207" t="n">
         <v>56.18</v>
       </c>
-      <c r="S207" t="n">
+      <c r="T207" t="n">
         <v>6</v>
       </c>
-      <c r="T207" t="n">
+      <c r="U207" t="n">
         <v>4.97</v>
       </c>
-      <c r="U207" t="n">
+      <c r="V207" t="n">
         <v>0.51</v>
       </c>
-      <c r="V207" t="n">
+      <c r="W207" t="n">
         <v>70.7</v>
       </c>
     </row>
@@ -15327,18 +15930,21 @@
         <v>53.1</v>
       </c>
       <c r="R208" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="S208" t="n">
         <v>132.75</v>
       </c>
-      <c r="S208" t="n">
+      <c r="T208" t="n">
         <v>61</v>
       </c>
-      <c r="T208" t="n">
+      <c r="U208" t="n">
         <v>3.69</v>
       </c>
-      <c r="U208" t="n">
+      <c r="V208" t="n">
         <v>0</v>
       </c>
-      <c r="V208" t="n">
+      <c r="W208" t="n">
         <v>16.1</v>
       </c>
     </row>
@@ -15399,18 +16005,21 @@
         <v>117.5</v>
       </c>
       <c r="R209" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="S209" t="n">
         <v>4.98045135262149e+17</v>
       </c>
-      <c r="S209" t="n">
+      <c r="T209" t="n">
         <v>73</v>
       </c>
-      <c r="T209" t="n">
+      <c r="U209" t="n">
         <v>1.71</v>
       </c>
-      <c r="U209" t="n">
+      <c r="V209" t="n">
         <v>0</v>
       </c>
-      <c r="V209" t="n">
+      <c r="W209" t="n">
         <v>56.3</v>
       </c>
     </row>
@@ -15471,18 +16080,21 @@
         <v>70.2</v>
       </c>
       <c r="R210" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="S210" t="n">
         <v>34.08</v>
       </c>
-      <c r="S210" t="n">
+      <c r="T210" t="n">
         <v>92</v>
       </c>
-      <c r="T210" t="n">
+      <c r="U210" t="n">
         <v>6.39</v>
       </c>
-      <c r="U210" t="n">
+      <c r="V210" t="n">
         <v>1.09</v>
       </c>
-      <c r="V210" t="n">
+      <c r="W210" t="n">
         <v>-75</v>
       </c>
     </row>
@@ -15543,18 +16155,21 @@
         <v>54.5</v>
       </c>
       <c r="R211" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="S211" t="n">
         <v>2725</v>
       </c>
-      <c r="S211" t="n">
+      <c r="T211" t="n">
         <v>81</v>
       </c>
-      <c r="T211" t="n">
+      <c r="U211" t="n">
         <v>1.28</v>
       </c>
-      <c r="U211" t="n">
+      <c r="V211" t="n">
         <v>0</v>
       </c>
-      <c r="V211" t="n">
+      <c r="W211" t="n">
         <v>-66.8</v>
       </c>
     </row>
@@ -15615,18 +16230,21 @@
         <v>33.6</v>
       </c>
       <c r="R212" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="S212" t="n">
         <v>16.02</v>
       </c>
-      <c r="S212" t="n">
+      <c r="T212" t="n">
         <v>23</v>
       </c>
-      <c r="T212" t="n">
+      <c r="U212" t="n">
         <v>2.3</v>
       </c>
-      <c r="U212" t="n">
+      <c r="V212" t="n">
         <v>0</v>
       </c>
-      <c r="V212" t="n">
+      <c r="W212" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -15687,18 +16305,21 @@
         <v>564</v>
       </c>
       <c r="R213" t="n">
+        <v>682.1</v>
+      </c>
+      <c r="S213" t="n">
         <v>222.92</v>
       </c>
-      <c r="S213" t="n">
+      <c r="T213" t="n">
         <v>5</v>
       </c>
-      <c r="T213" t="n">
+      <c r="U213" t="n">
         <v>16</v>
       </c>
-      <c r="U213" t="n">
+      <c r="V213" t="n">
         <v>0</v>
       </c>
-      <c r="V213" t="n">
+      <c r="W213" t="n">
         <v>54.4</v>
       </c>
     </row>
@@ -15759,18 +16380,21 @@
         <v>1060</v>
       </c>
       <c r="R214" t="n">
+        <v>4027</v>
+      </c>
+      <c r="S214" t="n">
         <v>65.19</v>
       </c>
-      <c r="S214" t="n">
+      <c r="T214" t="n">
         <v>59</v>
       </c>
-      <c r="T214" t="n">
+      <c r="U214" t="n">
         <v>11.44</v>
       </c>
-      <c r="U214" t="n">
+      <c r="V214" t="n">
         <v>0.25</v>
       </c>
-      <c r="V214" t="n">
+      <c r="W214" t="n">
         <v>108.5</v>
       </c>
     </row>
@@ -15830,13 +16454,14 @@
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr"/>
-      <c r="T215" t="n">
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="U215" t="n">
+      <c r="V215" t="n">
         <v>0</v>
       </c>
-      <c r="V215" t="n">
+      <c r="W215" t="n">
         <v>-6.7</v>
       </c>
     </row>
@@ -15894,13 +16519,14 @@
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr"/>
-      <c r="T216" t="n">
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="n">
         <v>2.98</v>
       </c>
-      <c r="U216" t="n">
+      <c r="V216" t="n">
         <v>0</v>
       </c>
-      <c r="V216" t="n">
+      <c r="W216" t="n">
         <v>-14.5</v>
       </c>
     </row>
@@ -15961,18 +16587,21 @@
         <v>27.8</v>
       </c>
       <c r="R217" t="n">
+        <v>31</v>
+      </c>
+      <c r="S217" t="n">
         <v>308.33</v>
       </c>
-      <c r="S217" t="n">
+      <c r="T217" t="n">
         <v>3</v>
       </c>
-      <c r="T217" t="n">
+      <c r="U217" t="n">
         <v>21.75</v>
       </c>
-      <c r="U217" t="n">
+      <c r="V217" t="n">
         <v>0</v>
       </c>
-      <c r="V217" t="n">
+      <c r="W217" t="n">
         <v>13.3</v>
       </c>
     </row>
@@ -16032,13 +16661,14 @@
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr"/>
       <c r="S218" t="inlineStr"/>
-      <c r="T218" t="n">
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="n">
         <v>21.83</v>
       </c>
-      <c r="U218" t="n">
+      <c r="V218" t="n">
         <v>0</v>
       </c>
-      <c r="V218" t="n">
+      <c r="W218" t="n">
         <v>18.8</v>
       </c>
     </row>
@@ -16098,13 +16728,14 @@
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr"/>
-      <c r="T219" t="n">
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="n">
         <v>2.5</v>
       </c>
-      <c r="U219" t="n">
+      <c r="V219" t="n">
         <v>0</v>
       </c>
-      <c r="V219" t="n">
+      <c r="W219" t="n">
         <v>-59.5</v>
       </c>
     </row>
@@ -16165,18 +16796,21 @@
         <v>21.8</v>
       </c>
       <c r="R220" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S220" t="n">
         <v>121.11</v>
       </c>
-      <c r="S220" t="n">
+      <c r="T220" t="n">
         <v>86</v>
       </c>
-      <c r="T220" t="n">
+      <c r="U220" t="n">
         <v>6.72</v>
       </c>
-      <c r="U220" t="n">
+      <c r="V220" t="n">
         <v>0</v>
       </c>
-      <c r="V220" t="n">
+      <c r="W220" t="n">
         <v>-97.09999999999999</v>
       </c>
     </row>
@@ -16232,7 +16866,8 @@
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
-      <c r="V221" t="n">
+      <c r="V221" t="inlineStr"/>
+      <c r="W221" t="n">
         <v>58</v>
       </c>
     </row>
@@ -16267,6 +16902,7 @@
       <c r="T222" t="inlineStr"/>
       <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
+      <c r="W222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16299,6 +16935,7 @@
       <c r="T223" t="inlineStr"/>
       <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
+      <c r="W223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -16351,14 +16988,17 @@
         <v>97.90000000000001</v>
       </c>
       <c r="R224" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="S224" t="n">
         <v>12.73</v>
       </c>
-      <c r="S224" t="n">
+      <c r="T224" t="n">
         <v>23</v>
       </c>
-      <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
-      <c r="V224" t="n">
+      <c r="V224" t="inlineStr"/>
+      <c r="W224" t="n">
         <v>-72.7</v>
       </c>
     </row>
@@ -16413,18 +17053,21 @@
         <v>2040</v>
       </c>
       <c r="R225" t="n">
+        <v>748.4</v>
+      </c>
+      <c r="S225" t="n">
         <v>278.31</v>
       </c>
-      <c r="S225" t="n">
+      <c r="T225" t="n">
         <v>96</v>
       </c>
-      <c r="T225" t="n">
+      <c r="U225" t="n">
         <v>70.69</v>
       </c>
-      <c r="U225" t="n">
+      <c r="V225" t="n">
         <v>0.22</v>
       </c>
-      <c r="V225" t="inlineStr"/>
+      <c r="W225" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/台股財報估值.xlsx
+++ b/data/台股財報估值.xlsx
@@ -605,7 +605,9 @@
       <c r="Q2" t="n">
         <v>793</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>2234.7</v>
+      </c>
       <c r="S2" t="n">
         <v>19.64</v>
       </c>
@@ -753,7 +755,9 @@
       <c r="Q4" t="n">
         <v>24.2</v>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>7.3</v>
+      </c>
       <c r="S4" t="n">
         <v>25</v>
       </c>
@@ -826,7 +830,9 @@
       <c r="Q5" t="n">
         <v>19275</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>7286.5</v>
+      </c>
       <c r="S5" t="n">
         <v>163.53</v>
       </c>
@@ -899,7 +905,9 @@
       <c r="Q6" t="n">
         <v>376.5</v>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>205.1</v>
+      </c>
       <c r="S6" t="n">
         <v>28.33</v>
       </c>
@@ -972,7 +980,9 @@
       <c r="Q7" t="n">
         <v>1280</v>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>2439.5</v>
+      </c>
       <c r="S7" t="n">
         <v>23.77</v>
       </c>
@@ -1045,7 +1055,9 @@
       <c r="Q8" t="n">
         <v>636</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>677</v>
+      </c>
       <c r="S8" t="n">
         <v>20.22</v>
       </c>
@@ -1118,7 +1130,9 @@
       <c r="Q9" t="n">
         <v>2595</v>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>14561</v>
+      </c>
       <c r="S9" t="n">
         <v>49.07</v>
       </c>
@@ -1266,7 +1280,9 @@
       <c r="Q11" t="n">
         <v>4725</v>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>6332.1</v>
+      </c>
       <c r="S11" t="n">
         <v>142.15</v>
       </c>
@@ -1339,7 +1355,9 @@
       <c r="Q12" t="n">
         <v>831</v>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>2625</v>
+      </c>
       <c r="S12" t="n">
         <v>57.11</v>
       </c>
@@ -1412,7 +1430,9 @@
       <c r="Q13" t="n">
         <v>900</v>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>4639.6</v>
+      </c>
       <c r="S13" t="n">
         <v>32.22</v>
       </c>
@@ -1485,7 +1505,9 @@
       <c r="Q14" t="n">
         <v>2400</v>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>9458.5</v>
+      </c>
       <c r="S14" t="n">
         <v>39.31</v>
       </c>
@@ -1558,7 +1580,9 @@
       <c r="Q15" t="n">
         <v>2510</v>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>650902.5</v>
+      </c>
       <c r="S15" t="n">
         <v>33.74</v>
       </c>
@@ -1631,7 +1655,9 @@
       <c r="Q16" t="n">
         <v>180</v>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>48</v>
+      </c>
       <c r="S16" t="n">
         <v>11.78</v>
       </c>
@@ -1704,7 +1730,9 @@
       <c r="Q17" t="n">
         <v>1395</v>
       </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>7212.8</v>
+      </c>
       <c r="S17" t="n">
         <v>61.45</v>
       </c>
@@ -1777,7 +1805,9 @@
       <c r="Q18" t="n">
         <v>224</v>
       </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>74.3</v>
+      </c>
       <c r="S18" t="n">
         <v>14.85</v>
       </c>
@@ -1850,7 +1880,9 @@
       <c r="Q19" t="n">
         <v>5600</v>
       </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>20066</v>
+      </c>
       <c r="S19" t="n">
         <v>120.3</v>
       </c>
@@ -1923,7 +1955,9 @@
       <c r="Q20" t="n">
         <v>1190</v>
       </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>278.4</v>
+      </c>
       <c r="S20" t="n">
         <v>62.01</v>
       </c>
@@ -1996,7 +2030,9 @@
       <c r="Q21" t="n">
         <v>223.5</v>
       </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>2323.6</v>
+      </c>
       <c r="S21" t="n">
         <v>20.39</v>
       </c>
@@ -2069,7 +2105,9 @@
       <c r="Q22" t="n">
         <v>2310</v>
       </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>9823.200000000001</v>
+      </c>
       <c r="S22" t="n">
         <v>72.70999999999999</v>
       </c>
@@ -2142,7 +2180,9 @@
       <c r="Q23" t="n">
         <v>7550</v>
       </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>7194.9</v>
+      </c>
       <c r="S23" t="n">
         <v>66.54000000000001</v>
       </c>
@@ -2215,7 +2255,9 @@
       <c r="Q24" t="n">
         <v>315</v>
       </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>378.4</v>
+      </c>
       <c r="S24" t="n">
         <v>19.94</v>
       </c>
@@ -2288,7 +2330,9 @@
       <c r="Q25" t="n">
         <v>142</v>
       </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>227.2</v>
+      </c>
       <c r="S25" t="n">
         <v>16.42</v>
       </c>
@@ -2436,7 +2480,9 @@
       <c r="Q27" t="n">
         <v>188</v>
       </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>419.7</v>
+      </c>
       <c r="S27" t="n">
         <v>27.01</v>
       </c>
@@ -2509,7 +2555,9 @@
       <c r="Q28" t="n">
         <v>394</v>
       </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="n">
+        <v>298</v>
+      </c>
       <c r="S28" t="n">
         <v>27.9</v>
       </c>
@@ -2582,7 +2630,9 @@
       <c r="Q29" t="n">
         <v>154.5</v>
       </c>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>164.3</v>
+      </c>
       <c r="S29" t="n">
         <v>18.41</v>
       </c>
@@ -2655,7 +2705,9 @@
       <c r="Q30" t="n">
         <v>1370</v>
       </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>1716.9</v>
+      </c>
       <c r="S30" t="n">
         <v>40.04</v>
       </c>
@@ -2728,7 +2780,9 @@
       <c r="Q31" t="n">
         <v>318</v>
       </c>
-      <c r="R31" t="inlineStr"/>
+      <c r="R31" t="n">
+        <v>274</v>
+      </c>
       <c r="S31" t="n">
         <v>18.11</v>
       </c>
@@ -2876,7 +2930,9 @@
       <c r="Q33" t="n">
         <v>333</v>
       </c>
-      <c r="R33" t="inlineStr"/>
+      <c r="R33" t="n">
+        <v>799.4</v>
+      </c>
       <c r="S33" t="n">
         <v>26.08</v>
       </c>
@@ -2949,7 +3005,9 @@
       <c r="Q34" t="n">
         <v>1075</v>
       </c>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>1000.6</v>
+      </c>
       <c r="S34" t="n">
         <v>30.58</v>
       </c>
@@ -3022,7 +3080,9 @@
       <c r="Q35" t="n">
         <v>9460</v>
       </c>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>3409.2</v>
+      </c>
       <c r="S35" t="n">
         <v>192.04</v>
       </c>
@@ -3095,7 +3155,9 @@
       <c r="Q36" t="n">
         <v>3840</v>
       </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>5634.5</v>
+      </c>
       <c r="S36" t="n">
         <v>104.63</v>
       </c>
@@ -3168,7 +3230,9 @@
       <c r="Q37" t="n">
         <v>350</v>
       </c>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>826.8</v>
+      </c>
       <c r="S37" t="n">
         <v>30.33</v>
       </c>
@@ -3241,7 +3305,9 @@
       <c r="Q38" t="n">
         <v>344</v>
       </c>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>2304.4</v>
+      </c>
       <c r="S38" t="n">
         <v>16.07</v>
       </c>
@@ -3314,7 +3380,9 @@
       <c r="Q39" t="n">
         <v>142.5</v>
       </c>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="n">
+        <v>138.1</v>
+      </c>
       <c r="S39" t="n">
         <v>27.04</v>
       </c>
@@ -3387,7 +3455,9 @@
       <c r="Q40" t="n">
         <v>74.3</v>
       </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>111.5</v>
+      </c>
       <c r="S40" t="n">
         <v>19</v>
       </c>
@@ -3460,7 +3530,9 @@
       <c r="Q41" t="n">
         <v>116.5</v>
       </c>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>525.6</v>
+      </c>
       <c r="S41" t="n">
         <v>17.18</v>
       </c>
@@ -3533,7 +3605,9 @@
       <c r="Q42" t="n">
         <v>1115</v>
       </c>
-      <c r="R42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>5331</v>
+      </c>
       <c r="S42" t="n">
         <v>68.73999999999999</v>
       </c>
@@ -3606,7 +3680,9 @@
       <c r="Q43" t="n">
         <v>3585</v>
       </c>
-      <c r="R43" t="inlineStr"/>
+      <c r="R43" t="n">
+        <v>1048.9</v>
+      </c>
       <c r="S43" t="n">
         <v>67.83</v>
       </c>
@@ -3679,7 +3755,9 @@
       <c r="Q44" t="n">
         <v>1970</v>
       </c>
-      <c r="R44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>1897.8</v>
+      </c>
       <c r="S44" t="n">
         <v>26.04</v>
       </c>
@@ -3752,7 +3830,9 @@
       <c r="Q45" t="n">
         <v>499.5</v>
       </c>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>4336.9</v>
+      </c>
       <c r="S45" t="n">
         <v>38.63</v>
       </c>
@@ -3825,7 +3905,9 @@
       <c r="Q46" t="n">
         <v>506</v>
       </c>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>979.9</v>
+      </c>
       <c r="S46" t="n">
         <v>21.31</v>
       </c>
@@ -3973,7 +4055,9 @@
       <c r="Q48" t="n">
         <v>178.5</v>
       </c>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>535.5</v>
+      </c>
       <c r="S48" t="n">
         <v>24.65</v>
       </c>
@@ -4121,7 +4205,9 @@
       <c r="Q50" t="n">
         <v>443.5</v>
       </c>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>171.8</v>
+      </c>
       <c r="S50" t="n">
         <v>23.99</v>
       </c>
@@ -4194,7 +4280,9 @@
       <c r="Q51" t="n">
         <v>152.5</v>
       </c>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>90.40000000000001</v>
+      </c>
       <c r="S51" t="n">
         <v>16.54</v>
       </c>
@@ -4267,7 +4355,9 @@
       <c r="Q52" t="n">
         <v>52.6</v>
       </c>
-      <c r="R52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>580.9</v>
+      </c>
       <c r="S52" t="n">
         <v>6.03</v>
       </c>
@@ -4340,7 +4430,9 @@
       <c r="Q53" t="n">
         <v>288</v>
       </c>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>209.6</v>
+      </c>
       <c r="S53" t="n">
         <v>15.6</v>
       </c>
@@ -4413,7 +4505,9 @@
       <c r="Q54" t="n">
         <v>349</v>
       </c>
-      <c r="R54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>130.7</v>
+      </c>
       <c r="S54" t="n">
         <v>32.26</v>
       </c>
@@ -4486,7 +4580,9 @@
       <c r="Q55" t="n">
         <v>150</v>
       </c>
-      <c r="R55" t="inlineStr"/>
+      <c r="R55" t="n">
+        <v>430.4</v>
+      </c>
       <c r="S55" t="n">
         <v>17.5</v>
       </c>
@@ -4634,7 +4730,9 @@
       <c r="Q57" t="n">
         <v>115</v>
       </c>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="n">
+        <v>339</v>
+      </c>
       <c r="S57" t="n">
         <v>12.39</v>
       </c>
@@ -4707,7 +4805,9 @@
       <c r="Q58" t="n">
         <v>118.5</v>
       </c>
-      <c r="R58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>98.5</v>
+      </c>
       <c r="S58" t="n">
         <v>14.43</v>
       </c>
@@ -4780,7 +4880,9 @@
       <c r="Q59" t="n">
         <v>105</v>
       </c>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>21.9</v>
+      </c>
       <c r="S59" t="n">
         <v>21.52</v>
       </c>
@@ -4853,7 +4955,9 @@
       <c r="Q60" t="n">
         <v>409.5</v>
       </c>
-      <c r="R60" t="inlineStr"/>
+      <c r="R60" t="n">
+        <v>757.2</v>
+      </c>
       <c r="S60" t="n">
         <v>129.18</v>
       </c>
@@ -4926,7 +5030,9 @@
       <c r="Q61" t="n">
         <v>82.5</v>
       </c>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>183.5</v>
+      </c>
       <c r="S61" t="n">
         <v>12.91</v>
       </c>
@@ -4999,7 +5105,9 @@
       <c r="Q62" t="n">
         <v>1605</v>
       </c>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>442.3</v>
+      </c>
       <c r="S62" t="n">
         <v>89.70999999999999</v>
       </c>
@@ -5072,7 +5180,9 @@
       <c r="Q63" t="n">
         <v>6415</v>
       </c>
-      <c r="R63" t="inlineStr"/>
+      <c r="R63" t="n">
+        <v>6285.5</v>
+      </c>
       <c r="S63" t="n">
         <v>167.32</v>
       </c>
@@ -5145,7 +5255,9 @@
       <c r="Q64" t="n">
         <v>66.5</v>
       </c>
-      <c r="R64" t="inlineStr"/>
+      <c r="R64" t="n">
+        <v>31.5</v>
+      </c>
       <c r="S64" t="n">
         <v>14.55</v>
       </c>
@@ -5218,7 +5330,9 @@
       <c r="Q65" t="n">
         <v>382</v>
       </c>
-      <c r="R65" t="inlineStr"/>
+      <c r="R65" t="n">
+        <v>123.1</v>
+      </c>
       <c r="S65" t="n">
         <v>49.55</v>
       </c>
@@ -5291,7 +5405,9 @@
       <c r="Q66" t="n">
         <v>100.5</v>
       </c>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>37.3</v>
+      </c>
       <c r="S66" t="n">
         <v>13.26</v>
       </c>
@@ -5364,7 +5480,9 @@
       <c r="Q67" t="n">
         <v>138.5</v>
       </c>
-      <c r="R67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>51.8</v>
+      </c>
       <c r="S67" t="n">
         <v>19.79</v>
       </c>
@@ -5437,7 +5555,9 @@
       <c r="Q68" t="n">
         <v>118.5</v>
       </c>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>4412.1</v>
+      </c>
       <c r="S68" t="n">
         <v>24.04</v>
       </c>
@@ -5510,7 +5630,9 @@
       <c r="Q69" t="n">
         <v>630</v>
       </c>
-      <c r="R69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>987.6</v>
+      </c>
       <c r="S69" t="n">
         <v>83.44</v>
       </c>
@@ -5583,7 +5705,9 @@
       <c r="Q70" t="n">
         <v>119</v>
       </c>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>210.6</v>
+      </c>
       <c r="S70" t="n">
         <v>17.12</v>
       </c>
@@ -5656,7 +5780,9 @@
       <c r="Q71" t="n">
         <v>246.5</v>
       </c>
-      <c r="R71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>208.2</v>
+      </c>
       <c r="S71" t="n">
         <v>14.81</v>
       </c>
@@ -5729,7 +5855,9 @@
       <c r="Q72" t="n">
         <v>187</v>
       </c>
-      <c r="R72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>124.6</v>
+      </c>
       <c r="S72" t="n">
         <v>13.87</v>
       </c>
@@ -5802,7 +5930,9 @@
       <c r="Q73" t="n">
         <v>100.5</v>
       </c>
-      <c r="R73" t="inlineStr"/>
+      <c r="R73" t="n">
+        <v>627.4</v>
+      </c>
       <c r="S73" t="n">
         <v>12.27</v>
       </c>
@@ -5875,7 +6005,9 @@
       <c r="Q74" t="n">
         <v>155</v>
       </c>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>200</v>
+      </c>
       <c r="S74" t="n">
         <v>25.54</v>
       </c>
@@ -5948,7 +6080,9 @@
       <c r="Q75" t="n">
         <v>132.5</v>
       </c>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>97.2</v>
+      </c>
       <c r="S75" t="n">
         <v>14.31</v>
       </c>
@@ -6021,7 +6155,9 @@
       <c r="Q76" t="n">
         <v>26.7</v>
       </c>
-      <c r="R76" t="inlineStr"/>
+      <c r="R76" t="n">
+        <v>36.2</v>
+      </c>
       <c r="S76" t="n">
         <v>20.54</v>
       </c>
@@ -6094,7 +6230,9 @@
       <c r="Q77" t="n">
         <v>966</v>
       </c>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="n">
+        <v>895.8</v>
+      </c>
       <c r="S77" t="n">
         <v>76.06</v>
       </c>
@@ -6242,7 +6380,9 @@
       <c r="Q79" t="n">
         <v>1555</v>
       </c>
-      <c r="R79" t="inlineStr"/>
+      <c r="R79" t="n">
+        <v>1452.2</v>
+      </c>
       <c r="S79" t="n">
         <v>109.82</v>
       </c>
@@ -6315,7 +6455,9 @@
       <c r="Q80" t="n">
         <v>2085</v>
       </c>
-      <c r="R80" t="inlineStr"/>
+      <c r="R80" t="n">
+        <v>1627.8</v>
+      </c>
       <c r="S80" t="n">
         <v>77.11</v>
       </c>
@@ -6388,7 +6530,9 @@
       <c r="Q81" t="n">
         <v>79.3</v>
       </c>
-      <c r="R81" t="inlineStr"/>
+      <c r="R81" t="n">
+        <v>103.1</v>
+      </c>
       <c r="S81" t="n">
         <v>16.87</v>
       </c>
@@ -6461,7 +6605,9 @@
       <c r="Q82" t="n">
         <v>2150</v>
       </c>
-      <c r="R82" t="inlineStr"/>
+      <c r="R82" t="n">
+        <v>55847.2</v>
+      </c>
       <c r="S82" t="n">
         <v>79.31</v>
       </c>
@@ -6534,7 +6680,9 @@
       <c r="Q83" t="n">
         <v>181</v>
       </c>
-      <c r="R83" t="inlineStr"/>
+      <c r="R83" t="n">
+        <v>910.6</v>
+      </c>
       <c r="S83" t="n">
         <v>21.99</v>
       </c>
@@ -6607,7 +6755,9 @@
       <c r="Q84" t="n">
         <v>223.5</v>
       </c>
-      <c r="R84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>5176.5</v>
+      </c>
       <c r="S84" t="n">
         <v>32.87</v>
       </c>
@@ -6680,7 +6830,9 @@
       <c r="Q85" t="n">
         <v>889</v>
       </c>
-      <c r="R85" t="inlineStr"/>
+      <c r="R85" t="n">
+        <v>714.3</v>
+      </c>
       <c r="S85" t="n">
         <v>60.23</v>
       </c>
@@ -6828,7 +6980,9 @@
       <c r="Q87" t="n">
         <v>1005</v>
       </c>
-      <c r="R87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>15971.9</v>
+      </c>
       <c r="S87" t="n">
         <v>142.35</v>
       </c>
@@ -6901,7 +7055,9 @@
       <c r="Q88" t="n">
         <v>909</v>
       </c>
-      <c r="R88" t="inlineStr"/>
+      <c r="R88" t="n">
+        <v>5873.6</v>
+      </c>
       <c r="S88" t="n">
         <v>192.58</v>
       </c>
@@ -6974,7 +7130,9 @@
       <c r="Q89" t="n">
         <v>434</v>
       </c>
-      <c r="R89" t="inlineStr"/>
+      <c r="R89" t="n">
+        <v>1413.7</v>
+      </c>
       <c r="S89" t="n">
         <v>8.43</v>
       </c>
@@ -7047,7 +7205,9 @@
       <c r="Q90" t="n">
         <v>122</v>
       </c>
-      <c r="R90" t="inlineStr"/>
+      <c r="R90" t="n">
+        <v>145.2</v>
+      </c>
       <c r="S90" t="n">
         <v>12.96</v>
       </c>
@@ -7120,7 +7280,9 @@
       <c r="Q91" t="n">
         <v>143</v>
       </c>
-      <c r="R91" t="inlineStr"/>
+      <c r="R91" t="n">
+        <v>451.8</v>
+      </c>
       <c r="S91" t="n">
         <v>11.64</v>
       </c>
@@ -7268,7 +7430,9 @@
       <c r="Q93" t="n">
         <v>59.1</v>
       </c>
-      <c r="R93" t="inlineStr"/>
+      <c r="R93" t="n">
+        <v>54.1</v>
+      </c>
       <c r="S93" t="n">
         <v>13.65</v>
       </c>
@@ -7341,7 +7505,9 @@
       <c r="Q94" t="n">
         <v>713</v>
       </c>
-      <c r="R94" t="inlineStr"/>
+      <c r="R94" t="n">
+        <v>1061.8</v>
+      </c>
       <c r="S94" t="n">
         <v>69.48999999999999</v>
       </c>
@@ -7414,7 +7580,9 @@
       <c r="Q95" t="n">
         <v>1065</v>
       </c>
-      <c r="R95" t="inlineStr"/>
+      <c r="R95" t="n">
+        <v>5519.3</v>
+      </c>
       <c r="S95" t="n">
         <v>53.17</v>
       </c>
@@ -7487,7 +7655,9 @@
       <c r="Q96" t="n">
         <v>566</v>
       </c>
-      <c r="R96" t="inlineStr"/>
+      <c r="R96" t="n">
+        <v>2974.9</v>
+      </c>
       <c r="S96" t="n">
         <v>27.5</v>
       </c>
@@ -7560,7 +7730,9 @@
       <c r="Q97" t="n">
         <v>101.5</v>
       </c>
-      <c r="R97" t="inlineStr"/>
+      <c r="R97" t="n">
+        <v>169.5</v>
+      </c>
       <c r="S97" t="n">
         <v>14.95</v>
       </c>
@@ -7708,7 +7880,9 @@
       <c r="Q99" t="n">
         <v>774</v>
       </c>
-      <c r="R99" t="inlineStr"/>
+      <c r="R99" t="n">
+        <v>872.6</v>
+      </c>
       <c r="S99" t="n">
         <v>23.45</v>
       </c>
@@ -7781,7 +7955,9 @@
       <c r="Q100" t="n">
         <v>304</v>
       </c>
-      <c r="R100" t="inlineStr"/>
+      <c r="R100" t="n">
+        <v>205.2</v>
+      </c>
       <c r="S100" t="n">
         <v>40.16</v>
       </c>
@@ -7854,7 +8030,9 @@
       <c r="Q101" t="n">
         <v>870</v>
       </c>
-      <c r="R101" t="inlineStr"/>
+      <c r="R101" t="n">
+        <v>700.7</v>
+      </c>
       <c r="S101" t="n">
         <v>100.69</v>
       </c>
@@ -7927,7 +8105,9 @@
       <c r="Q102" t="n">
         <v>266</v>
       </c>
-      <c r="R102" t="inlineStr"/>
+      <c r="R102" t="n">
+        <v>159.2</v>
+      </c>
       <c r="S102" t="n">
         <v>149.44</v>
       </c>
@@ -8000,7 +8180,9 @@
       <c r="Q103" t="n">
         <v>49.4</v>
       </c>
-      <c r="R103" t="inlineStr"/>
+      <c r="R103" t="n">
+        <v>21.5</v>
+      </c>
       <c r="S103" t="n">
         <v>12.97</v>
       </c>
@@ -8073,7 +8255,9 @@
       <c r="Q104" t="n">
         <v>89.5</v>
       </c>
-      <c r="R104" t="inlineStr"/>
+      <c r="R104" t="n">
+        <v>212</v>
+      </c>
       <c r="S104" t="n">
         <v>36.09</v>
       </c>
@@ -8146,7 +8330,9 @@
       <c r="Q105" t="n">
         <v>674</v>
       </c>
-      <c r="R105" t="inlineStr"/>
+      <c r="R105" t="n">
+        <v>30069.7</v>
+      </c>
       <c r="S105" t="n">
         <v>62.06</v>
       </c>
@@ -8219,7 +8405,9 @@
       <c r="Q106" t="n">
         <v>108</v>
       </c>
-      <c r="R106" t="inlineStr"/>
+      <c r="R106" t="n">
+        <v>3895.6</v>
+      </c>
       <c r="S106" t="n">
         <v>27.34</v>
       </c>
@@ -8292,7 +8480,9 @@
       <c r="Q107" t="n">
         <v>1450</v>
       </c>
-      <c r="R107" t="inlineStr"/>
+      <c r="R107" t="n">
+        <v>1084.3</v>
+      </c>
       <c r="S107" t="n">
         <v>17.87</v>
       </c>
@@ -8365,7 +8555,9 @@
       <c r="Q108" t="n">
         <v>2580</v>
       </c>
-      <c r="R108" t="inlineStr"/>
+      <c r="R108" t="n">
+        <v>5704</v>
+      </c>
       <c r="S108" t="n">
         <v>24.52</v>
       </c>
@@ -8438,7 +8630,9 @@
       <c r="Q109" t="n">
         <v>259.5</v>
       </c>
-      <c r="R109" t="inlineStr"/>
+      <c r="R109" t="n">
+        <v>3092.8</v>
+      </c>
       <c r="S109" t="n">
         <v>45.77</v>
       </c>
@@ -8511,7 +8705,9 @@
       <c r="Q110" t="n">
         <v>58.5</v>
       </c>
-      <c r="R110" t="inlineStr"/>
+      <c r="R110" t="n">
+        <v>385.5</v>
+      </c>
       <c r="S110" t="n">
         <v>23.31</v>
       </c>
@@ -8584,7 +8780,9 @@
       <c r="Q111" t="n">
         <v>242.5</v>
       </c>
-      <c r="R111" t="inlineStr"/>
+      <c r="R111" t="n">
+        <v>1173.5</v>
+      </c>
       <c r="S111" t="n">
         <v>36.3</v>
       </c>
@@ -8657,7 +8855,9 @@
       <c r="Q112" t="n">
         <v>173.5</v>
       </c>
-      <c r="R112" t="inlineStr"/>
+      <c r="R112" t="n">
+        <v>649.9</v>
+      </c>
       <c r="S112" t="n">
         <v>26.49</v>
       </c>
@@ -8730,7 +8930,9 @@
       <c r="Q113" t="n">
         <v>2000</v>
       </c>
-      <c r="R113" t="inlineStr"/>
+      <c r="R113" t="n">
+        <v>3901.6</v>
+      </c>
       <c r="S113" t="n">
         <v>40.17</v>
       </c>
@@ -8803,7 +9005,9 @@
       <c r="Q114" t="n">
         <v>62</v>
       </c>
-      <c r="R114" t="inlineStr"/>
+      <c r="R114" t="n">
+        <v>37.4</v>
+      </c>
       <c r="S114" t="n">
         <v>14.06</v>
       </c>
@@ -8876,7 +9080,9 @@
       <c r="Q115" t="n">
         <v>56</v>
       </c>
-      <c r="R115" t="inlineStr"/>
+      <c r="R115" t="n">
+        <v>12.6</v>
+      </c>
       <c r="S115" t="n">
         <v>11.76</v>
       </c>
@@ -8949,7 +9155,9 @@
       <c r="Q116" t="n">
         <v>366</v>
       </c>
-      <c r="R116" t="inlineStr"/>
+      <c r="R116" t="n">
+        <v>2778.5</v>
+      </c>
       <c r="S116" t="n">
         <v>43.57</v>
       </c>
@@ -9022,7 +9230,9 @@
       <c r="Q117" t="n">
         <v>309.5</v>
       </c>
-      <c r="R117" t="inlineStr"/>
+      <c r="R117" t="n">
+        <v>1333</v>
+      </c>
       <c r="S117" t="n">
         <v>9.970000000000001</v>
       </c>
@@ -9095,7 +9305,9 @@
       <c r="Q118" t="n">
         <v>127</v>
       </c>
-      <c r="R118" t="inlineStr"/>
+      <c r="R118" t="n">
+        <v>346.8</v>
+      </c>
       <c r="S118" t="n">
         <v>36.92</v>
       </c>
@@ -9168,7 +9380,9 @@
       <c r="Q119" t="n">
         <v>33.7</v>
       </c>
-      <c r="R119" t="inlineStr"/>
+      <c r="R119" t="n">
+        <v>21.4</v>
+      </c>
       <c r="S119" t="n">
         <v>27.62</v>
       </c>
@@ -9312,7 +9526,9 @@
       <c r="Q121" t="n">
         <v>1900</v>
       </c>
-      <c r="R121" t="inlineStr"/>
+      <c r="R121" t="n">
+        <v>5487.5</v>
+      </c>
       <c r="S121" t="n">
         <v>135.14</v>
       </c>
@@ -9385,7 +9601,9 @@
       <c r="Q122" t="n">
         <v>91.7</v>
       </c>
-      <c r="R122" t="inlineStr"/>
+      <c r="R122" t="n">
+        <v>40.1</v>
+      </c>
       <c r="S122" t="n">
         <v>22.26</v>
       </c>
@@ -9458,7 +9676,9 @@
       <c r="Q123" t="n">
         <v>283</v>
       </c>
-      <c r="R123" t="inlineStr"/>
+      <c r="R123" t="n">
+        <v>417.9</v>
+      </c>
       <c r="S123" t="n">
         <v>58.47</v>
       </c>
@@ -9531,7 +9751,9 @@
       <c r="Q124" t="n">
         <v>293</v>
       </c>
-      <c r="R124" t="inlineStr"/>
+      <c r="R124" t="n">
+        <v>80.09999999999999</v>
+      </c>
       <c r="S124" t="n">
         <v>38.15</v>
       </c>
@@ -9604,7 +9826,9 @@
       <c r="Q125" t="n">
         <v>215.5</v>
       </c>
-      <c r="R125" t="inlineStr"/>
+      <c r="R125" t="n">
+        <v>276.1</v>
+      </c>
       <c r="S125" t="n">
         <v>10.5</v>
       </c>
@@ -9677,7 +9901,9 @@
       <c r="Q126" t="n">
         <v>93.8</v>
       </c>
-      <c r="R126" t="inlineStr"/>
+      <c r="R126" t="n">
+        <v>254</v>
+      </c>
       <c r="S126" t="n">
         <v>11.25</v>
       </c>
@@ -9975,7 +10201,9 @@
       <c r="Q130" t="n">
         <v>56.6</v>
       </c>
-      <c r="R130" t="inlineStr"/>
+      <c r="R130" t="n">
+        <v>56.6</v>
+      </c>
       <c r="S130" t="n">
         <v>18.03</v>
       </c>
@@ -10048,7 +10276,9 @@
       <c r="Q131" t="n">
         <v>5185</v>
       </c>
-      <c r="R131" t="inlineStr"/>
+      <c r="R131" t="n">
+        <v>6920.3</v>
+      </c>
       <c r="S131" t="n">
         <v>32.87</v>
       </c>
@@ -10121,7 +10351,9 @@
       <c r="Q132" t="n">
         <v>213</v>
       </c>
-      <c r="R132" t="inlineStr"/>
+      <c r="R132" t="n">
+        <v>74</v>
+      </c>
       <c r="S132" t="n">
         <v>27.17</v>
       </c>
@@ -10194,7 +10426,9 @@
       <c r="Q133" t="n">
         <v>170</v>
       </c>
-      <c r="R133" t="inlineStr"/>
+      <c r="R133" t="n">
+        <v>71.8</v>
+      </c>
       <c r="S133" t="n">
         <v>14.66</v>
       </c>
@@ -10267,7 +10501,9 @@
       <c r="Q134" t="n">
         <v>193.5</v>
       </c>
-      <c r="R134" t="inlineStr"/>
+      <c r="R134" t="n">
+        <v>263.7</v>
+      </c>
       <c r="S134" t="n">
         <v>33.95</v>
       </c>
@@ -10340,7 +10576,9 @@
       <c r="Q135" t="n">
         <v>43.8</v>
       </c>
-      <c r="R135" t="inlineStr"/>
+      <c r="R135" t="n">
+        <v>393.9</v>
+      </c>
       <c r="S135" t="n">
         <v>10.15</v>
       </c>
@@ -10413,7 +10651,9 @@
       <c r="Q136" t="n">
         <v>433</v>
       </c>
-      <c r="R136" t="inlineStr"/>
+      <c r="R136" t="n">
+        <v>397.9</v>
+      </c>
       <c r="S136" t="n">
         <v>54.47</v>
       </c>
@@ -10486,7 +10726,9 @@
       <c r="Q137" t="n">
         <v>788</v>
       </c>
-      <c r="R137" t="inlineStr"/>
+      <c r="R137" t="n">
+        <v>5853</v>
+      </c>
       <c r="S137" t="n">
         <v>14.08</v>
       </c>
@@ -10559,7 +10801,9 @@
       <c r="Q138" t="n">
         <v>552</v>
       </c>
-      <c r="R138" t="inlineStr"/>
+      <c r="R138" t="n">
+        <v>785.8</v>
+      </c>
       <c r="S138" t="n">
         <v>99.81999999999999</v>
       </c>
@@ -10632,7 +10876,9 @@
       <c r="Q139" t="n">
         <v>112.5</v>
       </c>
-      <c r="R139" t="inlineStr"/>
+      <c r="R139" t="n">
+        <v>1889</v>
+      </c>
       <c r="S139" t="n">
         <v>14.17</v>
       </c>
@@ -10705,7 +10951,9 @@
       <c r="Q140" t="n">
         <v>194.5</v>
       </c>
-      <c r="R140" t="inlineStr"/>
+      <c r="R140" t="n">
+        <v>551.6</v>
+      </c>
       <c r="S140" t="n">
         <v>194.5</v>
       </c>
@@ -10853,7 +11101,9 @@
       <c r="Q142" t="n">
         <v>78</v>
       </c>
-      <c r="R142" t="inlineStr"/>
+      <c r="R142" t="n">
+        <v>23.4</v>
+      </c>
       <c r="S142" t="n">
         <v>17.61</v>
       </c>
@@ -10926,7 +11176,9 @@
       <c r="Q143" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="R143" t="inlineStr"/>
+      <c r="R143" t="n">
+        <v>58.6</v>
+      </c>
       <c r="S143" t="n">
         <v>16.57</v>
       </c>
@@ -10999,7 +11251,9 @@
       <c r="Q144" t="n">
         <v>557</v>
       </c>
-      <c r="R144" t="inlineStr"/>
+      <c r="R144" t="n">
+        <v>811.4</v>
+      </c>
       <c r="S144" t="n">
         <v>165.77</v>
       </c>
@@ -11072,7 +11326,9 @@
       <c r="Q145" t="n">
         <v>225</v>
       </c>
-      <c r="R145" t="inlineStr"/>
+      <c r="R145" t="n">
+        <v>2855.6</v>
+      </c>
       <c r="S145" t="n">
         <v>15.52</v>
       </c>
@@ -11145,7 +11401,9 @@
       <c r="Q146" t="n">
         <v>897</v>
       </c>
-      <c r="R146" t="inlineStr"/>
+      <c r="R146" t="n">
+        <v>1488</v>
+      </c>
       <c r="S146" t="n">
         <v>115.59</v>
       </c>
@@ -11293,7 +11551,9 @@
       <c r="Q148" t="n">
         <v>179</v>
       </c>
-      <c r="R148" t="inlineStr"/>
+      <c r="R148" t="n">
+        <v>53.7</v>
+      </c>
       <c r="S148" t="n">
         <v>16.85</v>
       </c>
@@ -11441,7 +11701,9 @@
       <c r="Q150" t="n">
         <v>163</v>
       </c>
-      <c r="R150" t="inlineStr"/>
+      <c r="R150" t="n">
+        <v>455.2</v>
+      </c>
       <c r="S150" t="n">
         <v>23.76</v>
       </c>
@@ -11514,7 +11776,9 @@
       <c r="Q151" t="n">
         <v>52.2</v>
       </c>
-      <c r="R151" t="inlineStr"/>
+      <c r="R151" t="n">
+        <v>193.4</v>
+      </c>
       <c r="S151" t="n">
         <v>16.11</v>
       </c>
@@ -11587,7 +11851,9 @@
       <c r="Q152" t="n">
         <v>212.5</v>
       </c>
-      <c r="R152" t="inlineStr"/>
+      <c r="R152" t="n">
+        <v>132.3</v>
+      </c>
       <c r="S152" t="n">
         <v>24.45</v>
       </c>
@@ -11660,7 +11926,9 @@
       <c r="Q153" t="n">
         <v>630</v>
       </c>
-      <c r="R153" t="inlineStr"/>
+      <c r="R153" t="n">
+        <v>505.1</v>
+      </c>
       <c r="S153" t="n">
         <v>55.26</v>
       </c>
@@ -11727,7 +11995,9 @@
       <c r="Q154" t="n">
         <v>39.8</v>
       </c>
-      <c r="R154" t="inlineStr"/>
+      <c r="R154" t="n">
+        <v>864</v>
+      </c>
       <c r="S154" t="n">
         <v>11.12</v>
       </c>
@@ -11800,7 +12070,9 @@
       <c r="Q155" t="n">
         <v>39.3</v>
       </c>
-      <c r="R155" t="inlineStr"/>
+      <c r="R155" t="n">
+        <v>314.6</v>
+      </c>
       <c r="S155" t="n">
         <v>10.74</v>
       </c>
@@ -11873,7 +12145,9 @@
       <c r="Q156" t="n">
         <v>119.5</v>
       </c>
-      <c r="R156" t="inlineStr"/>
+      <c r="R156" t="n">
+        <v>362.6</v>
+      </c>
       <c r="S156" t="n">
         <v>14.5</v>
       </c>
@@ -11946,7 +12220,9 @@
       <c r="Q157" t="n">
         <v>191</v>
       </c>
-      <c r="R157" t="inlineStr"/>
+      <c r="R157" t="n">
+        <v>153.2</v>
+      </c>
       <c r="S157" t="n">
         <v>41.43</v>
       </c>
@@ -12019,7 +12295,9 @@
       <c r="Q158" t="n">
         <v>587</v>
       </c>
-      <c r="R158" t="inlineStr"/>
+      <c r="R158" t="n">
+        <v>6284.4</v>
+      </c>
       <c r="S158" t="n">
         <v>77.84999999999999</v>
       </c>
@@ -12092,7 +12370,9 @@
       <c r="Q159" t="n">
         <v>114</v>
       </c>
-      <c r="R159" t="inlineStr"/>
+      <c r="R159" t="n">
+        <v>803.2</v>
+      </c>
       <c r="S159" t="n">
         <v>96.61</v>
       </c>
@@ -12165,7 +12445,9 @@
       <c r="Q160" t="n">
         <v>144.5</v>
       </c>
-      <c r="R160" t="inlineStr"/>
+      <c r="R160" t="n">
+        <v>11209.5</v>
+      </c>
       <c r="S160" t="n">
         <v>28.73</v>
       </c>
@@ -12238,7 +12520,9 @@
       <c r="Q161" t="n">
         <v>139</v>
       </c>
-      <c r="R161" t="inlineStr"/>
+      <c r="R161" t="n">
+        <v>111.7</v>
+      </c>
       <c r="S161" t="n">
         <v>14.85</v>
       </c>
@@ -12311,7 +12595,9 @@
       <c r="Q162" t="n">
         <v>37.8</v>
       </c>
-      <c r="R162" t="inlineStr"/>
+      <c r="R162" t="n">
+        <v>16.8</v>
+      </c>
       <c r="S162" t="n">
         <v>24.71</v>
       </c>
@@ -12378,7 +12664,9 @@
       <c r="Q163" t="n">
         <v>52</v>
       </c>
-      <c r="R163" t="inlineStr"/>
+      <c r="R163" t="n">
+        <v>832.7</v>
+      </c>
       <c r="S163" t="n">
         <v>17.33</v>
       </c>
@@ -12451,7 +12739,9 @@
       <c r="Q164" t="n">
         <v>462</v>
       </c>
-      <c r="R164" t="inlineStr"/>
+      <c r="R164" t="n">
+        <v>219.4</v>
+      </c>
       <c r="S164" t="n">
         <v>1184.62</v>
       </c>
@@ -12524,7 +12814,9 @@
       <c r="Q165" t="n">
         <v>43</v>
       </c>
-      <c r="R165" t="inlineStr"/>
+      <c r="R165" t="n">
+        <v>77.59999999999999</v>
+      </c>
       <c r="S165" t="n">
         <v>25.32</v>
       </c>
@@ -12597,7 +12889,9 @@
       <c r="Q166" t="n">
         <v>796</v>
       </c>
-      <c r="R166" t="inlineStr"/>
+      <c r="R166" t="n">
+        <v>4194.2</v>
+      </c>
       <c r="S166" t="n">
         <v>195.58</v>
       </c>
@@ -12670,7 +12964,9 @@
       <c r="Q167" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="R167" t="inlineStr"/>
+      <c r="R167" t="n">
+        <v>17</v>
+      </c>
       <c r="S167" t="n">
         <v>26.63</v>
       </c>
@@ -12743,7 +13039,9 @@
       <c r="Q168" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="R168" t="inlineStr"/>
+      <c r="R168" t="n">
+        <v>87.7</v>
+      </c>
       <c r="S168" t="n">
         <v>19.1</v>
       </c>
@@ -12816,7 +13114,9 @@
       <c r="Q169" t="n">
         <v>34</v>
       </c>
-      <c r="R169" t="inlineStr"/>
+      <c r="R169" t="n">
+        <v>1036.3</v>
+      </c>
       <c r="S169" t="n">
         <v>25.76</v>
       </c>
@@ -12889,7 +13189,9 @@
       <c r="Q170" t="n">
         <v>35.1</v>
       </c>
-      <c r="R170" t="inlineStr"/>
+      <c r="R170" t="n">
+        <v>42.2</v>
+      </c>
       <c r="S170" t="n">
         <v>14.75</v>
       </c>
@@ -12962,7 +13264,9 @@
       <c r="Q171" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="R171" t="inlineStr"/>
+      <c r="R171" t="n">
+        <v>71.40000000000001</v>
+      </c>
       <c r="S171" t="n">
         <v>87.52</v>
       </c>
@@ -13035,7 +13339,9 @@
       <c r="Q172" t="n">
         <v>79</v>
       </c>
-      <c r="R172" t="inlineStr"/>
+      <c r="R172" t="n">
+        <v>576.9</v>
+      </c>
       <c r="S172" t="n">
         <v>19.36</v>
       </c>
@@ -13108,7 +13414,9 @@
       <c r="Q173" t="n">
         <v>50.1</v>
       </c>
-      <c r="R173" t="inlineStr"/>
+      <c r="R173" t="n">
+        <v>471.9</v>
+      </c>
       <c r="S173" t="n">
         <v>61.85</v>
       </c>
@@ -13181,7 +13489,9 @@
       <c r="Q174" t="n">
         <v>284.5</v>
       </c>
-      <c r="R174" t="inlineStr"/>
+      <c r="R174" t="n">
+        <v>241.7</v>
+      </c>
       <c r="S174" t="n">
         <v>7.28</v>
       </c>
@@ -13254,7 +13564,9 @@
       <c r="Q175" t="n">
         <v>45.4</v>
       </c>
-      <c r="R175" t="inlineStr"/>
+      <c r="R175" t="n">
+        <v>85.5</v>
+      </c>
       <c r="S175" t="n">
         <v>26.86</v>
       </c>
@@ -13327,7 +13639,9 @@
       <c r="Q176" t="n">
         <v>165.5</v>
       </c>
-      <c r="R176" t="inlineStr"/>
+      <c r="R176" t="n">
+        <v>305.9</v>
+      </c>
       <c r="S176" t="n">
         <v>70.13</v>
       </c>
@@ -13400,7 +13714,9 @@
       <c r="Q177" t="n">
         <v>113.5</v>
       </c>
-      <c r="R177" t="inlineStr"/>
+      <c r="R177" t="n">
+        <v>232.8</v>
+      </c>
       <c r="S177" t="n">
         <v>20.2</v>
       </c>
@@ -13473,7 +13789,9 @@
       <c r="Q178" t="n">
         <v>134.5</v>
       </c>
-      <c r="R178" t="inlineStr"/>
+      <c r="R178" t="n">
+        <v>86.59999999999999</v>
+      </c>
       <c r="S178" t="n">
         <v>23.27</v>
       </c>
@@ -13546,7 +13864,9 @@
       <c r="Q179" t="n">
         <v>36.9</v>
       </c>
-      <c r="R179" t="inlineStr"/>
+      <c r="R179" t="n">
+        <v>35.6</v>
+      </c>
       <c r="S179" t="n">
         <v>35.43</v>
       </c>
@@ -13619,7 +13939,9 @@
       <c r="Q180" t="n">
         <v>245</v>
       </c>
-      <c r="R180" t="inlineStr"/>
+      <c r="R180" t="n">
+        <v>1276.4</v>
+      </c>
       <c r="S180" t="n">
         <v>36.46</v>
       </c>
@@ -13692,7 +14014,9 @@
       <c r="Q181" t="n">
         <v>71.3</v>
       </c>
-      <c r="R181" t="inlineStr"/>
+      <c r="R181" t="n">
+        <v>219.3</v>
+      </c>
       <c r="S181" t="n">
         <v>36.38</v>
       </c>
@@ -13765,7 +14089,9 @@
       <c r="Q182" t="n">
         <v>343.5</v>
       </c>
-      <c r="R182" t="inlineStr"/>
+      <c r="R182" t="n">
+        <v>1215.3</v>
+      </c>
       <c r="S182" t="n">
         <v>75</v>
       </c>
@@ -13913,7 +14239,9 @@
       <c r="Q184" t="n">
         <v>222</v>
       </c>
-      <c r="R184" t="inlineStr"/>
+      <c r="R184" t="n">
+        <v>9990</v>
+      </c>
       <c r="S184" t="n">
         <v>65.88</v>
       </c>
@@ -13986,7 +14314,9 @@
       <c r="Q185" t="n">
         <v>116.5</v>
       </c>
-      <c r="R185" t="inlineStr"/>
+      <c r="R185" t="n">
+        <v>668.3</v>
+      </c>
       <c r="S185" t="n">
         <v>3883.33</v>
       </c>
@@ -14059,7 +14389,9 @@
       <c r="Q186" t="n">
         <v>29.6</v>
       </c>
-      <c r="R186" t="inlineStr"/>
+      <c r="R186" t="n">
+        <v>152.8</v>
+      </c>
       <c r="S186" t="n">
         <v>16.69</v>
       </c>
@@ -14132,7 +14464,9 @@
       <c r="Q187" t="n">
         <v>129</v>
       </c>
-      <c r="R187" t="inlineStr"/>
+      <c r="R187" t="n">
+        <v>183.8</v>
+      </c>
       <c r="S187" t="n">
         <v>65.81999999999999</v>
       </c>
@@ -14280,7 +14614,9 @@
       <c r="Q189" t="n">
         <v>72.2</v>
       </c>
-      <c r="R189" t="inlineStr"/>
+      <c r="R189" t="n">
+        <v>1715.8</v>
+      </c>
       <c r="S189" t="n">
         <v>30.21</v>
       </c>
@@ -14353,7 +14689,9 @@
       <c r="Q190" t="n">
         <v>139</v>
       </c>
-      <c r="R190" t="inlineStr"/>
+      <c r="R190" t="n">
+        <v>401.1</v>
+      </c>
       <c r="S190" t="n">
         <v>339.02</v>
       </c>
@@ -14424,7 +14762,9 @@
       <c r="Q191" t="n">
         <v>187.5</v>
       </c>
-      <c r="R191" t="inlineStr"/>
+      <c r="R191" t="n">
+        <v>69</v>
+      </c>
       <c r="S191" t="n">
         <v>93.28</v>
       </c>
@@ -14495,7 +14835,9 @@
       <c r="Q192" t="n">
         <v>54</v>
       </c>
-      <c r="R192" t="inlineStr"/>
+      <c r="R192" t="n">
+        <v>5144</v>
+      </c>
       <c r="S192" t="n">
         <v>19.35</v>
       </c>
@@ -14568,7 +14910,9 @@
       <c r="Q193" t="n">
         <v>30.9</v>
       </c>
-      <c r="R193" t="inlineStr"/>
+      <c r="R193" t="n">
+        <v>157.6</v>
+      </c>
       <c r="S193" t="n">
         <v>19.22</v>
       </c>
@@ -14716,7 +15060,9 @@
       <c r="Q195" t="n">
         <v>128.5</v>
       </c>
-      <c r="R195" t="inlineStr"/>
+      <c r="R195" t="n">
+        <v>101.6</v>
+      </c>
       <c r="S195" t="n">
         <v>313.41</v>
       </c>
@@ -14864,7 +15210,9 @@
       <c r="Q197" t="n">
         <v>31.6</v>
       </c>
-      <c r="R197" t="inlineStr"/>
+      <c r="R197" t="n">
+        <v>679.7</v>
+      </c>
       <c r="S197" t="n">
         <v>7.7</v>
       </c>
@@ -14937,7 +15285,9 @@
       <c r="Q198" t="n">
         <v>72.90000000000001</v>
       </c>
-      <c r="R198" t="inlineStr"/>
+      <c r="R198" t="n">
+        <v>34.6</v>
+      </c>
       <c r="S198" t="n">
         <v>85.76000000000001</v>
       </c>
@@ -15010,7 +15360,9 @@
       <c r="Q199" t="n">
         <v>10</v>
       </c>
-      <c r="R199" t="inlineStr"/>
+      <c r="R199" t="n">
+        <v>7.4</v>
+      </c>
       <c r="S199" t="n">
         <v>11.63</v>
       </c>
@@ -15083,7 +15435,9 @@
       <c r="Q200" t="n">
         <v>27.6</v>
       </c>
-      <c r="R200" t="inlineStr"/>
+      <c r="R200" t="n">
+        <v>546.8</v>
+      </c>
       <c r="S200" t="n">
         <v>18.01</v>
       </c>
@@ -15156,7 +15510,9 @@
       <c r="Q201" t="n">
         <v>52.5</v>
       </c>
-      <c r="R201" t="inlineStr"/>
+      <c r="R201" t="n">
+        <v>63.1</v>
+      </c>
       <c r="S201" t="n">
         <v>18.49</v>
       </c>
@@ -15229,7 +15585,9 @@
       <c r="Q202" t="n">
         <v>541</v>
       </c>
-      <c r="R202" t="inlineStr"/>
+      <c r="R202" t="n">
+        <v>2293.5</v>
+      </c>
       <c r="S202" t="n">
         <v>103.64</v>
       </c>
@@ -15302,7 +15660,9 @@
       <c r="Q203" t="n">
         <v>400</v>
       </c>
-      <c r="R203" t="inlineStr"/>
+      <c r="R203" t="n">
+        <v>138.3</v>
+      </c>
       <c r="S203" t="n">
         <v>320</v>
       </c>
@@ -15375,7 +15735,9 @@
       <c r="Q204" t="n">
         <v>105.5</v>
       </c>
-      <c r="R204" t="inlineStr"/>
+      <c r="R204" t="n">
+        <v>115.8</v>
+      </c>
       <c r="S204" t="n">
         <v>251.19</v>
       </c>
@@ -15448,7 +15810,9 @@
       <c r="Q205" t="n">
         <v>2375</v>
       </c>
-      <c r="R205" t="inlineStr"/>
+      <c r="R205" t="n">
+        <v>2197.3</v>
+      </c>
       <c r="S205" t="n">
         <v>310.86</v>
       </c>
@@ -15521,7 +15885,9 @@
       <c r="Q206" t="n">
         <v>505</v>
       </c>
-      <c r="R206" t="inlineStr"/>
+      <c r="R206" t="n">
+        <v>15648.1</v>
+      </c>
       <c r="S206" t="n">
         <v>45.21</v>
       </c>
@@ -15594,7 +15960,9 @@
       <c r="Q207" t="n">
         <v>525</v>
       </c>
-      <c r="R207" t="inlineStr"/>
+      <c r="R207" t="n">
+        <v>570.4</v>
+      </c>
       <c r="S207" t="n">
         <v>2019.23</v>
       </c>
@@ -15667,7 +16035,9 @@
       <c r="Q208" t="n">
         <v>66.7</v>
       </c>
-      <c r="R208" t="inlineStr"/>
+      <c r="R208" t="n">
+        <v>35.4</v>
+      </c>
       <c r="S208" t="n">
         <v>68.76000000000001</v>
       </c>
@@ -15740,7 +16110,9 @@
       <c r="Q209" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="R209" t="inlineStr"/>
+      <c r="R209" t="n">
+        <v>2227.6</v>
+      </c>
       <c r="S209" t="n">
         <v>589.23</v>
       </c>
@@ -15813,7 +16185,9 @@
       <c r="Q210" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="R210" t="inlineStr"/>
+      <c r="R210" t="n">
+        <v>355.9</v>
+      </c>
       <c r="S210" t="n">
         <v>40.65</v>
       </c>
@@ -15886,7 +16260,9 @@
       <c r="Q211" t="n">
         <v>902</v>
       </c>
-      <c r="R211" t="inlineStr"/>
+      <c r="R211" t="n">
+        <v>1025</v>
+      </c>
       <c r="S211" t="n">
         <v>5637.5</v>
       </c>
@@ -15959,7 +16335,9 @@
       <c r="Q212" t="n">
         <v>58.3</v>
       </c>
-      <c r="R212" t="inlineStr"/>
+      <c r="R212" t="n">
+        <v>31.6</v>
+      </c>
       <c r="S212" t="n">
         <v>253.48</v>
       </c>
@@ -16032,7 +16410,9 @@
       <c r="Q213" t="n">
         <v>88.5</v>
       </c>
-      <c r="R213" t="inlineStr"/>
+      <c r="R213" t="n">
+        <v>359.9</v>
+      </c>
       <c r="S213" t="n">
         <v>24.25</v>
       </c>
@@ -16105,7 +16485,9 @@
       <c r="Q214" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="R214" t="inlineStr"/>
+      <c r="R214" t="n">
+        <v>130.6</v>
+      </c>
       <c r="S214" t="n">
         <v>69.34</v>
       </c>
@@ -16178,7 +16560,9 @@
       <c r="Q215" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="R215" t="inlineStr"/>
+      <c r="R215" t="n">
+        <v>3462.9</v>
+      </c>
       <c r="S215" t="n">
         <v>46.36</v>
       </c>
@@ -16251,7 +16635,9 @@
       <c r="Q216" t="n">
         <v>66</v>
       </c>
-      <c r="R216" t="inlineStr"/>
+      <c r="R216" t="n">
+        <v>5272.9</v>
+      </c>
       <c r="S216" t="n">
         <v>600</v>
       </c>
@@ -16324,7 +16710,9 @@
       <c r="Q217" t="n">
         <v>69</v>
       </c>
-      <c r="R217" t="inlineStr"/>
+      <c r="R217" t="n">
+        <v>54.7</v>
+      </c>
       <c r="S217" t="n">
         <v>18.75</v>
       </c>
@@ -16712,7 +17100,9 @@
       <c r="Q223" t="n">
         <v>19.6</v>
       </c>
-      <c r="R223" t="inlineStr"/>
+      <c r="R223" t="n">
+        <v>1180.2</v>
+      </c>
       <c r="S223" t="n">
         <v>12.84</v>
       </c>
@@ -17110,7 +17500,9 @@
       <c r="Q229" t="n">
         <v>97.2</v>
       </c>
-      <c r="R229" t="inlineStr"/>
+      <c r="R229" t="n">
+        <v>175.4</v>
+      </c>
       <c r="S229" t="n">
         <v>56.18</v>
       </c>
@@ -17183,7 +17575,9 @@
       <c r="Q230" t="n">
         <v>53.1</v>
       </c>
-      <c r="R230" t="inlineStr"/>
+      <c r="R230" t="n">
+        <v>60.6</v>
+      </c>
       <c r="S230" t="n">
         <v>132.75</v>
       </c>
@@ -17256,7 +17650,9 @@
       <c r="Q231" t="n">
         <v>117.5</v>
       </c>
-      <c r="R231" t="inlineStr"/>
+      <c r="R231" t="n">
+        <v>360.6</v>
+      </c>
       <c r="S231" t="n">
         <v>4.98045135262149e+17</v>
       </c>
@@ -17404,7 +17800,9 @@
       <c r="Q233" t="n">
         <v>70.2</v>
       </c>
-      <c r="R233" t="inlineStr"/>
+      <c r="R233" t="n">
+        <v>80.7</v>
+      </c>
       <c r="S233" t="n">
         <v>34.08</v>
       </c>
@@ -17477,7 +17875,9 @@
       <c r="Q234" t="n">
         <v>54.5</v>
       </c>
-      <c r="R234" t="inlineStr"/>
+      <c r="R234" t="n">
+        <v>29.1</v>
+      </c>
       <c r="S234" t="n">
         <v>2725</v>
       </c>
@@ -17550,7 +17950,9 @@
       <c r="Q235" t="n">
         <v>33.6</v>
       </c>
-      <c r="R235" t="inlineStr"/>
+      <c r="R235" t="n">
+        <v>68.59999999999999</v>
+      </c>
       <c r="S235" t="n">
         <v>16.02</v>
       </c>
@@ -17623,7 +18025,9 @@
       <c r="Q236" t="n">
         <v>564</v>
       </c>
-      <c r="R236" t="inlineStr"/>
+      <c r="R236" t="n">
+        <v>682.1</v>
+      </c>
       <c r="S236" t="n">
         <v>222.92</v>
       </c>
@@ -17696,7 +18100,9 @@
       <c r="Q237" t="n">
         <v>1060</v>
       </c>
-      <c r="R237" t="inlineStr"/>
+      <c r="R237" t="n">
+        <v>4027</v>
+      </c>
       <c r="S237" t="n">
         <v>65.19</v>
       </c>
@@ -17901,7 +18307,9 @@
       <c r="Q240" t="n">
         <v>27.8</v>
       </c>
-      <c r="R240" t="inlineStr"/>
+      <c r="R240" t="n">
+        <v>31</v>
+      </c>
       <c r="S240" t="n">
         <v>308.33</v>
       </c>
@@ -18108,7 +18516,9 @@
       <c r="Q243" t="n">
         <v>21.8</v>
       </c>
-      <c r="R243" t="inlineStr"/>
+      <c r="R243" t="n">
+        <v>14.8</v>
+      </c>
       <c r="S243" t="n">
         <v>121.11</v>
       </c>
@@ -18298,7 +18708,9 @@
       <c r="Q247" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="R247" t="inlineStr"/>
+      <c r="R247" t="n">
+        <v>22.6</v>
+      </c>
       <c r="S247" t="n">
         <v>12.73</v>
       </c>
@@ -18361,7 +18773,9 @@
       <c r="Q248" t="n">
         <v>2040</v>
       </c>
-      <c r="R248" t="inlineStr"/>
+      <c r="R248" t="n">
+        <v>748.4</v>
+      </c>
       <c r="S248" t="n">
         <v>278.31</v>
       </c>

--- a/data/台股財報估值.xlsx
+++ b/data/台股財報估值.xlsx
@@ -658,7 +658,11 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -834,7 +838,11 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -915,7 +923,11 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1376,7 +1388,11 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1647,7 +1663,11 @@
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2488,7 +2508,11 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2569,7 +2593,11 @@
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2650,7 +2678,11 @@
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2826,7 +2858,11 @@
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2907,7 +2943,11 @@
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2988,7 +3028,11 @@
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3259,7 +3303,11 @@
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3430,22 +3478,14 @@
       <c r="W33" t="n">
         <v>17.5</v>
       </c>
-      <c r="X33" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 成長為負(-3%)</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3663,11 @@
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3799,7 +3843,11 @@
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3880,7 +3928,11 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3961,7 +4013,11 @@
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4042,7 +4098,11 @@
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4218,7 +4278,11 @@
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4394,7 +4458,11 @@
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4470,22 +4538,14 @@
       <c r="W45" t="n">
         <v>32.1</v>
       </c>
-      <c r="X45" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>12.56</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>39.8</v>
-      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 成長為負(-3%)</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4723,11 @@
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4934,7 +4998,11 @@
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5110,7 +5178,11 @@
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5286,7 +5358,11 @@
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5462,7 +5538,11 @@
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr"/>
       <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5638,7 +5718,11 @@
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5814,7 +5898,11 @@
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6180,7 +6268,11 @@
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="inlineStr"/>
-      <c r="AC64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6261,7 +6353,11 @@
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6627,7 +6723,11 @@
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
-      <c r="AC69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6803,7 +6903,11 @@
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr"/>
-      <c r="AC71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6979,7 +7083,11 @@
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr"/>
-      <c r="AC73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7060,7 +7168,11 @@
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
-      <c r="AC74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7141,7 +7253,11 @@
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr"/>
-      <c r="AC75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7222,7 +7338,11 @@
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr"/>
-      <c r="AC76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7398,7 +7518,11 @@
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr"/>
-      <c r="AC78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7574,7 +7698,11 @@
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7655,7 +7783,11 @@
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7831,7 +7963,11 @@
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr"/>
-      <c r="AC83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8197,7 +8333,11 @@
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr"/>
-      <c r="AC87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8278,7 +8418,11 @@
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr"/>
       <c r="AB88" t="inlineStr"/>
-      <c r="AC88" t="inlineStr"/>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8359,7 +8503,11 @@
       <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="inlineStr"/>
       <c r="AB89" t="inlineStr"/>
-      <c r="AC89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8720,22 +8868,14 @@
       <c r="W93" t="n">
         <v>52.1</v>
       </c>
-      <c r="X93" t="n">
-        <v>-9</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>15</v>
-      </c>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr"/>
       <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>⏸ 成長為負(-9%)</t>
         </is>
       </c>
     </row>
@@ -8818,7 +8958,11 @@
       <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr"/>
-      <c r="AC94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8899,7 +9043,11 @@
       <c r="Z95" t="inlineStr"/>
       <c r="AA95" t="inlineStr"/>
       <c r="AB95" t="inlineStr"/>
-      <c r="AC95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9170,7 +9318,11 @@
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
-      <c r="AC98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9346,7 +9498,11 @@
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
-      <c r="AC100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9522,7 +9678,11 @@
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr"/>
       <c r="AB102" t="inlineStr"/>
-      <c r="AC102" t="inlineStr"/>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9603,7 +9763,11 @@
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr"/>
       <c r="AB103" t="inlineStr"/>
-      <c r="AC103" t="inlineStr"/>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9684,7 +9848,11 @@
       <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr"/>
       <c r="AB104" t="inlineStr"/>
-      <c r="AC104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9765,7 +9933,11 @@
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr"/>
       <c r="AB105" t="inlineStr"/>
-      <c r="AC105" t="inlineStr"/>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10036,7 +10208,11 @@
       <c r="Z108" t="inlineStr"/>
       <c r="AA108" t="inlineStr"/>
       <c r="AB108" t="inlineStr"/>
-      <c r="AC108" t="inlineStr"/>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10117,7 +10293,11 @@
       <c r="Z109" t="inlineStr"/>
       <c r="AA109" t="inlineStr"/>
       <c r="AB109" t="inlineStr"/>
-      <c r="AC109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10198,7 +10378,11 @@
       <c r="Z110" t="inlineStr"/>
       <c r="AA110" t="inlineStr"/>
       <c r="AB110" t="inlineStr"/>
-      <c r="AC110" t="inlineStr"/>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10279,7 +10463,11 @@
       <c r="Z111" t="inlineStr"/>
       <c r="AA111" t="inlineStr"/>
       <c r="AB111" t="inlineStr"/>
-      <c r="AC111" t="inlineStr"/>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10455,7 +10643,11 @@
       <c r="Z113" t="inlineStr"/>
       <c r="AA113" t="inlineStr"/>
       <c r="AB113" t="inlineStr"/>
-      <c r="AC113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10721,22 +10913,14 @@
       <c r="W116" t="n">
         <v>30.2</v>
       </c>
-      <c r="X116" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="AA116" t="n">
-        <v>52.2</v>
-      </c>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr"/>
       <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 成長為負(-16%)</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11193,11 @@
       <c r="Z119" t="inlineStr"/>
       <c r="AA119" t="inlineStr"/>
       <c r="AB119" t="inlineStr"/>
-      <c r="AC119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11086,7 +11274,11 @@
       <c r="Z120" t="inlineStr"/>
       <c r="AA120" t="inlineStr"/>
       <c r="AB120" t="inlineStr"/>
-      <c r="AC120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11167,7 +11359,11 @@
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="inlineStr"/>
       <c r="AB121" t="inlineStr"/>
-      <c r="AC121" t="inlineStr"/>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11248,7 +11444,11 @@
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr"/>
-      <c r="AC122" t="inlineStr"/>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11519,7 +11719,11 @@
       <c r="Z125" t="inlineStr"/>
       <c r="AA125" t="inlineStr"/>
       <c r="AB125" t="inlineStr"/>
-      <c r="AC125" t="inlineStr"/>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11695,7 +11899,11 @@
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr"/>
-      <c r="AC127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11776,7 +11984,11 @@
       <c r="Z128" t="inlineStr"/>
       <c r="AA128" t="inlineStr"/>
       <c r="AB128" t="inlineStr"/>
-      <c r="AC128" t="inlineStr"/>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11857,7 +12069,11 @@
       <c r="Z129" t="inlineStr"/>
       <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="inlineStr"/>
-      <c r="AC129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12033,7 +12249,11 @@
       <c r="Z131" t="inlineStr"/>
       <c r="AA131" t="inlineStr"/>
       <c r="AB131" t="inlineStr"/>
-      <c r="AC131" t="inlineStr"/>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12299,22 +12519,14 @@
       <c r="W134" t="n">
         <v>22.1</v>
       </c>
-      <c r="X134" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>36</v>
-      </c>
+      <c r="X134" t="inlineStr"/>
+      <c r="Y134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr"/>
+      <c r="AA134" t="inlineStr"/>
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 成長為負(-6%)</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12609,11 @@
       <c r="Z135" t="inlineStr"/>
       <c r="AA135" t="inlineStr"/>
       <c r="AB135" t="inlineStr"/>
-      <c r="AC135" t="inlineStr"/>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12573,7 +12789,11 @@
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr"/>
-      <c r="AC137" t="inlineStr"/>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12654,7 +12874,11 @@
       <c r="Z138" t="inlineStr"/>
       <c r="AA138" t="inlineStr"/>
       <c r="AB138" t="inlineStr"/>
-      <c r="AC138" t="inlineStr"/>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12735,7 +12959,11 @@
       <c r="Z139" t="inlineStr"/>
       <c r="AA139" t="inlineStr"/>
       <c r="AB139" t="inlineStr"/>
-      <c r="AC139" t="inlineStr"/>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12816,7 +13044,11 @@
       <c r="Z140" t="inlineStr"/>
       <c r="AA140" t="inlineStr"/>
       <c r="AB140" t="inlineStr"/>
-      <c r="AC140" t="inlineStr"/>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12897,7 +13129,11 @@
       <c r="Z141" t="inlineStr"/>
       <c r="AA141" t="inlineStr"/>
       <c r="AB141" t="inlineStr"/>
-      <c r="AC141" t="inlineStr"/>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12978,7 +13214,11 @@
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr"/>
-      <c r="AC142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13059,7 +13299,11 @@
       <c r="Z143" t="inlineStr"/>
       <c r="AA143" t="inlineStr"/>
       <c r="AB143" t="inlineStr"/>
-      <c r="AC143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13140,7 +13384,11 @@
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr"/>
       <c r="AB144" t="inlineStr"/>
-      <c r="AC144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13221,7 +13469,11 @@
       <c r="Z145" t="inlineStr"/>
       <c r="AA145" t="inlineStr"/>
       <c r="AB145" t="inlineStr"/>
-      <c r="AC145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13302,7 +13554,11 @@
       <c r="Z146" t="inlineStr"/>
       <c r="AA146" t="inlineStr"/>
       <c r="AB146" t="inlineStr"/>
-      <c r="AC146" t="inlineStr"/>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13383,7 +13639,11 @@
       <c r="Z147" t="inlineStr"/>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr"/>
-      <c r="AC147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13654,7 +13914,11 @@
       <c r="Z150" t="inlineStr"/>
       <c r="AA150" t="inlineStr"/>
       <c r="AB150" t="inlineStr"/>
-      <c r="AC150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13735,7 +13999,11 @@
       <c r="Z151" t="inlineStr"/>
       <c r="AA151" t="inlineStr"/>
       <c r="AB151" t="inlineStr"/>
-      <c r="AC151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13911,7 +14179,11 @@
       <c r="Z153" t="inlineStr"/>
       <c r="AA153" t="inlineStr"/>
       <c r="AB153" t="inlineStr"/>
-      <c r="AC153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13986,7 +14258,11 @@
       <c r="Z154" t="inlineStr"/>
       <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="inlineStr"/>
-      <c r="AC154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14067,7 +14343,11 @@
       <c r="Z155" t="inlineStr"/>
       <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="inlineStr"/>
-      <c r="AC155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14243,7 +14523,11 @@
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="inlineStr"/>
-      <c r="AC157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14324,7 +14608,11 @@
       <c r="Z158" t="inlineStr"/>
       <c r="AA158" t="inlineStr"/>
       <c r="AB158" t="inlineStr"/>
-      <c r="AC158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14405,7 +14693,11 @@
       <c r="Z159" t="inlineStr"/>
       <c r="AA159" t="inlineStr"/>
       <c r="AB159" t="inlineStr"/>
-      <c r="AC159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14581,7 +14873,11 @@
       <c r="Z161" t="inlineStr"/>
       <c r="AA161" t="inlineStr"/>
       <c r="AB161" t="inlineStr"/>
-      <c r="AC161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14662,7 +14958,11 @@
       <c r="Z162" t="inlineStr"/>
       <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="inlineStr"/>
-      <c r="AC162" t="inlineStr"/>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14737,7 +15037,11 @@
       <c r="Z163" t="inlineStr"/>
       <c r="AA163" t="inlineStr"/>
       <c r="AB163" t="inlineStr"/>
-      <c r="AC163" t="inlineStr"/>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14818,7 +15122,11 @@
       <c r="Z164" t="inlineStr"/>
       <c r="AA164" t="inlineStr"/>
       <c r="AB164" t="inlineStr"/>
-      <c r="AC164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14899,7 +15207,11 @@
       <c r="Z165" t="inlineStr"/>
       <c r="AA165" t="inlineStr"/>
       <c r="AB165" t="inlineStr"/>
-      <c r="AC165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14980,7 +15292,11 @@
       <c r="Z166" t="inlineStr"/>
       <c r="AA166" t="inlineStr"/>
       <c r="AB166" t="inlineStr"/>
-      <c r="AC166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15061,7 +15377,11 @@
       <c r="Z167" t="inlineStr"/>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr"/>
-      <c r="AC167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15237,7 +15557,11 @@
       <c r="Z169" t="inlineStr"/>
       <c r="AA169" t="inlineStr"/>
       <c r="AB169" t="inlineStr"/>
-      <c r="AC169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -15318,7 +15642,11 @@
       <c r="Z170" t="inlineStr"/>
       <c r="AA170" t="inlineStr"/>
       <c r="AB170" t="inlineStr"/>
-      <c r="AC170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -15399,7 +15727,11 @@
       <c r="Z171" t="inlineStr"/>
       <c r="AA171" t="inlineStr"/>
       <c r="AB171" t="inlineStr"/>
-      <c r="AC171" t="inlineStr"/>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -15575,7 +15907,11 @@
       <c r="Z173" t="inlineStr"/>
       <c r="AA173" t="inlineStr"/>
       <c r="AB173" t="inlineStr"/>
-      <c r="AC173" t="inlineStr"/>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -15656,7 +15992,11 @@
       <c r="Z174" t="inlineStr"/>
       <c r="AA174" t="inlineStr"/>
       <c r="AB174" t="inlineStr"/>
-      <c r="AC174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -15737,7 +16077,11 @@
       <c r="Z175" t="inlineStr"/>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="inlineStr"/>
-      <c r="AC175" t="inlineStr"/>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -15818,7 +16162,11 @@
       <c r="Z176" t="inlineStr"/>
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr"/>
-      <c r="AC176" t="inlineStr"/>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -15899,7 +16247,11 @@
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr"/>
-      <c r="AC177" t="inlineStr"/>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -15980,7 +16332,11 @@
       <c r="Z178" t="inlineStr"/>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
-      <c r="AC178" t="inlineStr"/>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -16061,7 +16417,11 @@
       <c r="Z179" t="inlineStr"/>
       <c r="AA179" t="inlineStr"/>
       <c r="AB179" t="inlineStr"/>
-      <c r="AC179" t="inlineStr"/>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -16332,7 +16692,11 @@
       <c r="Z182" t="inlineStr"/>
       <c r="AA182" t="inlineStr"/>
       <c r="AB182" t="inlineStr"/>
-      <c r="AC182" t="inlineStr"/>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -16413,7 +16777,11 @@
       <c r="Z183" t="inlineStr"/>
       <c r="AA183" t="inlineStr"/>
       <c r="AB183" t="inlineStr"/>
-      <c r="AC183" t="inlineStr"/>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -16494,7 +16862,11 @@
       <c r="Z184" t="inlineStr"/>
       <c r="AA184" t="inlineStr"/>
       <c r="AB184" t="inlineStr"/>
-      <c r="AC184" t="inlineStr"/>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -16575,7 +16947,11 @@
       <c r="Z185" t="inlineStr"/>
       <c r="AA185" t="inlineStr"/>
       <c r="AB185" t="inlineStr"/>
-      <c r="AC185" t="inlineStr"/>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -16656,7 +17032,11 @@
       <c r="Z186" t="inlineStr"/>
       <c r="AA186" t="inlineStr"/>
       <c r="AB186" t="inlineStr"/>
-      <c r="AC186" t="inlineStr"/>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -16737,7 +17117,11 @@
       <c r="Z187" t="inlineStr"/>
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr"/>
-      <c r="AC187" t="inlineStr"/>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -16818,7 +17202,11 @@
       <c r="Z188" t="inlineStr"/>
       <c r="AA188" t="inlineStr"/>
       <c r="AB188" t="inlineStr"/>
-      <c r="AC188" t="inlineStr"/>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -16899,7 +17287,11 @@
       <c r="Z189" t="inlineStr"/>
       <c r="AA189" t="inlineStr"/>
       <c r="AB189" t="inlineStr"/>
-      <c r="AC189" t="inlineStr"/>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -16980,7 +17372,11 @@
       <c r="Z190" t="inlineStr"/>
       <c r="AA190" t="inlineStr"/>
       <c r="AB190" t="inlineStr"/>
-      <c r="AC190" t="inlineStr"/>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -17138,7 +17534,11 @@
       <c r="Z192" t="inlineStr"/>
       <c r="AA192" t="inlineStr"/>
       <c r="AB192" t="inlineStr"/>
-      <c r="AC192" t="inlineStr"/>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -17219,7 +17619,11 @@
       <c r="Z193" t="inlineStr"/>
       <c r="AA193" t="inlineStr"/>
       <c r="AB193" t="inlineStr"/>
-      <c r="AC193" t="inlineStr"/>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -17300,7 +17704,11 @@
       <c r="Z194" t="inlineStr"/>
       <c r="AA194" t="inlineStr"/>
       <c r="AB194" t="inlineStr"/>
-      <c r="AC194" t="inlineStr"/>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -17381,7 +17789,11 @@
       <c r="Z195" t="inlineStr"/>
       <c r="AA195" t="inlineStr"/>
       <c r="AB195" t="inlineStr"/>
-      <c r="AC195" t="inlineStr"/>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -17462,7 +17874,11 @@
       <c r="Z196" t="inlineStr"/>
       <c r="AA196" t="inlineStr"/>
       <c r="AB196" t="inlineStr"/>
-      <c r="AC196" t="inlineStr"/>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -17543,7 +17959,11 @@
       <c r="Z197" t="inlineStr"/>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr"/>
-      <c r="AC197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -17624,7 +18044,11 @@
       <c r="Z198" t="inlineStr"/>
       <c r="AA198" t="inlineStr"/>
       <c r="AB198" t="inlineStr"/>
-      <c r="AC198" t="inlineStr"/>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -17705,7 +18129,11 @@
       <c r="Z199" t="inlineStr"/>
       <c r="AA199" t="inlineStr"/>
       <c r="AB199" t="inlineStr"/>
-      <c r="AC199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -17786,7 +18214,11 @@
       <c r="Z200" t="inlineStr"/>
       <c r="AA200" t="inlineStr"/>
       <c r="AB200" t="inlineStr"/>
-      <c r="AC200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -17867,7 +18299,11 @@
       <c r="Z201" t="inlineStr"/>
       <c r="AA201" t="inlineStr"/>
       <c r="AB201" t="inlineStr"/>
-      <c r="AC201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -17948,7 +18384,11 @@
       <c r="Z202" t="inlineStr"/>
       <c r="AA202" t="inlineStr"/>
       <c r="AB202" t="inlineStr"/>
-      <c r="AC202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -18029,7 +18469,11 @@
       <c r="Z203" t="inlineStr"/>
       <c r="AA203" t="inlineStr"/>
       <c r="AB203" t="inlineStr"/>
-      <c r="AC203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -18110,7 +18554,11 @@
       <c r="Z204" t="inlineStr"/>
       <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="inlineStr"/>
-      <c r="AC204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -18191,7 +18639,11 @@
       <c r="Z205" t="inlineStr"/>
       <c r="AA205" t="inlineStr"/>
       <c r="AB205" t="inlineStr"/>
-      <c r="AC205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -18272,7 +18724,11 @@
       <c r="Z206" t="inlineStr"/>
       <c r="AA206" t="inlineStr"/>
       <c r="AB206" t="inlineStr"/>
-      <c r="AC206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -18353,7 +18809,11 @@
       <c r="Z207" t="inlineStr"/>
       <c r="AA207" t="inlineStr"/>
       <c r="AB207" t="inlineStr"/>
-      <c r="AC207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -18434,7 +18894,11 @@
       <c r="Z208" t="inlineStr"/>
       <c r="AA208" t="inlineStr"/>
       <c r="AB208" t="inlineStr"/>
-      <c r="AC208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -18515,7 +18979,11 @@
       <c r="Z209" t="inlineStr"/>
       <c r="AA209" t="inlineStr"/>
       <c r="AB209" t="inlineStr"/>
-      <c r="AC209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -18691,7 +19159,11 @@
       <c r="Z211" t="inlineStr"/>
       <c r="AA211" t="inlineStr"/>
       <c r="AB211" t="inlineStr"/>
-      <c r="AC211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -18772,7 +19244,11 @@
       <c r="Z212" t="inlineStr"/>
       <c r="AA212" t="inlineStr"/>
       <c r="AB212" t="inlineStr"/>
-      <c r="AC212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -18853,7 +19329,11 @@
       <c r="Z213" t="inlineStr"/>
       <c r="AA213" t="inlineStr"/>
       <c r="AB213" t="inlineStr"/>
-      <c r="AC213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -18934,7 +19414,11 @@
       <c r="Z214" t="inlineStr"/>
       <c r="AA214" t="inlineStr"/>
       <c r="AB214" t="inlineStr"/>
-      <c r="AC214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -19015,7 +19499,11 @@
       <c r="Z215" t="inlineStr"/>
       <c r="AA215" t="inlineStr"/>
       <c r="AB215" t="inlineStr"/>
-      <c r="AC215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -19096,7 +19584,11 @@
       <c r="Z216" t="inlineStr"/>
       <c r="AA216" t="inlineStr"/>
       <c r="AB216" t="inlineStr"/>
-      <c r="AC216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -19177,7 +19669,11 @@
       <c r="Z217" t="inlineStr"/>
       <c r="AA217" t="inlineStr"/>
       <c r="AB217" t="inlineStr"/>
-      <c r="AC217" t="inlineStr"/>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -19248,7 +19744,11 @@
       <c r="Z218" t="inlineStr"/>
       <c r="AA218" t="inlineStr"/>
       <c r="AB218" t="inlineStr"/>
-      <c r="AC218" t="inlineStr"/>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -19319,7 +19819,11 @@
       <c r="Z219" t="inlineStr"/>
       <c r="AA219" t="inlineStr"/>
       <c r="AB219" t="inlineStr"/>
-      <c r="AC219" t="inlineStr"/>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -19475,7 +19979,11 @@
       <c r="Z221" t="inlineStr"/>
       <c r="AA221" t="inlineStr"/>
       <c r="AB221" t="inlineStr"/>
-      <c r="AC221" t="inlineStr"/>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -19716,7 +20224,11 @@
       <c r="Z224" t="inlineStr"/>
       <c r="AA224" t="inlineStr"/>
       <c r="AB224" t="inlineStr"/>
-      <c r="AC224" t="inlineStr"/>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -19787,7 +20299,11 @@
       <c r="Z225" t="inlineStr"/>
       <c r="AA225" t="inlineStr"/>
       <c r="AB225" t="inlineStr"/>
-      <c r="AC225" t="inlineStr"/>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -19858,7 +20374,11 @@
       <c r="Z226" t="inlineStr"/>
       <c r="AA226" t="inlineStr"/>
       <c r="AB226" t="inlineStr"/>
-      <c r="AC226" t="inlineStr"/>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -19929,7 +20449,11 @@
       <c r="Z227" t="inlineStr"/>
       <c r="AA227" t="inlineStr"/>
       <c r="AB227" t="inlineStr"/>
-      <c r="AC227" t="inlineStr"/>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -20000,7 +20524,11 @@
       <c r="Z228" t="inlineStr"/>
       <c r="AA228" t="inlineStr"/>
       <c r="AB228" t="inlineStr"/>
-      <c r="AC228" t="inlineStr"/>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -20081,7 +20609,11 @@
       <c r="Z229" t="inlineStr"/>
       <c r="AA229" t="inlineStr"/>
       <c r="AB229" t="inlineStr"/>
-      <c r="AC229" t="inlineStr"/>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -20162,7 +20694,11 @@
       <c r="Z230" t="inlineStr"/>
       <c r="AA230" t="inlineStr"/>
       <c r="AB230" t="inlineStr"/>
-      <c r="AC230" t="inlineStr"/>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -20243,7 +20779,11 @@
       <c r="Z231" t="inlineStr"/>
       <c r="AA231" t="inlineStr"/>
       <c r="AB231" t="inlineStr"/>
-      <c r="AC231" t="inlineStr"/>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -20324,7 +20864,11 @@
       <c r="Z232" t="inlineStr"/>
       <c r="AA232" t="inlineStr"/>
       <c r="AB232" t="inlineStr"/>
-      <c r="AC232" t="inlineStr"/>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -20405,7 +20949,11 @@
       <c r="Z233" t="inlineStr"/>
       <c r="AA233" t="inlineStr"/>
       <c r="AB233" t="inlineStr"/>
-      <c r="AC233" t="inlineStr"/>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -20486,7 +21034,11 @@
       <c r="Z234" t="inlineStr"/>
       <c r="AA234" t="inlineStr"/>
       <c r="AB234" t="inlineStr"/>
-      <c r="AC234" t="inlineStr"/>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -20567,7 +21119,11 @@
       <c r="Z235" t="inlineStr"/>
       <c r="AA235" t="inlineStr"/>
       <c r="AB235" t="inlineStr"/>
-      <c r="AC235" t="inlineStr"/>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -20648,7 +21204,11 @@
       <c r="Z236" t="inlineStr"/>
       <c r="AA236" t="inlineStr"/>
       <c r="AB236" t="inlineStr"/>
-      <c r="AC236" t="inlineStr"/>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -20729,7 +21289,11 @@
       <c r="Z237" t="inlineStr"/>
       <c r="AA237" t="inlineStr"/>
       <c r="AB237" t="inlineStr"/>
-      <c r="AC237" t="inlineStr"/>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -20802,7 +21366,11 @@
       <c r="Z238" t="inlineStr"/>
       <c r="AA238" t="inlineStr"/>
       <c r="AB238" t="inlineStr"/>
-      <c r="AC238" t="inlineStr"/>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -20873,7 +21441,11 @@
       <c r="Z239" t="inlineStr"/>
       <c r="AA239" t="inlineStr"/>
       <c r="AB239" t="inlineStr"/>
-      <c r="AC239" t="inlineStr"/>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -20954,7 +21526,11 @@
       <c r="Z240" t="inlineStr"/>
       <c r="AA240" t="inlineStr"/>
       <c r="AB240" t="inlineStr"/>
-      <c r="AC240" t="inlineStr"/>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -21027,7 +21603,11 @@
       <c r="Z241" t="inlineStr"/>
       <c r="AA241" t="inlineStr"/>
       <c r="AB241" t="inlineStr"/>
-      <c r="AC241" t="inlineStr"/>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -21100,7 +21680,11 @@
       <c r="Z242" t="inlineStr"/>
       <c r="AA242" t="inlineStr"/>
       <c r="AB242" t="inlineStr"/>
-      <c r="AC242" t="inlineStr"/>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -21181,7 +21765,11 @@
       <c r="Z243" t="inlineStr"/>
       <c r="AA243" t="inlineStr"/>
       <c r="AB243" t="inlineStr"/>
-      <c r="AC243" t="inlineStr"/>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">

--- a/data/台股財報估值.xlsx
+++ b/data/台股財報估值.xlsx
@@ -23293,7 +23293,11 @@
           <t>兆豐金</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D243" t="inlineStr">
         <is>
           <t>2026-03-31</t>
@@ -23375,7 +23379,11 @@
           <t>合庫金</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D244" t="inlineStr">
         <is>
           <t>2026-03-31</t>
@@ -44309,7 +44317,11 @@
           <t>兆豐金</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D243" t="n">
         <v>0</v>
       </c>
@@ -44385,7 +44397,11 @@
           <t>合庫金</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>🏦</t>
+        </is>
+      </c>
       <c r="D244" t="n">
         <v>0</v>
       </c>
